--- a/data/May/InternalDailyReport.xlsx
+++ b/data/May/InternalDailyReport.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B08A2CF-0D78-4FBC-B3C7-0AFFC0A84373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571D6E50-D714-411D-8667-43F5EE129573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId2"/>
+    <sheet name="04-05" sheetId="8" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$2:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'04-05'!$A$2:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +62,643 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="299">
+  <si>
+    <t>Tình trạng TT</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>TÊN KH</t>
+  </si>
+  <si>
+    <t>MÃ</t>
+  </si>
+  <si>
+    <t>ĐỊA CHỈ</t>
+  </si>
+  <si>
+    <t>QUẬN</t>
+  </si>
+  <si>
+    <t>TIỀN THU</t>
+  </si>
+  <si>
+    <t>TIỀN SHIP</t>
+  </si>
+  <si>
+    <t>TIỀN HÀNG</t>
+  </si>
+  <si>
+    <t>NGƯỜI ĐI</t>
+  </si>
+  <si>
+    <t>NGƯỜI LẤY</t>
+  </si>
+  <si>
+    <t>NGÀY LẤY</t>
+  </si>
+  <si>
+    <t>GHI CHÚ</t>
+  </si>
+  <si>
+    <t>ỨNG TIỀN</t>
+  </si>
+  <si>
+    <t>HÀNG TỒN</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>hàng sỉ</t>
+  </si>
+  <si>
+    <t>ĐOÀN NGÂN CHÂU</t>
+  </si>
+  <si>
+    <t>MAI CHI</t>
+  </si>
+  <si>
+    <t>toa BS16 - The oasis - vinhome grand park</t>
+  </si>
+  <si>
+    <t>a.quyen</t>
+  </si>
+  <si>
+    <t>c.cuong</t>
+  </si>
+  <si>
+    <t>01-05-2026</t>
+  </si>
+  <si>
+    <t>Thu Lê</t>
+  </si>
+  <si>
+    <t>HD017813</t>
+  </si>
+  <si>
+    <t>293 vành đai trong, P.Bình trị đông B</t>
+  </si>
+  <si>
+    <t>binh tan</t>
+  </si>
+  <si>
+    <t>AT 01-05</t>
+  </si>
+  <si>
+    <t>Như Quỳnh</t>
+  </si>
+  <si>
+    <t>HD017879</t>
+  </si>
+  <si>
+    <t>56/13/18 huỳnh thị hai phường tân chánh hiệp</t>
+  </si>
+  <si>
+    <t>C Thảo Thao Nguyen</t>
+  </si>
+  <si>
+    <t>HD017906</t>
+  </si>
+  <si>
+    <t>111/8B Trường Chinh, phường Đông Hưng Thuận</t>
+  </si>
+  <si>
+    <t>Kim Bình</t>
+  </si>
+  <si>
+    <t>HD018057</t>
+  </si>
+  <si>
+    <t>1253 phạm thế hiển p5</t>
+  </si>
+  <si>
+    <t>Ánh Linh</t>
+  </si>
+  <si>
+    <t>HD018056</t>
+  </si>
+  <si>
+    <t>Toà A chung cư diamond 49C lê quang kim p8</t>
+  </si>
+  <si>
+    <t>W3235</t>
+  </si>
+  <si>
+    <t>HD017713</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp 21, Tổ 3,Kp3</t>
+  </si>
+  <si>
+    <t>Đỗ Nhi</t>
+  </si>
+  <si>
+    <t>HD017976</t>
+  </si>
+  <si>
+    <t>25/49/15/8 nguyễn minh châu</t>
+  </si>
+  <si>
+    <t>tan phu</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Khánh Ly</t>
+  </si>
+  <si>
+    <t>HD017945</t>
+  </si>
+  <si>
+    <t>Chung cư akari block 9</t>
+  </si>
+  <si>
+    <t>Võ Thục Trinh</t>
+  </si>
+  <si>
+    <t>HD017966</t>
+  </si>
+  <si>
+    <t>Chung cư Topaz City block A1, 39 Cao Lỗ P4</t>
+  </si>
+  <si>
+    <t>Hang Nguyen fb Bella Nguyen</t>
+  </si>
+  <si>
+    <t>HD018060</t>
+  </si>
+  <si>
+    <t>10/23 chiến lược p bình trị đông</t>
+  </si>
+  <si>
+    <t>Ruby Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018067</t>
+  </si>
+  <si>
+    <t>M37/15 Cư Xá Phú Lâm A Phường 12</t>
+  </si>
+  <si>
+    <t>Diễn Phan</t>
+  </si>
+  <si>
+    <t>HD017789</t>
+  </si>
+  <si>
+    <t>11/26/14 đường nam cao, p tân phú</t>
+  </si>
+  <si>
+    <t>fb Thuyên Quyên</t>
+  </si>
+  <si>
+    <t>HD018007</t>
+  </si>
+  <si>
+    <t>68B/23/1C hương lộ 2, phường bình trị đông A</t>
+  </si>
+  <si>
+    <t>Hoa Tuyết</t>
+  </si>
+  <si>
+    <t>HD017605</t>
+  </si>
+  <si>
+    <t>126A/4 tổ 17 trung mỹ tây</t>
+  </si>
+  <si>
+    <t>ng nhận Duyên Mai</t>
+  </si>
+  <si>
+    <t>HD017665</t>
+  </si>
+  <si>
+    <t>lexington residence block c67 Mai chí thọ An Phú</t>
+  </si>
+  <si>
+    <t>MM QUYNH - GỬI HÀO</t>
+  </si>
+  <si>
+    <t>HD017748</t>
+  </si>
+  <si>
+    <t>22 đường tân thới nhất 1B, khu phố 5, phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Natalie Truong</t>
+  </si>
+  <si>
+    <t>HD017560</t>
+  </si>
+  <si>
+    <t>189/46A Bạch Đằng P3</t>
+  </si>
+  <si>
+    <t>go vap</t>
+  </si>
+  <si>
+    <t>Tran Thu</t>
+  </si>
+  <si>
+    <t>HD017899</t>
+  </si>
+  <si>
+    <t>76/14/6 duong so 7 linh trung</t>
+  </si>
+  <si>
+    <t>thu duc</t>
+  </si>
+  <si>
+    <t>Tran Thi Thuy Trang</t>
+  </si>
+  <si>
+    <t>HD017894</t>
+  </si>
+  <si>
+    <t>184 nguyễn xí- cc Bắc Đinh Bộ Lĩnh - lô A82 căn cầu thang cuối cùng, Phường 26</t>
+  </si>
+  <si>
+    <t>binh thanh</t>
+  </si>
+  <si>
+    <t>Trần Thảo Na</t>
+  </si>
+  <si>
+    <t>HD018101</t>
+  </si>
+  <si>
+    <t>74/5/47A đường số 9 phường an hội đông</t>
+  </si>
+  <si>
+    <t>Triệu Vy _ Cindy</t>
+  </si>
+  <si>
+    <t>HD017806</t>
+  </si>
+  <si>
+    <t>403 Tân Sơn, p12</t>
+  </si>
+  <si>
+    <t>Nguyễn Ánh Dương</t>
+  </si>
+  <si>
+    <t>HD017964</t>
+  </si>
+  <si>
+    <t>382/3/22 nguyễn thái sơn khu phố 1 phường An Nhơn</t>
+  </si>
+  <si>
+    <t>tan binh</t>
+  </si>
+  <si>
+    <t>Nguyễn bảo trân</t>
+  </si>
+  <si>
+    <t>HD017961</t>
+  </si>
+  <si>
+    <t>68/6 Thống Nhất, p10</t>
+  </si>
+  <si>
+    <t>Thu Thảo</t>
+  </si>
+  <si>
+    <t>HD018090</t>
+  </si>
+  <si>
+    <t>401 /21 phường 8, Nguyễn văn khối</t>
+  </si>
+  <si>
+    <t>Chi</t>
+  </si>
+  <si>
+    <t>HD017710</t>
+  </si>
+  <si>
+    <t>Block B, B607 Chung cư Dreamhome 2 đường số 59, Phường 14</t>
+  </si>
+  <si>
+    <t>Hứa Tuyên</t>
+  </si>
+  <si>
+    <t>HD018021</t>
+  </si>
+  <si>
+    <t>939 Nguyễn kiệm phường Hạnh Thông</t>
+  </si>
+  <si>
+    <t>Mộng Thuý Trảo</t>
+  </si>
+  <si>
+    <t>HD017827</t>
+  </si>
+  <si>
+    <t>53A kha vạn cân, kp1, hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>Ngọc Ánh</t>
+  </si>
+  <si>
+    <t>HD018053</t>
+  </si>
+  <si>
+    <t>236/43/9 điện biên phủ</t>
+  </si>
+  <si>
+    <t>An An</t>
+  </si>
+  <si>
+    <t>HD017441</t>
+  </si>
+  <si>
+    <t>374 Xô viết nghệ tĩnh, P25</t>
+  </si>
+  <si>
+    <t>Ngân Phan</t>
+  </si>
+  <si>
+    <t>HD017688</t>
+  </si>
+  <si>
+    <t>Chung cư Sarina tháp B (Sarina 1B), đường B2, mặt sau đường Hoàng Thế Thiện, Phường An Khánh</t>
+  </si>
+  <si>
+    <t>Mén HM</t>
+  </si>
+  <si>
+    <t>HD017895</t>
+  </si>
+  <si>
+    <t>Toà landmark 2</t>
+  </si>
+  <si>
+    <t>Trúc Phương</t>
+  </si>
+  <si>
+    <t>HD017982</t>
+  </si>
+  <si>
+    <t>Chung cư citiesto, cát lái</t>
+  </si>
+  <si>
+    <t>đổi hàng</t>
+  </si>
+  <si>
+    <t>BOS BMB</t>
+  </si>
+  <si>
+    <t>119 hoàng diệu 2 linh trung</t>
+  </si>
+  <si>
+    <t>jenny bouti</t>
+  </si>
+  <si>
+    <t>401 Quang trung f10</t>
+  </si>
+  <si>
+    <t>Nguyễn Havy</t>
+  </si>
+  <si>
+    <t>HD017867</t>
+  </si>
+  <si>
+    <t>CC The Park Residence, 12 Nguyễn Hữu Thọ, Phước Kiển</t>
+  </si>
+  <si>
+    <t>nha be</t>
+  </si>
+  <si>
+    <t>c.hieu</t>
+  </si>
+  <si>
+    <t>Minơ fb Lê Tú</t>
+  </si>
+  <si>
+    <t>HD017844</t>
+  </si>
+  <si>
+    <t>chung cư Sài Gòn Mia - lock A ) 200 đường số 9A- xã bình hưng</t>
+  </si>
+  <si>
+    <t>binh chanh</t>
+  </si>
+  <si>
+    <t>Phuong Thaoo</t>
+  </si>
+  <si>
+    <t>HD018004</t>
+  </si>
+  <si>
+    <t>12c trần phú p4</t>
+  </si>
+  <si>
+    <t>Trang Lưu</t>
+  </si>
+  <si>
+    <t>HD017868</t>
+  </si>
+  <si>
+    <t>223/2G phạm viết chánh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>Yun Sokhour D17386666</t>
+  </si>
+  <si>
+    <t>HD017709</t>
+  </si>
+  <si>
+    <t>nhà xe Khải nam</t>
+  </si>
+  <si>
+    <t>Uyên Thư</t>
+  </si>
+  <si>
+    <t>HD017958</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Chiêu Phường Bàn Cờ</t>
+  </si>
+  <si>
+    <t>Mỹ Kiều</t>
+  </si>
+  <si>
+    <t>HD017795</t>
+  </si>
+  <si>
+    <t>51 lê quý đôn phường xuân hòa</t>
+  </si>
+  <si>
+    <t>Thu Thuỷ</t>
+  </si>
+  <si>
+    <t>HD018074</t>
+  </si>
+  <si>
+    <t>181 đường 79 tân quy</t>
+  </si>
+  <si>
+    <t>Trần Ngọc trang - malaysia - Tuyên</t>
+  </si>
+  <si>
+    <t>HD017715</t>
+  </si>
+  <si>
+    <t>36/15 yên thế, phường 2</t>
+  </si>
+  <si>
+    <t>Yin Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017561</t>
+  </si>
+  <si>
+    <t>116a đường số 16 p tân quy</t>
+  </si>
+  <si>
+    <t>anh phước (đồ của chị yến)</t>
+  </si>
+  <si>
+    <t>HD017832</t>
+  </si>
+  <si>
+    <t>241 lê thánh tôn, p. bến thành</t>
+  </si>
+  <si>
+    <t>shop chịu ship</t>
+  </si>
+  <si>
+    <t>Nhu Thanh</t>
+  </si>
+  <si>
+    <t>HD017793</t>
+  </si>
+  <si>
+    <t>99 D1 Hoàng Trọng Mậu, Him Lam, Tân Hưng</t>
+  </si>
+  <si>
+    <t>Mone Ng</t>
+  </si>
+  <si>
+    <t>HD017667</t>
+  </si>
+  <si>
+    <t>Sky Garden 2 p tân phong PMH</t>
+  </si>
+  <si>
+    <t>Kimmie Van</t>
+  </si>
+  <si>
+    <t>HD017625</t>
+  </si>
+  <si>
+    <t>645/48 đường Trần Xuân Soạn p. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Mai Anh</t>
+  </si>
+  <si>
+    <t>HD017687</t>
+  </si>
+  <si>
+    <t>109/22/14 Dương Bá Trạc p1</t>
+  </si>
+  <si>
+    <t>Ngọc Phạm</t>
+  </si>
+  <si>
+    <t>HD017869</t>
+  </si>
+  <si>
+    <t>80 BÀ HUYỆN THANH QUAN, P.9</t>
+  </si>
+  <si>
+    <t>bảo bảo fb Phương Phương</t>
+  </si>
+  <si>
+    <t>HD017593</t>
+  </si>
+  <si>
+    <t>132 bến vân đồn p5</t>
+  </si>
+  <si>
+    <t>Thao My</t>
+  </si>
+  <si>
+    <t>HD017676</t>
+  </si>
+  <si>
+    <t>346 Bên Vân đồn f1 Chung cư Gold View</t>
+  </si>
+  <si>
+    <t>MAI TRẦN</t>
+  </si>
+  <si>
+    <t>135 hải thượng lãn ông P10</t>
+  </si>
+  <si>
+    <t>Tiền</t>
+  </si>
+  <si>
+    <t>Số đơn</t>
+  </si>
+  <si>
+    <t>Tiền Thu</t>
+  </si>
+  <si>
+    <t>lợi nhuận</t>
+  </si>
+  <si>
+    <t>cod</t>
+  </si>
+  <si>
+    <t>Sài Gòn</t>
+  </si>
+  <si>
+    <t>TỔNG ĐƠN NHẬN</t>
+  </si>
+  <si>
+    <t>at 01-05</t>
+  </si>
+  <si>
+    <t>Trừ Ship</t>
+  </si>
+  <si>
+    <t>tiền ship</t>
+  </si>
+  <si>
+    <t>Đơn trả &amp; c.khoản</t>
+  </si>
+  <si>
+    <t>tiền lấy</t>
+  </si>
+  <si>
+    <t>Tiền Hàng Hcm</t>
+  </si>
+  <si>
+    <t>đơn trả</t>
+  </si>
+  <si>
+    <t>đền đơn</t>
+  </si>
+  <si>
+    <t>đơn cũ ck</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>nợ cũ</t>
+  </si>
+  <si>
+    <t>tổng</t>
+  </si>
+  <si>
+    <t>THANH TOÁN</t>
+  </si>
+  <si>
+    <t>CK Đủ 100%</t>
+  </si>
   <si>
     <t>THÁNG 5</t>
   </si>
@@ -92,640 +730,235 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Tình trạng TT</t>
-  </si>
-  <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>TÊN KH</t>
-  </si>
-  <si>
-    <t>MÃ</t>
-  </si>
-  <si>
-    <t>ĐỊA CHỈ</t>
-  </si>
-  <si>
-    <t>QUẬN</t>
-  </si>
-  <si>
-    <t>TIỀN THU</t>
-  </si>
-  <si>
-    <t>TIỀN SHIP</t>
-  </si>
-  <si>
-    <t>TIỀN HÀNG</t>
-  </si>
-  <si>
-    <t>NGƯỜI ĐI</t>
-  </si>
-  <si>
-    <t>NGƯỜI LẤY</t>
-  </si>
-  <si>
-    <t>NGÀY LẤY</t>
-  </si>
-  <si>
-    <t>GHI CHÚ</t>
-  </si>
-  <si>
-    <t>ỨNG TIỀN</t>
-  </si>
-  <si>
-    <t>HÀNG TỒN</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>ĐOÀN NGÂN CHÂU</t>
-  </si>
-  <si>
-    <t>Thu Lê</t>
-  </si>
-  <si>
-    <t>HD017813</t>
-  </si>
-  <si>
-    <t>293 vành đai trong, P.Bình trị đông B</t>
-  </si>
-  <si>
-    <t>binh tan</t>
-  </si>
-  <si>
-    <t>AT 01-05</t>
-  </si>
-  <si>
-    <t>c.cuong</t>
-  </si>
-  <si>
-    <t>01-05-2026</t>
-  </si>
-  <si>
-    <t>Như Quỳnh</t>
-  </si>
-  <si>
-    <t>HD017879</t>
-  </si>
-  <si>
-    <t>56/13/18 huỳnh thị hai phường tân chánh hiệp</t>
-  </si>
-  <si>
-    <t>C Thảo Thao Nguyen</t>
-  </si>
-  <si>
-    <t>HD017906</t>
-  </si>
-  <si>
-    <t>111/8B Trường Chinh, phường Đông Hưng Thuận</t>
-  </si>
-  <si>
-    <t>Nguyễn Havy</t>
-  </si>
-  <si>
-    <t>HD017867</t>
-  </si>
-  <si>
-    <t>CC The Park Residence, 12 Nguyễn Hữu Thọ, Phước Kiển</t>
-  </si>
-  <si>
-    <t>nha be</t>
-  </si>
-  <si>
-    <t>c.hieu</t>
-  </si>
-  <si>
-    <t>Kim Bình</t>
-  </si>
-  <si>
-    <t>HD018057</t>
-  </si>
-  <si>
-    <t>1253 phạm thế hiển p5</t>
-  </si>
-  <si>
-    <t>Ánh Linh</t>
-  </si>
-  <si>
-    <t>HD018056</t>
-  </si>
-  <si>
-    <t>Toà A chung cư diamond 49C lê quang kim p8</t>
-  </si>
-  <si>
-    <t>ng nhận Duyên Mai</t>
-  </si>
-  <si>
-    <t>HD017665</t>
-  </si>
-  <si>
-    <t>lexington residence block c67 Mai chí thọ An Phú</t>
-  </si>
-  <si>
-    <t>Minơ fb Lê Tú</t>
-  </si>
-  <si>
-    <t>HD017844</t>
-  </si>
-  <si>
-    <t>chung cư Sài Gòn Mia - lock A ) 200 đường số 9A- xã bình hưng</t>
-  </si>
-  <si>
-    <t>binh chanh</t>
-  </si>
-  <si>
-    <t>W3235</t>
-  </si>
-  <si>
-    <t>HD017713</t>
-  </si>
-  <si>
-    <t>375 tân thới hiệp 21, Tổ 3,Kp3</t>
-  </si>
-  <si>
-    <t>Phuong Thaoo</t>
-  </si>
-  <si>
-    <t>HD018004</t>
-  </si>
-  <si>
-    <t>12c trần phú p4</t>
-  </si>
-  <si>
-    <t>Trang Lưu</t>
-  </si>
-  <si>
-    <t>HD017868</t>
-  </si>
-  <si>
-    <t>223/2G phạm viết chánh phường nguyễn cư trinh</t>
-  </si>
-  <si>
-    <t>MM QUYNH - GỬI HÀO</t>
-  </si>
-  <si>
-    <t>HD017748</t>
-  </si>
-  <si>
-    <t>22 đường tân thới nhất 1B, khu phố 5, phường Tân Thới Nhất</t>
-  </si>
-  <si>
-    <t>Natalie Truong</t>
-  </si>
-  <si>
-    <t>HD017560</t>
-  </si>
-  <si>
-    <t>189/46A Bạch Đằng P3</t>
-  </si>
-  <si>
-    <t>go vap</t>
-  </si>
-  <si>
-    <t>Yun Sokhour D17386666</t>
-  </si>
-  <si>
-    <t>HD017709</t>
-  </si>
-  <si>
-    <t>nhà xe Khải nam</t>
-  </si>
-  <si>
-    <t>Tran Thu</t>
-  </si>
-  <si>
-    <t>HD017899</t>
-  </si>
-  <si>
-    <t>76/14/6 duong so 7 linh trung</t>
-  </si>
-  <si>
-    <t>thu duc</t>
-  </si>
-  <si>
-    <t>Tran Thi Thuy Trang</t>
-  </si>
-  <si>
-    <t>HD017894</t>
-  </si>
-  <si>
-    <t>184 nguyễn xí- cc Bắc Đinh Bộ Lĩnh - lô A82 căn cầu thang cuối cùng, Phường 26</t>
-  </si>
-  <si>
-    <t>binh thanh</t>
-  </si>
-  <si>
-    <t>Đỗ Nhi</t>
-  </si>
-  <si>
-    <t>HD017976</t>
-  </si>
-  <si>
-    <t>25/49/15/8 nguyễn minh châu</t>
-  </si>
-  <si>
-    <t>tan phu</t>
-  </si>
-  <si>
-    <t>Trần Thảo Na</t>
-  </si>
-  <si>
-    <t>HD018101</t>
-  </si>
-  <si>
-    <t>74/5/47A đường số 9 phường an hội đông</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Khánh Ly</t>
-  </si>
-  <si>
-    <t>HD017945</t>
-  </si>
-  <si>
-    <t>Chung cư akari block 9</t>
-  </si>
-  <si>
-    <t>Triệu Vy _ Cindy</t>
-  </si>
-  <si>
-    <t>HD017806</t>
-  </si>
-  <si>
-    <t>403 Tân Sơn, p12</t>
-  </si>
-  <si>
-    <t>Uyên Thư</t>
-  </si>
-  <si>
-    <t>HD017958</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Chiêu Phường Bàn Cờ</t>
-  </si>
-  <si>
-    <t>Nguyễn Ánh Dương</t>
-  </si>
-  <si>
-    <t>HD017964</t>
-  </si>
-  <si>
-    <t>382/3/22 nguyễn thái sơn khu phố 1 phường An Nhơn</t>
-  </si>
-  <si>
-    <t>tan binh</t>
-  </si>
-  <si>
-    <t>Nguyễn bảo trân</t>
-  </si>
-  <si>
-    <t>HD017961</t>
-  </si>
-  <si>
-    <t>68/6 Thống Nhất, p10</t>
-  </si>
-  <si>
-    <t>Võ Thục Trinh</t>
-  </si>
-  <si>
-    <t>HD017966</t>
-  </si>
-  <si>
-    <t>Chung cư Topaz City block A1, 39 Cao Lỗ P4</t>
-  </si>
-  <si>
-    <t>Mỹ Kiều</t>
-  </si>
-  <si>
-    <t>HD017795</t>
-  </si>
-  <si>
-    <t>51 lê quý đôn phường xuân hòa</t>
-  </si>
-  <si>
-    <t>Thu Thảo</t>
-  </si>
-  <si>
-    <t>HD018090</t>
-  </si>
-  <si>
-    <t>401 /21 phường 8, Nguyễn văn khối</t>
-  </si>
-  <si>
-    <t>Hang Nguyen fb Bella Nguyen</t>
-  </si>
-  <si>
-    <t>HD018060</t>
-  </si>
-  <si>
-    <t>10/23 chiến lược p bình trị đông</t>
-  </si>
-  <si>
-    <t>Chi</t>
-  </si>
-  <si>
-    <t>HD017710</t>
-  </si>
-  <si>
-    <t>Block B, B607 Chung cư Dreamhome 2 đường số 59, Phường 14</t>
-  </si>
-  <si>
-    <t>Hứa Tuyên</t>
-  </si>
-  <si>
-    <t>HD018021</t>
-  </si>
-  <si>
-    <t>939 Nguyễn kiệm phường Hạnh Thông</t>
-  </si>
-  <si>
-    <t>Ruby Nguyễn</t>
-  </si>
-  <si>
-    <t>HD018067</t>
-  </si>
-  <si>
-    <t>M37/15 Cư Xá Phú Lâm A Phường 12</t>
-  </si>
-  <si>
-    <t>Thu Thuỷ</t>
-  </si>
-  <si>
-    <t>HD018074</t>
-  </si>
-  <si>
-    <t>181 đường 79 tân quy</t>
-  </si>
-  <si>
-    <t>Trần Ngọc trang - malaysia - Tuyên</t>
-  </si>
-  <si>
-    <t>HD017715</t>
-  </si>
-  <si>
-    <t>36/15 yên thế, phường 2</t>
-  </si>
-  <si>
-    <t>Yin Nguyễn</t>
-  </si>
-  <si>
-    <t>HD017561</t>
-  </si>
-  <si>
-    <t>116a đường số 16 p tân quy</t>
-  </si>
-  <si>
-    <t>Mộng Thuý Trảo</t>
-  </si>
-  <si>
-    <t>HD017827</t>
-  </si>
-  <si>
-    <t>53A kha vạn cân, kp1, hiệp bình chánh</t>
-  </si>
-  <si>
-    <t>anh phước (đồ của chị yến)</t>
-  </si>
-  <si>
-    <t>HD017832</t>
-  </si>
-  <si>
-    <t>241 lê thánh tôn, p. bến thành</t>
-  </si>
-  <si>
-    <t>shop chịu ship</t>
-  </si>
-  <si>
-    <t>Diễn Phan</t>
-  </si>
-  <si>
-    <t>HD017789</t>
-  </si>
-  <si>
-    <t>11/26/14 đường nam cao, p tân phú</t>
-  </si>
-  <si>
-    <t>Ngọc Ánh</t>
-  </si>
-  <si>
-    <t>HD018053</t>
-  </si>
-  <si>
-    <t>236/43/9 điện biên phủ</t>
-  </si>
-  <si>
-    <t>Nhu Thanh</t>
-  </si>
-  <si>
-    <t>HD017793</t>
-  </si>
-  <si>
-    <t>99 D1 Hoàng Trọng Mậu, Him Lam, Tân Hưng</t>
-  </si>
-  <si>
-    <t>fb Thuyên Quyên</t>
-  </si>
-  <si>
-    <t>HD018007</t>
-  </si>
-  <si>
-    <t>68B/23/1C hương lộ 2, phường bình trị đông A</t>
-  </si>
-  <si>
-    <t>An An</t>
-  </si>
-  <si>
-    <t>HD017441</t>
-  </si>
-  <si>
-    <t>374 Xô viết nghệ tĩnh, P25</t>
-  </si>
-  <si>
-    <t>Mone Ng</t>
-  </si>
-  <si>
-    <t>HD017667</t>
-  </si>
-  <si>
-    <t>Sky Garden 2 p tân phong PMH</t>
-  </si>
-  <si>
-    <t>Ngân Phan</t>
-  </si>
-  <si>
-    <t>HD017688</t>
-  </si>
-  <si>
-    <t>Chung cư Sarina tháp B (Sarina 1B), đường B2, mặt sau đường Hoàng Thế Thiện, Phường An Khánh</t>
-  </si>
-  <si>
-    <t>Kimmie Van</t>
-  </si>
-  <si>
-    <t>HD017625</t>
-  </si>
-  <si>
-    <t>645/48 đường Trần Xuân Soạn p. Tân Hưng</t>
-  </si>
-  <si>
-    <t>Mai Anh</t>
-  </si>
-  <si>
-    <t>HD017687</t>
-  </si>
-  <si>
-    <t>109/22/14 Dương Bá Trạc p1</t>
-  </si>
-  <si>
-    <t>Hoa Tuyết</t>
-  </si>
-  <si>
-    <t>HD017605</t>
-  </si>
-  <si>
-    <t>126A/4 tổ 17 trung mỹ tây</t>
-  </si>
-  <si>
-    <t>Mén HM</t>
-  </si>
-  <si>
-    <t>HD017895</t>
-  </si>
-  <si>
-    <t>Toà landmark 2</t>
-  </si>
-  <si>
-    <t>Ngọc Phạm</t>
-  </si>
-  <si>
-    <t>HD017869</t>
-  </si>
-  <si>
-    <t>80 BÀ HUYỆN THANH QUAN, P.9</t>
-  </si>
-  <si>
-    <t>bảo bảo fb Phương Phương</t>
-  </si>
-  <si>
-    <t>HD017593</t>
-  </si>
-  <si>
-    <t>132 bến vân đồn p5</t>
-  </si>
-  <si>
-    <t>Trúc Phương</t>
-  </si>
-  <si>
-    <t>HD017982</t>
-  </si>
-  <si>
-    <t>Chung cư citiesto, cát lái</t>
-  </si>
-  <si>
-    <t>đổi hàng</t>
-  </si>
-  <si>
-    <t>Thao My</t>
-  </si>
-  <si>
-    <t>HD017676</t>
-  </si>
-  <si>
-    <t>346 Bên Vân đồn f1 Chung cư Gold View</t>
-  </si>
-  <si>
-    <t>hàng sỉ</t>
-  </si>
-  <si>
-    <t>MAI CHI</t>
-  </si>
-  <si>
-    <t>toa BS16 - The oasis - vinhome grand park</t>
-  </si>
-  <si>
-    <t>a.quyen</t>
-  </si>
-  <si>
-    <t>MAI TRẦN</t>
-  </si>
-  <si>
-    <t>135 hải thượng lãn ông P10</t>
-  </si>
-  <si>
-    <t>BOS BMB</t>
-  </si>
-  <si>
-    <t>119 hoàng diệu 2 linh trung</t>
-  </si>
-  <si>
-    <t>jenny bouti</t>
-  </si>
-  <si>
-    <t>401 Quang trung f10</t>
-  </si>
-  <si>
-    <t>Tiền</t>
-  </si>
-  <si>
-    <t>Số đơn</t>
-  </si>
-  <si>
-    <t>Tiền Thu</t>
-  </si>
-  <si>
-    <t>lợi nhuận</t>
-  </si>
-  <si>
-    <t>cod</t>
-  </si>
-  <si>
-    <t>Sài Gòn</t>
-  </si>
-  <si>
-    <t>TỔNG ĐƠN NHẬN</t>
-  </si>
-  <si>
-    <t>at 01-05</t>
-  </si>
-  <si>
-    <t>Trừ Ship</t>
-  </si>
-  <si>
-    <t>tiền ship</t>
-  </si>
-  <si>
-    <t>Đơn trả &amp; c.khoản</t>
-  </si>
-  <si>
-    <t>tiền lấy</t>
-  </si>
-  <si>
-    <t>Tiền Hàng Hcm</t>
-  </si>
-  <si>
-    <t>đơn trả</t>
-  </si>
-  <si>
-    <t>đền đơn</t>
-  </si>
-  <si>
-    <t>đơn cũ ck</t>
-  </si>
-  <si>
-    <t>shop</t>
-  </si>
-  <si>
-    <t>nợ cũ</t>
-  </si>
-  <si>
-    <t>tổng</t>
-  </si>
-  <si>
-    <t>THANH TOÁN</t>
-  </si>
-  <si>
-    <t>CK Đủ 100%</t>
+    <t>_col17</t>
+  </si>
+  <si>
+    <t>Dạ Thảo (Hàng của Thanh đi Malaysia)</t>
+  </si>
+  <si>
+    <t>HD018104</t>
+  </si>
+  <si>
+    <t>66 đường số 17 phường 10</t>
+  </si>
+  <si>
+    <t>AT 04-05</t>
+  </si>
+  <si>
+    <t>04-05-2026</t>
+  </si>
+  <si>
+    <t>hương</t>
+  </si>
+  <si>
+    <t>HD018201</t>
+  </si>
+  <si>
+    <t>97 đường 24A -bình trị đông b</t>
+  </si>
+  <si>
+    <t>Ngọc - fb Nguyễn Mười Ut</t>
+  </si>
+  <si>
+    <t>HD018123</t>
+  </si>
+  <si>
+    <t>45/8 đường số 8 phường bình hưng hòa A</t>
+  </si>
+  <si>
+    <t>Hạnh Huỳnh</t>
+  </si>
+  <si>
+    <t>HD018243</t>
+  </si>
+  <si>
+    <t>42A, đường Mã Lò, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mỹ Hạnh</t>
+  </si>
+  <si>
+    <t>HD018199</t>
+  </si>
+  <si>
+    <t>S3.02 vinhomes garden park long bình</t>
+  </si>
+  <si>
+    <t>Ngọc Thủy</t>
+  </si>
+  <si>
+    <t>41 Mạc Đĩnh Chi, đakao, P1</t>
+  </si>
+  <si>
+    <t>Bé Bờm</t>
+  </si>
+  <si>
+    <t>HD018225</t>
+  </si>
+  <si>
+    <t>167/10 Đào Sư Tích, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Quế Trân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018214</t>
+  </si>
+  <si>
+    <t>145 Nguyễn Cửu Đàm - Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>Hoàng Trinh</t>
+  </si>
+  <si>
+    <t>HD018238</t>
+  </si>
+  <si>
+    <t>71/1/33.Nguyễn van Thuong p Thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Bé My</t>
+  </si>
+  <si>
+    <t>HD017792</t>
+  </si>
+  <si>
+    <t>304/45 đường số 8 bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Mã Thục Phối</t>
+  </si>
+  <si>
+    <t>HD016561</t>
+  </si>
+  <si>
+    <t>156 hàn hải nguyên f8</t>
+  </si>
+  <si>
+    <t>chi hương fb Kim Tien Phan</t>
+  </si>
+  <si>
+    <t>HD018239</t>
+  </si>
+  <si>
+    <t>328 đường số 8 thông tây hội</t>
+  </si>
+  <si>
+    <t>chip chip</t>
+  </si>
+  <si>
+    <t>HD018274</t>
+  </si>
+  <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
+    <t>Ngọc Tuyền</t>
+  </si>
+  <si>
+    <t>HD018193</t>
+  </si>
+  <si>
+    <t>Saigon Royal OT2</t>
+  </si>
+  <si>
+    <t>My Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018234</t>
+  </si>
+  <si>
+    <t>256/33 liên khu 4 - 5 - Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Kim Anh</t>
+  </si>
+  <si>
+    <t>HD018216</t>
+  </si>
+  <si>
+    <t>124/83/1 xô viết nghệ tĩnh p21</t>
+  </si>
+  <si>
+    <t>Người nhận chuột</t>
+  </si>
+  <si>
+    <t>HD018256</t>
+  </si>
+  <si>
+    <t>số 229A Đường bùi thị xuân phường 1</t>
+  </si>
+  <si>
+    <t>TRANG TRẦN 2</t>
+  </si>
+  <si>
+    <t>1122/23/7 quang trung phường 8</t>
+  </si>
+  <si>
+    <t>Qn Nguyễn</t>
+  </si>
+  <si>
+    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
+  </si>
+  <si>
+    <t>NIKI VIJANDRE + Air Shipment + Mien Tran</t>
+  </si>
+  <si>
+    <t>14 Lam Thi Ho, Tan Chanh Hiep Ward</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm Nguyễn</t>
+  </si>
+  <si>
+    <t>HD016319</t>
+  </si>
+  <si>
+    <t>240/38/4 Tô ngọc vân, phường Thanh Xuân</t>
+  </si>
+  <si>
+    <t>luu tra</t>
+  </si>
+  <si>
+    <t>27-04-2026</t>
+  </si>
+  <si>
+    <t>Nguyễn Hải Phụng</t>
+  </si>
+  <si>
+    <t>HD015693</t>
+  </si>
+  <si>
+    <t>36 bờ bao tận trắng P. Sơn Kỳ (chung cư celedon cổng diamond brilliant block B2)</t>
+  </si>
+  <si>
+    <t>25-04-2026</t>
+  </si>
+  <si>
+    <t>Huong, A20.08</t>
+  </si>
+  <si>
+    <t>HD014420</t>
+  </si>
+  <si>
+    <t>CC Tân Phước lỗ a 153 Lý Thường Kiệt, Phường 7</t>
+  </si>
+  <si>
+    <t>23-04-2026</t>
+  </si>
+  <si>
+    <t>at 04-05</t>
+  </si>
+  <si>
+    <t>1 đơn</t>
+  </si>
+  <si>
+    <t>3 đơn</t>
   </si>
 </sst>
 </file>
@@ -854,7 +1087,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -876,6 +1109,11 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1216,68 +1454,68 @@
   <sheetData>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="F3" s="16">
         <v>9</v>
@@ -1293,13 +1531,13 @@
         <v>860</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
@@ -1312,19 +1550,19 @@
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="15" t="s">
         <v>26</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>30</v>
       </c>
       <c r="G4" s="16">
         <v>920</v>
@@ -1337,13 +1575,13 @@
         <v>890</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
@@ -1356,16 +1594,16 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
       <c r="B5" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F5" s="16">
         <v>12</v>
@@ -1381,13 +1619,13 @@
         <v>860</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
@@ -1400,16 +1638,16 @@
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
       <c r="B6" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F6" s="16">
         <v>12</v>
@@ -1425,13 +1663,13 @@
         <v>350</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -1444,16 +1682,16 @@
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F7" s="16">
         <v>8</v>
@@ -1469,13 +1707,13 @@
         <v>470</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -1488,16 +1726,16 @@
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F8" s="16">
         <v>8</v>
@@ -1513,13 +1751,13 @@
         <v>860</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -1532,16 +1770,16 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="15"/>
       <c r="B9" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F9" s="16">
         <v>12</v>
@@ -1557,13 +1795,13 @@
         <v>-30</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -1580,19 +1818,19 @@
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="G10" s="16">
         <v>785</v>
@@ -1605,13 +1843,13 @@
         <v>760</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
@@ -1624,19 +1862,19 @@
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>30</v>
       </c>
       <c r="G11" s="16">
         <v>720</v>
@@ -1649,13 +1887,13 @@
         <v>690</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
@@ -1668,16 +1906,16 @@
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="F12" s="16">
         <v>8</v>
@@ -1693,13 +1931,13 @@
         <v>750</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -1712,19 +1950,19 @@
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>30</v>
       </c>
       <c r="G13" s="16">
         <v>670</v>
@@ -1737,13 +1975,13 @@
         <v>640</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
@@ -1756,16 +1994,16 @@
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="F14" s="16">
         <v>6</v>
@@ -1781,13 +2019,13 @@
         <v>1420</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
@@ -1800,16 +2038,16 @@
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>145</v>
+        <v>59</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="F15" s="16">
         <v>9</v>
@@ -1825,13 +2063,13 @@
         <v>750</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
@@ -1844,19 +2082,19 @@
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>26</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
       </c>
       <c r="G16" s="16">
         <v>0</v>
@@ -1869,13 +2107,13 @@
         <v>-30</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
@@ -1892,16 +2130,16 @@
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>172</v>
+        <v>65</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="F17" s="16">
         <v>12</v>
@@ -1917,13 +2155,13 @@
         <v>660</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
@@ -1936,16 +2174,16 @@
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="15"/>
       <c r="B18" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F18" s="16">
         <v>2</v>
@@ -1961,13 +2199,13 @@
         <v>790</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
@@ -1980,16 +2218,16 @@
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F19" s="16">
         <v>12</v>
@@ -2005,13 +2243,13 @@
         <v>-30</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
@@ -2021,26 +2259,26 @@
         <v>1</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" ref="R19:R20" si="2">H19</f>
+        <f>H19</f>
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
       <c r="B20" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G20" s="16">
         <v>0</v>
@@ -2053,13 +2291,13 @@
         <v>-40</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -2069,26 +2307,26 @@
         <v>1</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="2"/>
+        <f>H20</f>
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" s="16">
         <v>690</v>
@@ -2101,13 +2339,13 @@
         <v>660</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
@@ -2120,19 +2358,19 @@
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
       <c r="B22" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="16">
         <v>660</v>
@@ -2145,13 +2383,13 @@
         <v>640</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
@@ -2164,19 +2402,19 @@
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G23" s="16">
         <v>375</v>
@@ -2189,13 +2427,13 @@
         <v>350</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -2208,19 +2446,19 @@
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G24" s="16">
         <v>0</v>
@@ -2233,13 +2471,13 @@
         <v>-25</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
@@ -2256,19 +2494,19 @@
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G25" s="16">
         <v>725</v>
@@ -2281,13 +2519,13 @@
         <v>700</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -2300,19 +2538,19 @@
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G26" s="16">
         <v>0</v>
@@ -2325,13 +2563,13 @@
         <v>-25</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
@@ -2348,19 +2586,19 @@
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
       <c r="B27" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G27" s="16">
         <v>1765</v>
@@ -2373,13 +2611,13 @@
         <v>1740</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
@@ -2392,19 +2630,19 @@
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G28" s="16">
         <v>0</v>
@@ -2417,13 +2655,13 @@
         <v>-25</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
@@ -2440,19 +2678,19 @@
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
       <c r="B29" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G29" s="16">
         <v>765</v>
@@ -2465,13 +2703,13 @@
         <v>740</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
@@ -2484,19 +2722,19 @@
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
       <c r="B30" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" s="16">
         <v>820</v>
@@ -2509,13 +2747,13 @@
         <v>790</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -2528,19 +2766,19 @@
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G31" s="16">
         <v>740</v>
@@ -2553,13 +2791,13 @@
         <v>720</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
@@ -2572,19 +2810,19 @@
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
       <c r="B32" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G32" s="16">
         <v>770</v>
@@ -2597,13 +2835,13 @@
         <v>750</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
@@ -2616,16 +2854,16 @@
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
       <c r="B33" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F33" s="16">
         <v>2</v>
@@ -2641,13 +2879,13 @@
         <v>-30</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
@@ -2664,19 +2902,19 @@
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G34" s="16">
         <v>590</v>
@@ -2685,17 +2923,17 @@
         <v>20</v>
       </c>
       <c r="I34" s="16">
-        <f t="shared" ref="I34:I41" si="3">G34-H34</f>
+        <f t="shared" ref="I34:I41" si="2">G34-H34</f>
         <v>570</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
@@ -2708,16 +2946,16 @@
     <row r="35" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>186</v>
+        <v>125</v>
       </c>
       <c r="F35" s="18">
         <v>2</v>
@@ -2729,20 +2967,20 @@
         <v>30</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="N35" s="17"/>
       <c r="O35" s="17"/>
@@ -2753,20 +2991,20 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" s="16">
         <v>1165</v>
@@ -2775,17 +3013,17 @@
         <v>35</v>
       </c>
       <c r="I36" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1130</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -2797,20 +3035,20 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="15" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G37" s="16">
         <v>2985</v>
@@ -2819,17 +3057,17 @@
         <v>35</v>
       </c>
       <c r="I37" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2950</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
@@ -2842,19 +3080,19 @@
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="G38" s="16">
         <v>1145</v>
@@ -2863,17 +3101,17 @@
         <v>35</v>
       </c>
       <c r="I38" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1110</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
@@ -2886,19 +3124,19 @@
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="15"/>
       <c r="B39" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="G39" s="16">
         <v>675</v>
@@ -2907,17 +3145,17 @@
         <v>35</v>
       </c>
       <c r="I39" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>640</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
@@ -2930,16 +3168,16 @@
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="15"/>
       <c r="B40" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="F40" s="16">
         <v>5</v>
@@ -2951,17 +3189,17 @@
         <v>25</v>
       </c>
       <c r="I40" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>760</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
@@ -2974,16 +3212,16 @@
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="F41" s="16">
         <v>1</v>
@@ -2995,17 +3233,17 @@
         <v>25</v>
       </c>
       <c r="I41" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>700</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
@@ -3018,16 +3256,16 @@
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="F42" s="16">
         <v>5</v>
@@ -3043,13 +3281,13 @@
         <v>-25</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
@@ -3066,16 +3304,16 @@
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="F43" s="16">
         <v>3</v>
@@ -3091,13 +3329,13 @@
         <v>1560</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
@@ -3110,16 +3348,16 @@
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="15"/>
       <c r="B44" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="F44" s="16">
         <v>3</v>
@@ -3135,13 +3373,13 @@
         <v>790</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
@@ -3154,16 +3392,16 @@
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="15"/>
       <c r="B45" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="F45" s="16">
         <v>7</v>
@@ -3179,13 +3417,13 @@
         <v>660</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M45" s="15"/>
       <c r="N45" s="15"/>
@@ -3198,19 +3436,19 @@
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="15"/>
       <c r="B46" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G46" s="16">
         <v>0</v>
@@ -3223,13 +3461,13 @@
         <v>-25</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
@@ -3243,63 +3481,65 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C47" s="15" t="s">
+    <row r="47" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="18">
+        <v>7</v>
+      </c>
+      <c r="G47" s="18">
+        <v>60</v>
+      </c>
+      <c r="H47" s="18">
+        <v>30</v>
+      </c>
+      <c r="I47" s="18">
+        <f>G47-H47</f>
+        <v>30</v>
+      </c>
+      <c r="J47" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="F47" s="16">
-        <v>7</v>
-      </c>
-      <c r="G47" s="16">
-        <v>720</v>
-      </c>
-      <c r="H47" s="16">
-        <v>30</v>
-      </c>
-      <c r="I47" s="16">
-        <f>G47-H47</f>
-        <v>690</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L47" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15">
+      <c r="K47" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="F48" s="16">
         <v>1</v>
@@ -3315,16 +3555,16 @@
         <v>2010</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M48" s="20" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="N48" s="15"/>
       <c r="O48" s="15"/>
@@ -3340,16 +3580,16 @@
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F49" s="16">
         <v>7</v>
@@ -3365,13 +3605,13 @@
         <v>1770</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
@@ -3384,16 +3624,16 @@
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
       <c r="B50" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F50" s="16">
         <v>7</v>
@@ -3409,13 +3649,13 @@
         <v>740</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
@@ -3428,16 +3668,16 @@
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
       <c r="B51" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F51" s="16">
         <v>7</v>
@@ -3453,13 +3693,13 @@
         <v>740</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
@@ -3472,16 +3712,16 @@
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="15"/>
       <c r="B52" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F52" s="16">
         <v>8</v>
@@ -3497,13 +3737,13 @@
         <v>-25</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L52" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
@@ -3513,23 +3753,23 @@
         <v>1</v>
       </c>
       <c r="R52" s="10">
-        <f t="shared" ref="R52:R53" si="4">H52</f>
+        <f>H52</f>
         <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="15"/>
       <c r="B53" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F53" s="16">
         <v>3</v>
@@ -3545,13 +3785,13 @@
         <v>-25</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
@@ -3561,23 +3801,23 @@
         <v>1</v>
       </c>
       <c r="R53" s="10">
-        <f t="shared" si="4"/>
+        <f>H53</f>
         <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
       <c r="B54" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F54" s="16">
         <v>4</v>
@@ -3593,13 +3833,13 @@
         <v>790</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
@@ -3612,16 +3852,16 @@
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="15"/>
       <c r="B55" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C55" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>188</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>190</v>
       </c>
       <c r="F55" s="16">
         <v>4</v>
@@ -3637,13 +3877,13 @@
         <v>790</v>
       </c>
       <c r="J55" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
@@ -3655,17 +3895,17 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D56" s="15"/>
       <c r="E56" s="15" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F56" s="16">
         <v>5</v>
@@ -3681,13 +3921,13 @@
         <v>-30</v>
       </c>
       <c r="J56" s="15" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L56" s="15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
@@ -3707,47 +3947,47 @@
         <v>50</v>
       </c>
       <c r="G58" s="1">
-        <f t="shared" ref="G58:Q58" si="5">SUBTOTAL(9,G3:G56)</f>
-        <v>37475</v>
+        <f t="shared" ref="G58:Q58" si="3">SUBTOTAL(9,G3:G56)</f>
+        <v>36815</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1520</v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="5"/>
-        <v>35955</v>
+        <f t="shared" si="3"/>
+        <v>35295</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
     </row>
@@ -3759,53 +3999,53 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D60" s="23"/>
+        <v>17</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" s="26"/>
       <c r="E60" s="4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="H60">
         <f>-9*25</f>
         <v>-225</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C61" s="24">
+        <v>195</v>
+      </c>
+      <c r="C61" s="27">
         <f>SUMIFS(I$3:I$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
-        <v>35955</v>
-      </c>
-      <c r="D61" s="24"/>
+        <v>35295</v>
+      </c>
+      <c r="D61" s="27"/>
       <c r="E61" s="3">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>54</v>
       </c>
       <c r="F61" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K61" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L61">
         <f>SUMIFS(G$3:G$56,J$3:J$56,K$60)</f>
@@ -3816,7 +4056,7 @@
         <v>14</v>
       </c>
       <c r="O61" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="P61">
         <f>L66</f>
@@ -3825,14 +4065,14 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C62" s="25">
-        <v>0</v>
-      </c>
-      <c r="D62" s="25"/>
+        <v>199</v>
+      </c>
+      <c r="C62" s="28">
+        <v>0</v>
+      </c>
+      <c r="D62" s="28"/>
       <c r="K62" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L62">
         <f>SUM(H59:H60)</f>
@@ -3843,31 +4083,31 @@
         <v>14</v>
       </c>
       <c r="O62" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="P62">
         <f>L74</f>
-        <v>13715</v>
+        <v>13055</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C63" s="25">
+        <v>201</v>
+      </c>
+      <c r="C63" s="28">
         <f>-SUMIFS(I$3:I$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
       </c>
-      <c r="D63" s="25"/>
+      <c r="D63" s="28"/>
       <c r="E63" s="2">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="O63" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="P63">
         <f>L82</f>
@@ -3876,22 +4116,22 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C64" s="23">
+        <v>203</v>
+      </c>
+      <c r="C64" s="26">
         <f>SUBTOTAL(9,C61:C63)</f>
-        <v>35955</v>
-      </c>
-      <c r="D64" s="23"/>
+        <v>35295</v>
+      </c>
+      <c r="D64" s="26"/>
       <c r="E64">
         <f>E61</f>
         <v>54</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="O64" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="P64">
         <f>L90</f>
@@ -3900,27 +4140,27 @@
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
+        <v>205</v>
+      </c>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
       <c r="K65" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="O65" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="P65">
         <f>-C68</f>
-        <v>-35955</v>
+        <v>-35295</v>
       </c>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B66" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
+        <v>208</v>
+      </c>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
       <c r="L66" s="13">
         <f>SUBTOTAL(9,L61:L65)</f>
         <v>9140</v>
@@ -3930,7 +4170,7 @@
         <v>14</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="P66" s="4">
         <f>SUBTOTAL(9,P61:P65)</f>
@@ -3939,33 +4179,33 @@
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C68" s="22">
+        <v>210</v>
+      </c>
+      <c r="C68" s="25">
         <f>C64+C65+C66</f>
-        <v>35955</v>
-      </c>
-      <c r="D68" s="22"/>
+        <v>35295</v>
+      </c>
+      <c r="D68" s="25"/>
       <c r="E68" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="K68" s="11" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K69" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L69">
         <f>SUMIFS(G$3:G$56,J$3:J$56,K$68)</f>
-        <v>14150</v>
+        <v>13490</v>
       </c>
       <c r="M69">
         <f>SUMIFS(Q$3:Q$56,J$3:J$56,K$68)-INT(COUNTIFS(J$3:J$56,K$68,M$3:M$56,"*gộp*")/2)</f>
@@ -3974,7 +4214,7 @@
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K70" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L70">
         <f>-SUMIFS(H$3:H$56,J$3:J$56,K$68)+M70*5</f>
@@ -3987,23 +4227,23 @@
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K71" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K72" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K73" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L74" s="13">
         <f>SUBTOTAL(9,L69:L73)</f>
-        <v>13715</v>
+        <v>13055</v>
       </c>
       <c r="M74" s="13">
         <f>M69</f>
@@ -4012,18 +4252,18 @@
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K76" s="11" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="M76" s="11" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K77" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L77">
         <f>SUMIFS(G$3:G$56,J$3:J$56,K$76)</f>
@@ -4036,7 +4276,7 @@
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K78" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L78">
         <f>-SUMIFS(H$3:H$56,J$3:J$56,K$76)+M78*5</f>
@@ -4049,7 +4289,7 @@
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K79" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="L79">
         <f>-M79*2</f>
@@ -4062,12 +4302,12 @@
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.25">
       <c r="K80" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K81" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="11:13" x14ac:dyDescent="0.25">
@@ -4082,18 +4322,18 @@
     </row>
     <row r="84" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K84" s="11" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K85" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L85">
         <f>SUMIFS(G$3:G$56,J$3:J$56,K$84)</f>
@@ -4106,7 +4346,7 @@
     </row>
     <row r="86" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K86" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L86">
         <f>-SUMIFS(H$3:H$56,J$3:J$56,K$84)+M86*5</f>
@@ -4119,17 +4359,17 @@
     </row>
     <row r="87" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K87" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K88" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K89" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="11:13" x14ac:dyDescent="0.25">
@@ -4143,7 +4383,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000001000000}">
+  <autoFilter ref="A2:P56" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P56">
       <sortCondition ref="J2:J56"/>
     </sortState>
@@ -4163,6 +4403,1665 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A2:Q60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="73.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="F3" s="16">
+        <v>9</v>
+      </c>
+      <c r="G3" s="16">
+        <v>60</v>
+      </c>
+      <c r="H3" s="16">
+        <v>30</v>
+      </c>
+      <c r="I3" s="16">
+        <f>G3-H3</f>
+        <v>30</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F4" s="16">
+        <v>6</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16">
+        <v>25</v>
+      </c>
+      <c r="I4" s="16">
+        <f>-H4</f>
+        <v>-25</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <v>30</v>
+      </c>
+      <c r="I5" s="16">
+        <f>-H5</f>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <v>30</v>
+      </c>
+      <c r="I6" s="16">
+        <f>-H6</f>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="16">
+        <v>820</v>
+      </c>
+      <c r="H7" s="16">
+        <v>30</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" ref="I7:I12" si="0">G7-H7</f>
+        <v>790</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="16">
+        <v>35</v>
+      </c>
+      <c r="H8" s="16">
+        <v>35</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="16">
+        <v>985</v>
+      </c>
+      <c r="H9" s="16">
+        <v>25</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1430</v>
+      </c>
+      <c r="H10" s="16">
+        <v>30</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F11" s="16">
+        <v>12</v>
+      </c>
+      <c r="G11" s="16">
+        <v>890</v>
+      </c>
+      <c r="H11" s="16">
+        <v>30</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="16">
+        <v>770</v>
+      </c>
+      <c r="H12" s="16">
+        <v>30</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <v>20</v>
+      </c>
+      <c r="I13" s="16">
+        <f>-H13</f>
+        <v>-20</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="16">
+        <v>905</v>
+      </c>
+      <c r="H14" s="16">
+        <v>25</v>
+      </c>
+      <c r="I14" s="16">
+        <f>G14-H14</f>
+        <v>880</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <v>20</v>
+      </c>
+      <c r="I15" s="16">
+        <f>-H15</f>
+        <v>-20</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
+        <v>40</v>
+      </c>
+      <c r="I16" s="16">
+        <f>-H16</f>
+        <v>-40</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1720</v>
+      </c>
+      <c r="H17" s="16">
+        <v>30</v>
+      </c>
+      <c r="I17" s="16">
+        <f>G17-H17</f>
+        <v>1690</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" s="16">
+        <v>12</v>
+      </c>
+      <c r="G18" s="16">
+        <v>50</v>
+      </c>
+      <c r="H18" s="16">
+        <v>50</v>
+      </c>
+      <c r="I18" s="16">
+        <f>G18-H18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <v>25</v>
+      </c>
+      <c r="I19" s="16">
+        <f>-H19</f>
+        <v>-25</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F20" s="16">
+        <v>11</v>
+      </c>
+      <c r="G20" s="16">
+        <v>615</v>
+      </c>
+      <c r="H20" s="16">
+        <v>25</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" ref="I20:I25" si="1">G20-H20</f>
+        <v>590</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="F21" s="16">
+        <v>4</v>
+      </c>
+      <c r="G21" s="16">
+        <v>815</v>
+      </c>
+      <c r="H21" s="16">
+        <v>25</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="16">
+        <v>765</v>
+      </c>
+      <c r="H22" s="16">
+        <v>25</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F23" s="22">
+        <v>4</v>
+      </c>
+      <c r="G23" s="22">
+        <v>815</v>
+      </c>
+      <c r="H23" s="22">
+        <v>25</v>
+      </c>
+      <c r="I23" s="22">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="O23" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="P23" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q23" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="F24" s="22">
+        <v>12</v>
+      </c>
+      <c r="G24" s="22">
+        <v>860</v>
+      </c>
+      <c r="H24" s="22">
+        <v>0</v>
+      </c>
+      <c r="I24" s="22">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="O24" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="P24" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q24" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="22">
+        <v>1455</v>
+      </c>
+      <c r="H25" s="22">
+        <v>25</v>
+      </c>
+      <c r="I25" s="22">
+        <f t="shared" si="1"/>
+        <v>1430</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="N25" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="O25" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="P25" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q25" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="F26" s="22">
+        <v>11</v>
+      </c>
+      <c r="G26" s="22">
+        <v>0</v>
+      </c>
+      <c r="H26" s="22">
+        <v>25</v>
+      </c>
+      <c r="I26" s="22">
+        <f>-H26</f>
+        <v>-25</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="O26" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="P26" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D28" s="1">
+        <f>COUNTA(D3:D26)</f>
+        <v>20</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" ref="G28:Q28" si="2">SUBTOTAL(9,G3:G26)</f>
+        <v>12990</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="2"/>
+        <v>655</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="2"/>
+        <v>12335</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <f>-2*17</f>
+        <v>-34</v>
+      </c>
+      <c r="I29">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="26"/>
+      <c r="E30" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H30">
+        <f>-6*25</f>
+        <v>-150</v>
+      </c>
+      <c r="I30">
+        <v>17</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="27">
+        <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
+        <v>9280</v>
+      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="3">
+        <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
+        <v>20</v>
+      </c>
+      <c r="F31" t="s">
+        <v>196</v>
+      </c>
+      <c r="H31">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="I31">
+        <v>-17</v>
+      </c>
+      <c r="K31" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$30)</f>
+        <v>4930</v>
+      </c>
+      <c r="M31">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+      <c r="O31" t="s">
+        <v>296</v>
+      </c>
+      <c r="P31">
+        <f>L36</f>
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="28">
+        <v>0</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="K32" t="s">
+        <v>200</v>
+      </c>
+      <c r="L32">
+        <f>SUM(H29:H31)</f>
+        <v>-214</v>
+      </c>
+      <c r="M32">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)</f>
+        <v>9</v>
+      </c>
+      <c r="O32" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32">
+        <f>L44</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="28">
+        <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
+        <v>-3055</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="2">
+        <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
+        <v>4</v>
+      </c>
+      <c r="K33" t="s">
+        <v>202</v>
+      </c>
+      <c r="O33" t="s">
+        <v>135</v>
+      </c>
+      <c r="P33">
+        <f>L52</f>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="26">
+        <f>SUBTOTAL(9,C31:C33)</f>
+        <v>6225</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34">
+        <f>E31</f>
+        <v>20</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L34" s="23">
+        <v>-2315</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34">
+        <f>L60</f>
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="K35" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O35" t="s">
+        <v>207</v>
+      </c>
+      <c r="P35">
+        <f>-C38</f>
+        <v>-6225</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="L36" s="13">
+        <f>SUBTOTAL(9,L31:L35)</f>
+        <v>2401</v>
+      </c>
+      <c r="M36" s="13">
+        <f>M31</f>
+        <v>9</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P36" s="4">
+        <f>SUBTOTAL(9,P31:P35)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" s="25">
+        <f>C34+C35+C36</f>
+        <v>6225</v>
+      </c>
+      <c r="D38" s="25"/>
+      <c r="E38" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>197</v>
+      </c>
+      <c r="L39">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$38)</f>
+        <v>60</v>
+      </c>
+      <c r="M39">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>200</v>
+      </c>
+      <c r="L40">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$38)+M40*5</f>
+        <v>-25</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K42" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K43" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L44" s="13">
+        <f>SUBTOTAL(9,L39:L43)</f>
+        <v>35</v>
+      </c>
+      <c r="M44" s="13">
+        <f>M39</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K46" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>197</v>
+      </c>
+      <c r="L47">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$46)</f>
+        <v>2195</v>
+      </c>
+      <c r="M47">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$46)-INT(COUNTIFS(J$3:J$26,K$46,M$3:M$26,"*gộp*")/2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>200</v>
+      </c>
+      <c r="L48">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$46)+M48*5</f>
+        <v>-80</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$46)-INT(COUNTIFS(J$3:J$26,K$46,M$3:M$26,"*gộp*")/2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L50" s="23">
+        <v>-795</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L52" s="13">
+        <f>SUBTOTAL(9,L47:L51)</f>
+        <v>1320</v>
+      </c>
+      <c r="M52" s="13">
+        <f>M47</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" t="s">
+        <v>197</v>
+      </c>
+      <c r="L55">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$54)</f>
+        <v>2675</v>
+      </c>
+      <c r="M55">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$54)-INT(COUNTIFS(J$3:J$26,K$54,M$3:M$26,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>200</v>
+      </c>
+      <c r="L56">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$54)+M56*5</f>
+        <v>-155</v>
+      </c>
+      <c r="M56">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$54)-INT(COUNTIFS(J$3:J$26,K$54,M$3:M$26,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>202</v>
+      </c>
+      <c r="L57">
+        <f>-M57*2</f>
+        <v>-32</v>
+      </c>
+      <c r="M57">
+        <f>E34-(COUNTIFS(M$3:M$26,"*gộp*")/2)-COUNTIFS(M$3:M$26,"*đơn trả*")-COUNTIFS(M$3:M$26,"*hàng tỉnh*")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L60" s="13">
+        <f>SUBTOTAL(9,L55:L59)</f>
+        <v>2488</v>
+      </c>
+      <c r="M60" s="13">
+        <f>M55</f>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P26" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P26">
+      <sortCondition ref="J2:J26"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -4181,7 +6080,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="B1" s="5">
         <v>2026</v>
@@ -4189,19 +6088,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2</v>
+        <v>214</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>3</v>
+        <v>215</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>4</v>
+        <v>216</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>5</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4242,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="8">
-        <f t="shared" ref="E4:E28" ca="1" si="3">B4-C4-D4</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4252,7 +6151,7 @@
       </c>
       <c r="B5" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C5" s="8">
         <f t="shared" ca="1" si="2"/>
@@ -4260,11 +6159,11 @@
       </c>
       <c r="D5" s="8" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A5,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4284,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4305,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4326,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4347,7 +6246,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4368,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4389,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4410,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4431,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4452,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4473,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4494,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4515,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4536,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4557,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4578,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4599,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4620,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4641,7 +6540,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4662,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4683,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4704,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4725,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4746,22 +6645,22 @@
         <v>0</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="9" t="s">
-        <v>6</v>
+        <v>218</v>
       </c>
       <c r="E29" s="9">
         <f ca="1">SUBTOTAL(9,E4:E28)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="9" t="s">
-        <v>7</v>
+        <v>219</v>
       </c>
       <c r="E30" s="9" cm="1">
         <f t="array" ref="E30" ca="1">SUMPRODUCT(
@@ -4773,29 +6672,29 @@
         ),
     0)
 )</f>
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="9" t="s">
-        <v>8</v>
+        <v>220</v>
       </c>
       <c r="E31" s="9">
         <f ca="1">-E29*2</f>
-        <v>0</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D32" s="9" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="E32" s="9">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>0</v>
+        <v>-13</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D28">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport.xlsx
+++ b/data/May/InternalDailyReport.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571D6E50-D714-411D-8667-43F5EE129573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687AB54C-57BB-48FA-A38C-F8313A603340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
     <sheet name="04-05" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId3"/>
+    <sheet name="05-05" sheetId="9" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'04-05'!$A$2:$P$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$2:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'05-05'!$A$2:$P$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="450">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -700,6 +702,237 @@
     <t>CK Đủ 100%</t>
   </si>
   <si>
+    <t>_col17</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mỹ Hạnh</t>
+  </si>
+  <si>
+    <t>HD018199</t>
+  </si>
+  <si>
+    <t>S3.02 vinhomes garden park long bình</t>
+  </si>
+  <si>
+    <t>04-05-2026</t>
+  </si>
+  <si>
+    <t>Dạ Thảo (Hàng của Thanh đi Malaysia)</t>
+  </si>
+  <si>
+    <t>HD018104</t>
+  </si>
+  <si>
+    <t>66 đường số 17 phường 10</t>
+  </si>
+  <si>
+    <t>AT 04-05</t>
+  </si>
+  <si>
+    <t>hương</t>
+  </si>
+  <si>
+    <t>HD018201</t>
+  </si>
+  <si>
+    <t>97 đường 24A -bình trị đông b</t>
+  </si>
+  <si>
+    <t>Ngọc - fb Nguyễn Mười Ut</t>
+  </si>
+  <si>
+    <t>HD018123</t>
+  </si>
+  <si>
+    <t>45/8 đường số 8 phường bình hưng hòa A</t>
+  </si>
+  <si>
+    <t>Hạnh Huỳnh</t>
+  </si>
+  <si>
+    <t>HD018243</t>
+  </si>
+  <si>
+    <t>42A, đường Mã Lò, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Bé Bờm</t>
+  </si>
+  <si>
+    <t>HD018225</t>
+  </si>
+  <si>
+    <t>167/10 Đào Sư Tích, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Quế Trân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018214</t>
+  </si>
+  <si>
+    <t>145 Nguyễn Cửu Đàm - Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>Bé My</t>
+  </si>
+  <si>
+    <t>HD017792</t>
+  </si>
+  <si>
+    <t>304/45 đường số 8 bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>chip chip</t>
+  </si>
+  <si>
+    <t>HD018274</t>
+  </si>
+  <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
+    <t>My Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018234</t>
+  </si>
+  <si>
+    <t>256/33 liên khu 4 - 5 - Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Hoàng Trinh</t>
+  </si>
+  <si>
+    <t>HD018238</t>
+  </si>
+  <si>
+    <t>71/1/33.Nguyễn van Thuong p Thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>chi hương fb Kim Tien Phan</t>
+  </si>
+  <si>
+    <t>HD018239</t>
+  </si>
+  <si>
+    <t>328 đường số 8 thông tây hội</t>
+  </si>
+  <si>
+    <t>Kim Anh</t>
+  </si>
+  <si>
+    <t>HD018216</t>
+  </si>
+  <si>
+    <t>124/83/1 xô viết nghệ tĩnh p21</t>
+  </si>
+  <si>
+    <t>TRANG TRẦN 2</t>
+  </si>
+  <si>
+    <t>1122/23/7 quang trung phường 8</t>
+  </si>
+  <si>
+    <t>Qn Nguyễn</t>
+  </si>
+  <si>
+    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
+  </si>
+  <si>
+    <t>NIKI VIJANDRE + Air Shipment + Mien Tran</t>
+  </si>
+  <si>
+    <t>14 Lam Thi Ho, Tan Chanh Hiep Ward</t>
+  </si>
+  <si>
+    <t>Ngọc Thủy</t>
+  </si>
+  <si>
+    <t>41 Mạc Đĩnh Chi, đakao, P1</t>
+  </si>
+  <si>
+    <t>Mã Thục Phối</t>
+  </si>
+  <si>
+    <t>HD016561</t>
+  </si>
+  <si>
+    <t>156 hàn hải nguyên f8</t>
+  </si>
+  <si>
+    <t>Ngọc Tuyền</t>
+  </si>
+  <si>
+    <t>HD018193</t>
+  </si>
+  <si>
+    <t>Saigon Royal OT2</t>
+  </si>
+  <si>
+    <t>Người nhận chuột</t>
+  </si>
+  <si>
+    <t>HD018256</t>
+  </si>
+  <si>
+    <t>số 229A Đường bùi thị xuân phường 1</t>
+  </si>
+  <si>
+    <t>luu tra</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm Nguyễn</t>
+  </si>
+  <si>
+    <t>HD016319</t>
+  </si>
+  <si>
+    <t>240/38/4 Tô ngọc vân, phường Thanh Xuân</t>
+  </si>
+  <si>
+    <t>27-04-2026</t>
+  </si>
+  <si>
+    <t>Nguyễn Hải Phụng</t>
+  </si>
+  <si>
+    <t>HD015693</t>
+  </si>
+  <si>
+    <t>36 bờ bao tận trắng P. Sơn Kỳ (chung cư celedon cổng diamond brilliant block B2)</t>
+  </si>
+  <si>
+    <t>25-04-2026</t>
+  </si>
+  <si>
+    <t>Huong, A20.08</t>
+  </si>
+  <si>
+    <t>HD014420</t>
+  </si>
+  <si>
+    <t>CC Tân Phước lỗ a 153 Lý Thường Kiệt, Phường 7</t>
+  </si>
+  <si>
+    <t>23-04-2026</t>
+  </si>
+  <si>
+    <t>at 04-05</t>
+  </si>
+  <si>
+    <t>3 đơn</t>
+  </si>
+  <si>
+    <t>1 đơn</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -730,235 +963,457 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>_col17</t>
-  </si>
-  <si>
-    <t>Dạ Thảo (Hàng của Thanh đi Malaysia)</t>
-  </si>
-  <si>
-    <t>HD018104</t>
-  </si>
-  <si>
-    <t>66 đường số 17 phường 10</t>
-  </si>
-  <si>
-    <t>AT 04-05</t>
-  </si>
-  <si>
-    <t>04-05-2026</t>
-  </si>
-  <si>
-    <t>hương</t>
-  </si>
-  <si>
-    <t>HD018201</t>
-  </si>
-  <si>
-    <t>97 đường 24A -bình trị đông b</t>
-  </si>
-  <si>
-    <t>Ngọc - fb Nguyễn Mười Ut</t>
-  </si>
-  <si>
-    <t>HD018123</t>
-  </si>
-  <si>
-    <t>45/8 đường số 8 phường bình hưng hòa A</t>
-  </si>
-  <si>
-    <t>Hạnh Huỳnh</t>
-  </si>
-  <si>
-    <t>HD018243</t>
-  </si>
-  <si>
-    <t>42A, đường Mã Lò, phường Bình Trị Đông A</t>
-  </si>
-  <si>
-    <t>Hồ Thị Mỹ Hạnh</t>
-  </si>
-  <si>
-    <t>HD018199</t>
-  </si>
-  <si>
-    <t>S3.02 vinhomes garden park long bình</t>
-  </si>
-  <si>
-    <t>Ngọc Thủy</t>
-  </si>
-  <si>
-    <t>41 Mạc Đĩnh Chi, đakao, P1</t>
-  </si>
-  <si>
-    <t>Bé Bờm</t>
-  </si>
-  <si>
-    <t>HD018225</t>
-  </si>
-  <si>
-    <t>167/10 Đào Sư Tích, Phước Kiển</t>
-  </si>
-  <si>
-    <t>Quế Trân Nguyễn</t>
-  </si>
-  <si>
-    <t>HD018214</t>
-  </si>
-  <si>
-    <t>145 Nguyễn Cửu Đàm - Tân Sơn Nhì</t>
-  </si>
-  <si>
-    <t>Hoàng Trinh</t>
-  </si>
-  <si>
-    <t>HD018238</t>
-  </si>
-  <si>
-    <t>71/1/33.Nguyễn van Thuong p Thạnh mỹ tây</t>
-  </si>
-  <si>
-    <t>Bé My</t>
-  </si>
-  <si>
-    <t>HD017792</t>
-  </si>
-  <si>
-    <t>304/45 đường số 8 bình hưng hoà a</t>
-  </si>
-  <si>
-    <t>Mã Thục Phối</t>
-  </si>
-  <si>
-    <t>HD016561</t>
-  </si>
-  <si>
-    <t>156 hàn hải nguyên f8</t>
-  </si>
-  <si>
-    <t>chi hương fb Kim Tien Phan</t>
-  </si>
-  <si>
-    <t>HD018239</t>
-  </si>
-  <si>
-    <t>328 đường số 8 thông tây hội</t>
-  </si>
-  <si>
-    <t>chip chip</t>
-  </si>
-  <si>
-    <t>HD018274</t>
-  </si>
-  <si>
-    <t>71/16 thới an 16</t>
-  </si>
-  <si>
-    <t>Ngọc Tuyền</t>
-  </si>
-  <si>
-    <t>HD018193</t>
-  </si>
-  <si>
-    <t>Saigon Royal OT2</t>
-  </si>
-  <si>
-    <t>My Nguyễn</t>
-  </si>
-  <si>
-    <t>HD018234</t>
-  </si>
-  <si>
-    <t>256/33 liên khu 4 - 5 - Bình Hưng Hòa B</t>
-  </si>
-  <si>
-    <t>Kim Anh</t>
-  </si>
-  <si>
-    <t>HD018216</t>
-  </si>
-  <si>
-    <t>124/83/1 xô viết nghệ tĩnh p21</t>
-  </si>
-  <si>
-    <t>Người nhận chuột</t>
-  </si>
-  <si>
-    <t>HD018256</t>
-  </si>
-  <si>
-    <t>số 229A Đường bùi thị xuân phường 1</t>
-  </si>
-  <si>
-    <t>TRANG TRẦN 2</t>
-  </si>
-  <si>
-    <t>1122/23/7 quang trung phường 8</t>
-  </si>
-  <si>
-    <t>Qn Nguyễn</t>
-  </si>
-  <si>
-    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
-  </si>
-  <si>
-    <t>NIKI VIJANDRE + Air Shipment + Mien Tran</t>
-  </si>
-  <si>
-    <t>14 Lam Thi Ho, Tan Chanh Hiep Ward</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>xx</t>
-  </si>
-  <si>
-    <t>Kim Anh Phạm Nguyễn</t>
-  </si>
-  <si>
-    <t>HD016319</t>
-  </si>
-  <si>
-    <t>240/38/4 Tô ngọc vân, phường Thanh Xuân</t>
-  </si>
-  <si>
-    <t>luu tra</t>
-  </si>
-  <si>
-    <t>27-04-2026</t>
-  </si>
-  <si>
-    <t>Nguyễn Hải Phụng</t>
-  </si>
-  <si>
-    <t>HD015693</t>
-  </si>
-  <si>
-    <t>36 bờ bao tận trắng P. Sơn Kỳ (chung cư celedon cổng diamond brilliant block B2)</t>
-  </si>
-  <si>
-    <t>25-04-2026</t>
-  </si>
-  <si>
-    <t>Huong, A20.08</t>
-  </si>
-  <si>
-    <t>HD014420</t>
-  </si>
-  <si>
-    <t>CC Tân Phước lỗ a 153 Lý Thường Kiệt, Phường 7</t>
-  </si>
-  <si>
-    <t>23-04-2026</t>
-  </si>
-  <si>
-    <t>at 04-05</t>
-  </si>
-  <si>
-    <t>1 đơn</t>
-  </si>
-  <si>
-    <t>3 đơn</t>
+    <t>Nhung SaLin</t>
+  </si>
+  <si>
+    <t>HD018538</t>
+  </si>
+  <si>
+    <t>19a Trần Quang diệu p13</t>
+  </si>
+  <si>
+    <t>05-05-2026</t>
+  </si>
+  <si>
+    <t>gộp</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018539</t>
+  </si>
+  <si>
+    <t>70 đường số 1 KDC nam long</t>
+  </si>
+  <si>
+    <t>AT 05-05</t>
+  </si>
+  <si>
+    <t>Trâm Trang</t>
+  </si>
+  <si>
+    <t>HD018328</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1</t>
+  </si>
+  <si>
+    <t>Giáng Hương</t>
+  </si>
+  <si>
+    <t>HD018400</t>
+  </si>
+  <si>
+    <t>111 đường số 10 phường 13</t>
+  </si>
+  <si>
+    <t>Nhi</t>
+  </si>
+  <si>
+    <t>HD018213</t>
+  </si>
+  <si>
+    <t>Hiểu My</t>
+  </si>
+  <si>
+    <t>HD018563</t>
+  </si>
+  <si>
+    <t>Toà 2, chung cư river panorama, 20 lê thị chợ, phường phú thuận</t>
+  </si>
+  <si>
+    <t>Trần Thục Oanh</t>
+  </si>
+  <si>
+    <t>HD018532</t>
+  </si>
+  <si>
+    <t>118 đường 3/2, p12</t>
+  </si>
+  <si>
+    <t>Nhung Bùi</t>
+  </si>
+  <si>
+    <t>H0018373</t>
+  </si>
+  <si>
+    <t>409/108/32/14c huynh thị hai, tân chánh hiệp</t>
+  </si>
+  <si>
+    <t>Trần Ngọc Thúy</t>
+  </si>
+  <si>
+    <t>HD018516</t>
+  </si>
+  <si>
+    <t>saigon mia block b cổng sau</t>
+  </si>
+  <si>
+    <t>Ngọc Vinh</t>
+  </si>
+  <si>
+    <t>HD018285</t>
+  </si>
+  <si>
+    <t>17-19 Trường Sơn P4</t>
+  </si>
+  <si>
+    <t>C. Phương fb Nuory Le</t>
+  </si>
+  <si>
+    <t>HD018435</t>
+  </si>
+  <si>
+    <t>A28/1Dw3 quốc lộ 50 ấp 1 xã bình hưng</t>
+  </si>
+  <si>
+    <t>ny nhỏ</t>
+  </si>
+  <si>
+    <t>HD018341</t>
+  </si>
+  <si>
+    <t>49 le quang kim p8</t>
+  </si>
+  <si>
+    <t>Miu miu quỳnh</t>
+  </si>
+  <si>
+    <t>HD018466</t>
+  </si>
+  <si>
+    <t>109 Bến Vân Đồn P9</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Bảo Loan</t>
+  </si>
+  <si>
+    <t>HD018401</t>
+  </si>
+  <si>
+    <t>tòa b2 chung cư lavida plus số 1181 nguyễn văn linh tân phong</t>
+  </si>
+  <si>
+    <t>Hoàng Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD018387</t>
+  </si>
+  <si>
+    <t>2/11 đường thiên phước, p9</t>
+  </si>
+  <si>
+    <t>Vy Vy</t>
+  </si>
+  <si>
+    <t>HD018348</t>
+  </si>
+  <si>
+    <t>Block B chung cư Sunrise RiverSide, Nguyễn Hữu Thọ, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng</t>
+  </si>
+  <si>
+    <t>HD018553</t>
+  </si>
+  <si>
+    <t>155/14 đs 11 bình hưng hoà</t>
+  </si>
+  <si>
+    <t>My Luu</t>
+  </si>
+  <si>
+    <t>HD018552</t>
+  </si>
+  <si>
+    <t>Toà T1, chung cư Vista Verde, số 8 Nguyễn Thanh Sơn, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>gộp, đổi hàng</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD018231</t>
+  </si>
+  <si>
+    <t>100/17 liên khu 1-6 bình trị đông</t>
+  </si>
+  <si>
+    <t>Thảo</t>
+  </si>
+  <si>
+    <t>HD018440</t>
+  </si>
+  <si>
+    <t>280a12 Lương Đình Của. An Phú</t>
+  </si>
+  <si>
+    <t>Nguyen Diem My</t>
+  </si>
+  <si>
+    <t>HD018321</t>
+  </si>
+  <si>
+    <t>212 lê quang định phường 14</t>
+  </si>
+  <si>
+    <t>Ngà Ngọc</t>
+  </si>
+  <si>
+    <t>HD018269</t>
+  </si>
+  <si>
+    <t>85 phan xích long p2</t>
+  </si>
+  <si>
+    <t>phu nhuan</t>
+  </si>
+  <si>
+    <t>Elena Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018325</t>
+  </si>
+  <si>
+    <t>56/41 dương ba trạc, Phường 02</t>
+  </si>
+  <si>
+    <t>HD018386</t>
+  </si>
+  <si>
+    <t>hàng của Đào Ngọc Bích</t>
+  </si>
+  <si>
+    <t>HD018540</t>
+  </si>
+  <si>
+    <t>007 Lộ B chung cư Tây Thạnh, phường Tân Thạnh</t>
+  </si>
+  <si>
+    <t>Việt Anh - fb Hồ Thị Uyên</t>
+  </si>
+  <si>
+    <t>HD018388</t>
+  </si>
+  <si>
+    <t>350/27 Lê Văn Quới, Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>HD018494</t>
+  </si>
+  <si>
+    <t>chung cư the park residence, 12 nguyễn hữu thọ phước kien nha be</t>
+  </si>
+  <si>
+    <t>cô dung fb Nini Thach</t>
+  </si>
+  <si>
+    <t>HD018521</t>
+  </si>
+  <si>
+    <t>137/74a âu dương lân - p2</t>
+  </si>
+  <si>
+    <t>Love May</t>
+  </si>
+  <si>
+    <t>HD018311</t>
+  </si>
+  <si>
+    <t>T4 Masteri Đường Số 10, Thảo Điền</t>
+  </si>
+  <si>
+    <t>Mi Ni</t>
+  </si>
+  <si>
+    <t>HD018437</t>
+  </si>
+  <si>
+    <t>536/32/23 âu cơ</t>
+  </si>
+  <si>
+    <t>HD018486</t>
+  </si>
+  <si>
+    <t>HD018546</t>
+  </si>
+  <si>
+    <t>Hoàng Thuý Liên</t>
+  </si>
+  <si>
+    <t>HD017772</t>
+  </si>
+  <si>
+    <t>290 an dương vương phường chợ quán</t>
+  </si>
+  <si>
+    <t>yenchau</t>
+  </si>
+  <si>
+    <t>HD018526</t>
+  </si>
+  <si>
+    <t>Chung cu Horita, lo C, Đường D4, P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Thư Ánh Võ</t>
+  </si>
+  <si>
+    <t>HD018343</t>
+  </si>
+  <si>
+    <t>5 lê thánh tôn bến nghé</t>
+  </si>
+  <si>
+    <t>Châu Châu</t>
+  </si>
+  <si>
+    <t>HD018490</t>
+  </si>
+  <si>
+    <t>E3/8 ấp 56 xã vĩnh lộc</t>
+  </si>
+  <si>
+    <t>Ly Sokny- 012776599</t>
+  </si>
+  <si>
+    <t>HD018248</t>
+  </si>
+  <si>
+    <t>359 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>Tuyết</t>
+  </si>
+  <si>
+    <t>HD018429</t>
+  </si>
+  <si>
+    <t>30/18 đường số 6 KP18 Phường Vĩnh Hội</t>
+  </si>
+  <si>
+    <t>Hồng Miên</t>
+  </si>
+  <si>
+    <t>HD018250</t>
+  </si>
+  <si>
+    <t>123 đường số 11 tân kiểng tân quy</t>
+  </si>
+  <si>
+    <t>Đinh Thị Kim Lan</t>
+  </si>
+  <si>
+    <t>HD018306</t>
+  </si>
+  <si>
+    <t>Ngân hàng Tpbank 303 (39/6) Trường Chinh P Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Thu Ba DS</t>
+  </si>
+  <si>
+    <t>HD018302</t>
+  </si>
+  <si>
+    <t>395 Bùi Đình Tuý, p14</t>
+  </si>
+  <si>
+    <t>Thanh Xuân</t>
+  </si>
+  <si>
+    <t>HD018565</t>
+  </si>
+  <si>
+    <t>17/4B Liên khu 5-6 bình hưng hòa b</t>
+  </si>
+  <si>
+    <t>Ivy Dao</t>
+  </si>
+  <si>
+    <t>HD018318</t>
+  </si>
+  <si>
+    <t>238/3 trường chinh, đông hưng thuận</t>
+  </si>
+  <si>
+    <t>HD018376</t>
+  </si>
+  <si>
+    <t>Loan Thỏ</t>
+  </si>
+  <si>
+    <t>HD018544</t>
+  </si>
+  <si>
+    <t>81/6 Hồ thị kỷ, phường 1</t>
+  </si>
+  <si>
+    <t>Hồng My</t>
+  </si>
+  <si>
+    <t>HD018549</t>
+  </si>
+  <si>
+    <t>192 Phạm Đức Sơn, Phường 16 (Chung Cư Heaven Riverview - Mỹ Phúc) Block B</t>
+  </si>
+  <si>
+    <t>Mỹ Ngọc</t>
+  </si>
+  <si>
+    <t>HD018275</t>
+  </si>
+  <si>
+    <t>242 nguyễn oanh, phường gò vấp</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hoà</t>
+  </si>
+  <si>
+    <t>FANG FANG</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>Ly Clara Selena</t>
+  </si>
+  <si>
+    <t>403 tân sơn p12</t>
+  </si>
+  <si>
+    <t>LISA</t>
+  </si>
+  <si>
+    <t>685 tân sơn phường 12</t>
+  </si>
+  <si>
+    <t>THU TRƯƠNG</t>
+  </si>
+  <si>
+    <t>159/43/5 Đường Bạch Đằng, phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>DARAVIN</t>
+  </si>
+  <si>
+    <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
+  </si>
+  <si>
+    <t>at 05-05</t>
+  </si>
+  <si>
+    <t>shipper ứng tiền cho nhà xe</t>
+  </si>
+  <si>
+    <t>27 nguyễn hữu thọ (sunrise city toà X1) phường Tân Hưng</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1463,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1058,6 +1513,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1087,7 +1548,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1114,6 +1575,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4001,10 +4463,10 @@
       <c r="A60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="26" t="s">
+      <c r="C60" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="D60" s="26"/>
+      <c r="D60" s="27"/>
       <c r="E60" s="4" t="s">
         <v>192</v>
       </c>
@@ -4032,11 +4494,11 @@
       <c r="B61" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="28">
         <f>SUMIFS(I$3:I$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>35295</v>
       </c>
-      <c r="D61" s="27"/>
+      <c r="D61" s="28"/>
       <c r="E61" s="3">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,L$3:L$56,A$61)</f>
         <v>54</v>
@@ -4067,10 +4529,10 @@
       <c r="B62" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C62" s="28">
-        <v>0</v>
-      </c>
-      <c r="D62" s="28"/>
+      <c r="C62" s="29">
+        <v>0</v>
+      </c>
+      <c r="D62" s="29"/>
       <c r="K62" t="s">
         <v>200</v>
       </c>
@@ -4094,11 +4556,11 @@
       <c r="B63" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="29">
         <f>-SUMIFS(I$3:I$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
       </c>
-      <c r="D63" s="28"/>
+      <c r="D63" s="29"/>
       <c r="E63" s="2">
         <f>SUMIFS(Q$3:Q$56,B$3:B$56,A$60,P$3:P$56,"xx",N$3:N$56,"x")</f>
         <v>0</v>
@@ -4118,11 +4580,11 @@
       <c r="B64" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C64" s="26">
+      <c r="C64" s="27">
         <f>SUBTOTAL(9,C61:C63)</f>
         <v>35295</v>
       </c>
-      <c r="D64" s="26"/>
+      <c r="D64" s="27"/>
       <c r="E64">
         <f>E61</f>
         <v>54</v>
@@ -4142,8 +4604,8 @@
       <c r="B65" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
       <c r="K65" s="2" t="s">
         <v>206</v>
       </c>
@@ -4159,8 +4621,8 @@
       <c r="B66" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
       <c r="L66" s="13">
         <f>SUBTOTAL(9,L61:L65)</f>
         <v>9140</v>
@@ -4181,11 +4643,11 @@
       <c r="B68" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="26">
         <f>C64+C65+C66</f>
         <v>35295</v>
       </c>
-      <c r="D68" s="25"/>
+      <c r="D68" s="26"/>
       <c r="E68" s="1" t="s">
         <v>211</v>
       </c>
@@ -4476,7 +4938,7 @@
         <v>15</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -4485,13 +4947,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="F3" s="16">
         <v>9</v>
@@ -4513,7 +4975,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>167</v>
@@ -4531,13 +4993,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F4" s="16">
         <v>6</v>
@@ -4553,13 +5015,13 @@
         <v>-25</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
@@ -4575,13 +5037,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>26</v>
@@ -4597,13 +5059,13 @@
         <v>-30</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M5" s="15" t="s">
         <v>126</v>
@@ -4621,13 +5083,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>26</v>
@@ -4643,13 +5105,13 @@
         <v>-30</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -4665,13 +5127,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>26</v>
@@ -4687,13 +5149,13 @@
         <v>790</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -4709,13 +5171,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>134</v>
@@ -4731,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>126</v>
@@ -4755,13 +5217,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>46</v>
@@ -4777,13 +5239,13 @@
         <v>960</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -4799,13 +5261,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>26</v>
@@ -4821,13 +5283,13 @@
         <v>1400</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
@@ -4843,13 +5305,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="F11" s="16">
         <v>12</v>
@@ -4865,13 +5327,13 @@
         <v>860</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
@@ -4887,13 +5349,13 @@
         <v>17</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>26</v>
@@ -4909,13 +5371,13 @@
         <v>740</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -4931,13 +5393,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>85</v>
@@ -4959,7 +5421,7 @@
         <v>21</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
@@ -4975,13 +5437,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>77</v>
@@ -5003,7 +5465,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
@@ -5019,13 +5481,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>85</v>
@@ -5047,7 +5509,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
@@ -5065,11 +5527,11 @@
         <v>17</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>77</v>
@@ -5091,7 +5553,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
@@ -5109,11 +5571,11 @@
         <v>17</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>77</v>
@@ -5135,7 +5597,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
@@ -5153,11 +5615,11 @@
         <v>17</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="F18" s="16">
         <v>12</v>
@@ -5179,7 +5641,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
@@ -5197,11 +5659,11 @@
         <v>17</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="F19" s="16">
         <v>1</v>
@@ -5223,7 +5685,7 @@
         <v>21</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M19" s="15" t="s">
         <v>126</v>
@@ -5241,13 +5703,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F20" s="16">
         <v>11</v>
@@ -5269,7 +5731,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -5285,13 +5747,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F21" s="16">
         <v>4</v>
@@ -5313,7 +5775,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
@@ -5329,13 +5791,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>95</v>
@@ -5357,7 +5819,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
@@ -5395,7 +5857,7 @@
         <v>790</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="K23" s="21" t="s">
         <v>21</v>
@@ -5407,13 +5869,13 @@
         <v>204</v>
       </c>
       <c r="N23" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="Q23" s="22">
         <v>1</v>
@@ -5425,13 +5887,13 @@
         <v>17</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F24" s="22">
         <v>12</v>
@@ -5447,25 +5909,25 @@
         <v>860</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="K24" s="21" t="s">
         <v>21</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="M24" s="21" t="s">
         <v>204</v>
       </c>
       <c r="N24" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="O24" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="Q24" s="22">
         <v>1</v>
@@ -5477,13 +5939,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>46</v>
@@ -5499,25 +5961,25 @@
         <v>1430</v>
       </c>
       <c r="J25" s="21" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="K25" s="21" t="s">
         <v>21</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="M25" s="21" t="s">
         <v>204</v>
       </c>
       <c r="N25" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="Q25" s="22">
         <v>1</v>
@@ -5529,13 +5991,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F26" s="22">
         <v>11</v>
@@ -5551,25 +6013,25 @@
         <v>-25</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="K26" s="21" t="s">
         <v>21</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="M26" s="21" t="s">
         <v>204</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="P26" s="21" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="Q26" s="22">
         <v>1</v>
@@ -5638,10 +6100,10 @@
       <c r="A30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="26"/>
+      <c r="D30" s="27"/>
       <c r="E30" s="4" t="s">
         <v>192</v>
       </c>
@@ -5653,7 +6115,7 @@
         <v>17</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>193</v>
@@ -5667,16 +6129,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>9280</v>
       </c>
-      <c r="D31" s="27"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="3">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
         <v>20</v>
@@ -5703,7 +6165,7 @@
         <v>9</v>
       </c>
       <c r="O31" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="P31">
         <f>L36</f>
@@ -5714,10 +6176,10 @@
       <c r="B32" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C32" s="28">
-        <v>0</v>
-      </c>
-      <c r="D32" s="28"/>
+      <c r="C32" s="29">
+        <v>0</v>
+      </c>
+      <c r="D32" s="29"/>
       <c r="K32" t="s">
         <v>200</v>
       </c>
@@ -5741,11 +6203,11 @@
       <c r="B33" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="29">
         <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>-3055</v>
       </c>
-      <c r="D33" s="28"/>
+      <c r="D33" s="29"/>
       <c r="E33" s="2">
         <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
         <v>4</v>
@@ -5765,11 +6227,11 @@
       <c r="B34" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <f>SUBTOTAL(9,C31:C33)</f>
         <v>6225</v>
       </c>
-      <c r="D34" s="26"/>
+      <c r="D34" s="27"/>
       <c r="E34">
         <f>E31</f>
         <v>20</v>
@@ -5781,7 +6243,7 @@
         <v>-2315</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="O34" t="s">
         <v>21</v>
@@ -5795,8 +6257,8 @@
       <c r="B35" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
       <c r="K35" s="2" t="s">
         <v>206</v>
       </c>
@@ -5812,8 +6274,8 @@
       <c r="B36" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
       <c r="L36" s="13">
         <f>SUBTOTAL(9,L31:L35)</f>
         <v>2401</v>
@@ -5834,11 +6296,11 @@
       <c r="B38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="26">
         <f>C34+C35+C36</f>
         <v>6225</v>
       </c>
-      <c r="D38" s="25"/>
+      <c r="D38" s="26"/>
       <c r="E38" s="1" t="s">
         <v>211</v>
       </c>
@@ -5953,7 +6415,7 @@
         <v>-795</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="11:13" x14ac:dyDescent="0.25">
@@ -6042,7 +6504,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P26" xr:uid="{00000000-0009-0000-0000-000002000000}">
+  <autoFilter ref="A2:P26" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P26">
       <sortCondition ref="J2:J26"/>
     </sortState>
@@ -6062,6 +6524,2833 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A2:Q81"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="72" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="F3" s="18">
+        <v>7</v>
+      </c>
+      <c r="G3" s="18">
+        <v>30</v>
+      </c>
+      <c r="H3" s="18">
+        <v>30</v>
+      </c>
+      <c r="I3" s="18">
+        <f t="shared" ref="I3:I55" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="16">
+        <v>6</v>
+      </c>
+      <c r="G4" s="16">
+        <v>915</v>
+      </c>
+      <c r="H4" s="16">
+        <v>25</v>
+      </c>
+      <c r="I4" s="24">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" s="16">
+        <v>7</v>
+      </c>
+      <c r="G5" s="16">
+        <v>850</v>
+      </c>
+      <c r="H5" s="16">
+        <v>30</v>
+      </c>
+      <c r="I5" s="24">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" s="16">
+        <v>12</v>
+      </c>
+      <c r="G6" s="16">
+        <v>670</v>
+      </c>
+      <c r="H6" s="16">
+        <v>30</v>
+      </c>
+      <c r="I6" s="24">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1515</v>
+      </c>
+      <c r="H7" s="16">
+        <v>35</v>
+      </c>
+      <c r="I7" s="24">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="F8" s="16">
+        <v>8</v>
+      </c>
+      <c r="G8" s="16">
+        <v>690</v>
+      </c>
+      <c r="H8" s="16">
+        <v>30</v>
+      </c>
+      <c r="I8" s="24">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="16">
+        <v>1345</v>
+      </c>
+      <c r="H9" s="16">
+        <v>25</v>
+      </c>
+      <c r="I9" s="24">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="16">
+        <v>850</v>
+      </c>
+      <c r="H10" s="16">
+        <v>30</v>
+      </c>
+      <c r="I10" s="24">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="16">
+        <v>830</v>
+      </c>
+      <c r="H11" s="16">
+        <v>30</v>
+      </c>
+      <c r="I11" s="24">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <v>25</v>
+      </c>
+      <c r="I12" s="24">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="16">
+        <v>780</v>
+      </c>
+      <c r="H13" s="16">
+        <v>30</v>
+      </c>
+      <c r="I13" s="24">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="F14" s="16">
+        <v>8</v>
+      </c>
+      <c r="G14" s="16">
+        <v>740</v>
+      </c>
+      <c r="H14" s="16">
+        <v>30</v>
+      </c>
+      <c r="I14" s="24">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="16">
+        <v>755</v>
+      </c>
+      <c r="H15" s="16">
+        <v>25</v>
+      </c>
+      <c r="I15" s="24">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="16">
+        <v>12</v>
+      </c>
+      <c r="G16" s="16">
+        <v>770</v>
+      </c>
+      <c r="H16" s="16">
+        <v>30</v>
+      </c>
+      <c r="I16" s="24">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="16">
+        <v>735</v>
+      </c>
+      <c r="H17" s="16">
+        <v>35</v>
+      </c>
+      <c r="I17" s="24">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>30</v>
+      </c>
+      <c r="I18" s="24">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="F19" s="16">
+        <v>8</v>
+      </c>
+      <c r="G19" s="16">
+        <v>690</v>
+      </c>
+      <c r="H19" s="16">
+        <v>30</v>
+      </c>
+      <c r="I19" s="24">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16">
+        <v>35</v>
+      </c>
+      <c r="I20" s="24">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="F21" s="18">
+        <v>2</v>
+      </c>
+      <c r="G21" s="18">
+        <v>120</v>
+      </c>
+      <c r="H21" s="18">
+        <v>60</v>
+      </c>
+      <c r="I21" s="18">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="F22" s="18">
+        <v>2</v>
+      </c>
+      <c r="G22" s="18">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18">
+        <v>0</v>
+      </c>
+      <c r="I22" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="F23" s="16">
+        <v>2</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1150</v>
+      </c>
+      <c r="H23" s="16">
+        <v>30</v>
+      </c>
+      <c r="I23" s="24">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="16">
+        <v>820</v>
+      </c>
+      <c r="H24" s="16">
+        <v>20</v>
+      </c>
+      <c r="I24" s="24">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="F25" s="16">
+        <v>2</v>
+      </c>
+      <c r="G25" s="16">
+        <v>2120</v>
+      </c>
+      <c r="H25" s="16">
+        <v>35</v>
+      </c>
+      <c r="I25" s="24">
+        <f t="shared" si="0"/>
+        <v>2085</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="F26" s="16">
+        <v>12</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16">
+        <v>30</v>
+      </c>
+      <c r="I26" s="24">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="18">
+        <v>0</v>
+      </c>
+      <c r="H27" s="18">
+        <v>20</v>
+      </c>
+      <c r="I27" s="18">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="F28" s="16">
+        <v>12</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <v>30</v>
+      </c>
+      <c r="I28" s="24">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="16">
+        <v>1165</v>
+      </c>
+      <c r="H29" s="16">
+        <v>25</v>
+      </c>
+      <c r="I29" s="24">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="16">
+        <v>30</v>
+      </c>
+      <c r="H30" s="16">
+        <v>30</v>
+      </c>
+      <c r="I30" s="24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="16">
+        <v>30</v>
+      </c>
+      <c r="H31" s="16">
+        <v>30</v>
+      </c>
+      <c r="I31" s="24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" s="16">
+        <v>40</v>
+      </c>
+      <c r="H32" s="16">
+        <v>40</v>
+      </c>
+      <c r="I32" s="24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="F33" s="16">
+        <v>3</v>
+      </c>
+      <c r="G33" s="16">
+        <v>775</v>
+      </c>
+      <c r="H33" s="16">
+        <v>25</v>
+      </c>
+      <c r="I33" s="24">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="F34" s="16">
+        <v>3</v>
+      </c>
+      <c r="G34" s="16">
+        <v>790</v>
+      </c>
+      <c r="H34" s="16">
+        <v>0</v>
+      </c>
+      <c r="I34" s="24">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="F35" s="16">
+        <v>4</v>
+      </c>
+      <c r="G35" s="16">
+        <v>535</v>
+      </c>
+      <c r="H35" s="16">
+        <v>25</v>
+      </c>
+      <c r="I35" s="24">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="F36" s="16">
+        <v>7</v>
+      </c>
+      <c r="G36" s="16">
+        <v>820</v>
+      </c>
+      <c r="H36" s="16">
+        <v>30</v>
+      </c>
+      <c r="I36" s="24">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="F37" s="16">
+        <v>10</v>
+      </c>
+      <c r="G37" s="16">
+        <v>2620</v>
+      </c>
+      <c r="H37" s="16">
+        <v>30</v>
+      </c>
+      <c r="I37" s="24">
+        <f t="shared" si="0"/>
+        <v>2590</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" s="16">
+        <v>705</v>
+      </c>
+      <c r="H38" s="16">
+        <v>35</v>
+      </c>
+      <c r="I38" s="24">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39" s="16">
+        <v>2860</v>
+      </c>
+      <c r="H39" s="16">
+        <v>30</v>
+      </c>
+      <c r="I39" s="24">
+        <f t="shared" si="0"/>
+        <v>2830</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="F40" s="16">
+        <v>4</v>
+      </c>
+      <c r="G40" s="16">
+        <v>1165</v>
+      </c>
+      <c r="H40" s="16">
+        <v>25</v>
+      </c>
+      <c r="I40" s="24">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="15"/>
+      <c r="B41" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="F41" s="16">
+        <v>7</v>
+      </c>
+      <c r="G41" s="16">
+        <v>1350</v>
+      </c>
+      <c r="H41" s="16">
+        <v>30</v>
+      </c>
+      <c r="I41" s="24">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G42" s="16">
+        <v>675</v>
+      </c>
+      <c r="H42" s="16">
+        <v>35</v>
+      </c>
+      <c r="I42" s="24">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="G43" s="16">
+        <v>660</v>
+      </c>
+      <c r="H43" s="16">
+        <v>20</v>
+      </c>
+      <c r="I43" s="24">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="F44" s="16">
+        <v>8</v>
+      </c>
+      <c r="G44" s="16">
+        <v>1430</v>
+      </c>
+      <c r="H44" s="16">
+        <v>30</v>
+      </c>
+      <c r="I44" s="24">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G45" s="16">
+        <v>855</v>
+      </c>
+      <c r="H45" s="16">
+        <v>35</v>
+      </c>
+      <c r="I45" s="24">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="F46" s="16">
+        <v>5</v>
+      </c>
+      <c r="G46" s="16">
+        <v>2120</v>
+      </c>
+      <c r="H46" s="16">
+        <v>30</v>
+      </c>
+      <c r="I46" s="24">
+        <f t="shared" si="0"/>
+        <v>2090</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="F47" s="16">
+        <v>7</v>
+      </c>
+      <c r="G47" s="16">
+        <v>0</v>
+      </c>
+      <c r="H47" s="16">
+        <v>30</v>
+      </c>
+      <c r="I47" s="24">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="F48" s="16">
+        <v>1</v>
+      </c>
+      <c r="G48" s="16">
+        <v>535</v>
+      </c>
+      <c r="H48" s="16">
+        <v>25</v>
+      </c>
+      <c r="I48" s="24">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="F49" s="16">
+        <v>1</v>
+      </c>
+      <c r="G49" s="16">
+        <v>-180</v>
+      </c>
+      <c r="H49" s="16">
+        <v>25</v>
+      </c>
+      <c r="I49" s="24">
+        <f t="shared" si="0"/>
+        <v>-205</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M49" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="15"/>
+      <c r="B50" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="F50" s="16">
+        <v>4</v>
+      </c>
+      <c r="G50" s="16">
+        <v>1355</v>
+      </c>
+      <c r="H50" s="16">
+        <v>25</v>
+      </c>
+      <c r="I50" s="24">
+        <f t="shared" si="0"/>
+        <v>1330</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="15"/>
+      <c r="B51" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="F51" s="16">
+        <v>7</v>
+      </c>
+      <c r="G51" s="16">
+        <v>1890</v>
+      </c>
+      <c r="H51" s="16">
+        <v>30</v>
+      </c>
+      <c r="I51" s="24">
+        <f t="shared" si="0"/>
+        <v>1860</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17"/>
+      <c r="B52" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" s="18">
+        <v>7</v>
+      </c>
+      <c r="G52" s="18">
+        <v>30</v>
+      </c>
+      <c r="H52" s="18">
+        <v>30</v>
+      </c>
+      <c r="I52" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="M52" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F53" s="16">
+        <v>10</v>
+      </c>
+      <c r="G53" s="16">
+        <v>25</v>
+      </c>
+      <c r="H53" s="16">
+        <v>25</v>
+      </c>
+      <c r="I53" s="24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G54" s="16">
+        <v>750</v>
+      </c>
+      <c r="H54" s="16">
+        <v>30</v>
+      </c>
+      <c r="I54" s="24">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="15"/>
+      <c r="P54" s="15"/>
+      <c r="Q54" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="F55" s="16">
+        <v>1</v>
+      </c>
+      <c r="G55" s="16">
+        <v>0</v>
+      </c>
+      <c r="H55" s="16">
+        <v>30</v>
+      </c>
+      <c r="I55" s="24">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D57" s="1">
+        <f>COUNTA(D3:D55)</f>
+        <v>47</v>
+      </c>
+      <c r="G57" s="1">
+        <f t="shared" ref="G57:Q57" si="1">SUBTOTAL(9,G3:G55)</f>
+        <v>39405</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="1"/>
+        <v>1515</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="1"/>
+        <v>37890</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <f>-9*17</f>
+        <v>-153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="27"/>
+      <c r="E59" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H59">
+        <f>-7*25</f>
+        <v>-175</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>302</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="28">
+        <f>SUMIFS(I$3:I$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
+        <v>37890</v>
+      </c>
+      <c r="D60" s="28"/>
+      <c r="E60" s="3">
+        <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,L$3:L$55,A$60)</f>
+        <v>53</v>
+      </c>
+      <c r="F60" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60">
+        <f>-2*30</f>
+        <v>-60</v>
+      </c>
+      <c r="K60" t="s">
+        <v>197</v>
+      </c>
+      <c r="L60">
+        <f>SUMIFS(G$3:G$55,J$3:J$55,K$59)</f>
+        <v>21765</v>
+      </c>
+      <c r="M60">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$59)-INT(COUNTIFS(J$3:J$55,K$59,M$3:M$55,"*gộp*")/2)</f>
+        <v>22</v>
+      </c>
+      <c r="O60" t="s">
+        <v>135</v>
+      </c>
+      <c r="P60">
+        <f>L65</f>
+        <v>21245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="29">
+        <v>0</v>
+      </c>
+      <c r="D61" s="29"/>
+      <c r="K61" t="s">
+        <v>200</v>
+      </c>
+      <c r="L61">
+        <f>-SUMIFS(H$3:H$55,J$3:J$55,K$59)+M61*5</f>
+        <v>-520</v>
+      </c>
+      <c r="M61">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$59)-INT(COUNTIFS(J$3:J$55,K$59,M$3:M$55,"*gộp*")/2)</f>
+        <v>22</v>
+      </c>
+      <c r="O61" t="s">
+        <v>447</v>
+      </c>
+      <c r="P61">
+        <f>L73</f>
+        <v>11777</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="29">
+        <f>-SUMIFS(I$3:I$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="29"/>
+      <c r="E62" s="2">
+        <f>SUMIFS(Q$3:Q$55,B$3:B$55,A$59,P$3:P$55,"xx",N$3:N$55,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K62" t="s">
+        <v>202</v>
+      </c>
+      <c r="O62" t="s">
+        <v>21</v>
+      </c>
+      <c r="P62">
+        <f>L81</f>
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B63" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C63" s="27">
+        <f>SUBTOTAL(9,C60:C62)</f>
+        <v>37890</v>
+      </c>
+      <c r="D63" s="27"/>
+      <c r="E63">
+        <f>E60</f>
+        <v>53</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="O63" t="s">
+        <v>207</v>
+      </c>
+      <c r="P63">
+        <f>-C67</f>
+        <v>-37890</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="K64" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P64" s="4">
+        <f>SUBTOTAL(9,P60:P63)</f>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="L65" s="13">
+        <f>SUBTOTAL(9,L60:L64)</f>
+        <v>21245</v>
+      </c>
+      <c r="M65" s="13">
+        <f>M60</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67" s="26">
+        <f>C63+C64+C65</f>
+        <v>37890</v>
+      </c>
+      <c r="D67" s="26"/>
+      <c r="E67" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K68" t="s">
+        <v>197</v>
+      </c>
+      <c r="L68">
+        <f>SUMIFS(G$3:G$55,J$3:J$55,K$67)</f>
+        <v>12165</v>
+      </c>
+      <c r="M68">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$67)-INT(COUNTIFS(J$3:J$55,K$67,M$3:M$55,"*gộp*")/2)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K69" t="s">
+        <v>200</v>
+      </c>
+      <c r="L69">
+        <f>SUM(H58:H60)</f>
+        <v>-388</v>
+      </c>
+      <c r="M69">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$67)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K71" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K72" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L73" s="13">
+        <f>SUBTOTAL(9,L68:L72)</f>
+        <v>11777</v>
+      </c>
+      <c r="M73" s="13">
+        <f>M68</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K75" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K76" t="s">
+        <v>197</v>
+      </c>
+      <c r="L76">
+        <f>SUMIFS(G$3:G$55,J$3:J$55,K$75)</f>
+        <v>5475</v>
+      </c>
+      <c r="M76">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$75)-INT(COUNTIFS(J$3:J$55,K$75,M$3:M$55,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K77" t="s">
+        <v>200</v>
+      </c>
+      <c r="L77">
+        <f>-SUMIFS(H$3:H$55,J$3:J$55,K$75)+M77*5</f>
+        <v>-295</v>
+      </c>
+      <c r="M77">
+        <f>SUMIFS(Q$3:Q$55,J$3:J$55,K$75)-INT(COUNTIFS(J$3:J$55,K$75,M$3:M$55,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K78" t="s">
+        <v>202</v>
+      </c>
+      <c r="L78">
+        <f>-M78*2</f>
+        <v>-102</v>
+      </c>
+      <c r="M78">
+        <f>E63-(COUNTIFS(M$3:M$55,"*gộp*")/2)-COUNTIFS(M$3:M$55,"*đơn trả*")-COUNTIFS(M$3:M$55,"*hàng tỉnh*")</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K79" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K80" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L81" s="13">
+        <f>SUBTOTAL(9,L76:L80)</f>
+        <v>5078</v>
+      </c>
+      <c r="M81" s="13">
+        <f>M76</f>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P55">
+      <sortCondition ref="J2:J55"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -6080,7 +9369,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>212</v>
+        <v>289</v>
       </c>
       <c r="B1" s="5">
         <v>2026</v>
@@ -6088,19 +9377,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>216</v>
+        <v>293</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>217</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6172,11 +9461,11 @@
       </c>
       <c r="B6" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C6" s="8">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" s="8" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;TEXT(A6,"DD-MM")&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
@@ -6184,7 +9473,7 @@
       </c>
       <c r="E6" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6651,16 +9940,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="9" t="s">
-        <v>218</v>
+        <v>295</v>
       </c>
       <c r="E29" s="9">
         <f ca="1">SUBTOTAL(9,E4:E28)</f>
-        <v>16</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="9" t="s">
-        <v>219</v>
+        <v>296</v>
       </c>
       <c r="E30" s="9" cm="1">
         <f t="array" ref="E30" ca="1">SUMPRODUCT(
@@ -6672,29 +9961,29 @@
         ),
     0)
 )</f>
-        <v>19</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="9" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="E31" s="9">
         <f ca="1">-E29*2</f>
-        <v>-32</v>
+        <v>-134</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D32" s="9" t="s">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="E32" s="9">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>-13</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D28">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport.xlsx
+++ b/data/May/InternalDailyReport.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687AB54C-57BB-48FA-A38C-F8313A603340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FE7E08-7A5E-4188-9E5E-7071CEB1D219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
     <sheet name="04-05" sheetId="8" r:id="rId2"/>
     <sheet name="05-05" sheetId="9" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId4"/>
+    <sheet name="06-05" sheetId="10" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'04-05'!$A$2:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'05-05'!$A$2:$P$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet1!$A$2:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'06-05'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="545">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -933,6 +935,459 @@
     <t>1 đơn</t>
   </si>
   <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018539</t>
+  </si>
+  <si>
+    <t>70 đường số 1 KDC nam long</t>
+  </si>
+  <si>
+    <t>AT 05-05</t>
+  </si>
+  <si>
+    <t>05-05-2026</t>
+  </si>
+  <si>
+    <t>Giáng Hương</t>
+  </si>
+  <si>
+    <t>HD018400</t>
+  </si>
+  <si>
+    <t>111 đường số 10 phường 13</t>
+  </si>
+  <si>
+    <t>Hiểu My</t>
+  </si>
+  <si>
+    <t>HD018563</t>
+  </si>
+  <si>
+    <t>Toà 2, chung cư river panorama, 20 lê thị chợ, phường phú thuận</t>
+  </si>
+  <si>
+    <t>Nhung Bùi</t>
+  </si>
+  <si>
+    <t>H0018373</t>
+  </si>
+  <si>
+    <t>409/108/32/14c huynh thị hai, tân chánh hiệp</t>
+  </si>
+  <si>
+    <t>C. Phương fb Nuory Le</t>
+  </si>
+  <si>
+    <t>HD018435</t>
+  </si>
+  <si>
+    <t>A28/1Dw3 quốc lộ 50 ấp 1 xã bình hưng</t>
+  </si>
+  <si>
+    <t>ny nhỏ</t>
+  </si>
+  <si>
+    <t>HD018341</t>
+  </si>
+  <si>
+    <t>49 le quang kim p8</t>
+  </si>
+  <si>
+    <t>Hoàng Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD018387</t>
+  </si>
+  <si>
+    <t>2/11 đường thiên phước, p9</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng</t>
+  </si>
+  <si>
+    <t>HD018553</t>
+  </si>
+  <si>
+    <t>155/14 đs 11 bình hưng hoà</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD018231</t>
+  </si>
+  <si>
+    <t>100/17 liên khu 1-6 bình trị đông</t>
+  </si>
+  <si>
+    <t>hàng của Đào Ngọc Bích</t>
+  </si>
+  <si>
+    <t>HD018540</t>
+  </si>
+  <si>
+    <t>007 Lộ B chung cư Tây Thạnh, phường Tân Thạnh</t>
+  </si>
+  <si>
+    <t>Việt Anh - fb Hồ Thị Uyên</t>
+  </si>
+  <si>
+    <t>HD018388</t>
+  </si>
+  <si>
+    <t>350/27 Lê Văn Quới, Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>cô dung fb Nini Thach</t>
+  </si>
+  <si>
+    <t>HD018521</t>
+  </si>
+  <si>
+    <t>137/74a âu dương lân - p2</t>
+  </si>
+  <si>
+    <t>Mi Ni</t>
+  </si>
+  <si>
+    <t>HD018437</t>
+  </si>
+  <si>
+    <t>536/32/23 âu cơ</t>
+  </si>
+  <si>
+    <t>HD018486</t>
+  </si>
+  <si>
+    <t>Châu Châu</t>
+  </si>
+  <si>
+    <t>HD018490</t>
+  </si>
+  <si>
+    <t>E3/8 ấp 56 xã vĩnh lộc</t>
+  </si>
+  <si>
+    <t>Thanh Xuân</t>
+  </si>
+  <si>
+    <t>HD018565</t>
+  </si>
+  <si>
+    <t>17/4B Liên khu 5-6 bình hưng hòa b</t>
+  </si>
+  <si>
+    <t>Hồng My</t>
+  </si>
+  <si>
+    <t>HD018549</t>
+  </si>
+  <si>
+    <t>192 Phạm Đức Sơn, Phường 16 (Chung Cư Heaven Riverview - Mỹ Phúc) Block B</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hoà</t>
+  </si>
+  <si>
+    <t>My Luu</t>
+  </si>
+  <si>
+    <t>HD018546</t>
+  </si>
+  <si>
+    <t>Toà T1, chung cư Vista Verde, số 8 Nguyễn Thanh Sơn, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>gộp, đổi hàng</t>
+  </si>
+  <si>
+    <t>HD018552</t>
+  </si>
+  <si>
+    <t>Thảo</t>
+  </si>
+  <si>
+    <t>HD018440</t>
+  </si>
+  <si>
+    <t>280a12 Lương Đình Của. An Phú</t>
+  </si>
+  <si>
+    <t>Nguyen Diem My</t>
+  </si>
+  <si>
+    <t>HD018321</t>
+  </si>
+  <si>
+    <t>212 lê quang định phường 14</t>
+  </si>
+  <si>
+    <t>Love May</t>
+  </si>
+  <si>
+    <t>HD018311</t>
+  </si>
+  <si>
+    <t>T4 Masteri Đường Số 10, Thảo Điền</t>
+  </si>
+  <si>
+    <t>Đinh Thị Kim Lan</t>
+  </si>
+  <si>
+    <t>HD018306</t>
+  </si>
+  <si>
+    <t>Ngân hàng Tpbank 303 (39/6) Trường Chinh P Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Thu Ba DS</t>
+  </si>
+  <si>
+    <t>HD018302</t>
+  </si>
+  <si>
+    <t>395 Bùi Đình Tuý, p14</t>
+  </si>
+  <si>
+    <t>Ivy Dao</t>
+  </si>
+  <si>
+    <t>HD018318</t>
+  </si>
+  <si>
+    <t>238/3 trường chinh, đông hưng thuận</t>
+  </si>
+  <si>
+    <t>Mỹ Ngọc</t>
+  </si>
+  <si>
+    <t>HD018275</t>
+  </si>
+  <si>
+    <t>242 nguyễn oanh, phường gò vấp</t>
+  </si>
+  <si>
+    <t>Ly Clara Selena</t>
+  </si>
+  <si>
+    <t>403 tân sơn p12</t>
+  </si>
+  <si>
+    <t>LISA</t>
+  </si>
+  <si>
+    <t>685 tân sơn phường 12</t>
+  </si>
+  <si>
+    <t>THU TRƯƠNG</t>
+  </si>
+  <si>
+    <t>159/43/5 Đường Bạch Đằng, phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Nhung SaLin</t>
+  </si>
+  <si>
+    <t>HD018386</t>
+  </si>
+  <si>
+    <t>19a Trần Quang diệu p13</t>
+  </si>
+  <si>
+    <t>gộp</t>
+  </si>
+  <si>
+    <t>HD018538</t>
+  </si>
+  <si>
+    <t>Trâm Trang</t>
+  </si>
+  <si>
+    <t>HD018328</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1</t>
+  </si>
+  <si>
+    <t>Nhi</t>
+  </si>
+  <si>
+    <t>HD018213</t>
+  </si>
+  <si>
+    <t>27 nguyễn hữu thọ (sunrise city toà X1) phường Tân Hưng</t>
+  </si>
+  <si>
+    <t>Trần Thục Oanh</t>
+  </si>
+  <si>
+    <t>HD018532</t>
+  </si>
+  <si>
+    <t>118 đường 3/2, p12</t>
+  </si>
+  <si>
+    <t>Trần Ngọc Thúy</t>
+  </si>
+  <si>
+    <t>HD018516</t>
+  </si>
+  <si>
+    <t>saigon mia block b cổng sau</t>
+  </si>
+  <si>
+    <t>Ngọc Vinh</t>
+  </si>
+  <si>
+    <t>HD018285</t>
+  </si>
+  <si>
+    <t>17-19 Trường Sơn P4</t>
+  </si>
+  <si>
+    <t>Miu miu quỳnh</t>
+  </si>
+  <si>
+    <t>HD018466</t>
+  </si>
+  <si>
+    <t>109 Bến Vân Đồn P9</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Bảo Loan</t>
+  </si>
+  <si>
+    <t>HD018401</t>
+  </si>
+  <si>
+    <t>tòa b2 chung cư lavida plus số 1181 nguyễn văn linh tân phong</t>
+  </si>
+  <si>
+    <t>Vy Vy</t>
+  </si>
+  <si>
+    <t>HD018348</t>
+  </si>
+  <si>
+    <t>Block B chung cư Sunrise RiverSide, Nguyễn Hữu Thọ, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Ngà Ngọc</t>
+  </si>
+  <si>
+    <t>HD018269</t>
+  </si>
+  <si>
+    <t>85 phan xích long p2</t>
+  </si>
+  <si>
+    <t>phu nhuan</t>
+  </si>
+  <si>
+    <t>Elena Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018325</t>
+  </si>
+  <si>
+    <t>56/41 dương ba trạc, Phường 02</t>
+  </si>
+  <si>
+    <t>HD018494</t>
+  </si>
+  <si>
+    <t>chung cư the park residence, 12 nguyễn hữu thọ phước kien nha be</t>
+  </si>
+  <si>
+    <t>Hoàng Thuý Liên</t>
+  </si>
+  <si>
+    <t>HD017772</t>
+  </si>
+  <si>
+    <t>290 an dương vương phường chợ quán</t>
+  </si>
+  <si>
+    <t>yenchau</t>
+  </si>
+  <si>
+    <t>HD018526</t>
+  </si>
+  <si>
+    <t>Chung cu Horita, lo C, Đường D4, P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Thư Ánh Võ</t>
+  </si>
+  <si>
+    <t>HD018343</t>
+  </si>
+  <si>
+    <t>5 lê thánh tôn bến nghé</t>
+  </si>
+  <si>
+    <t>Ly Sokny- 012776599</t>
+  </si>
+  <si>
+    <t>HD018248</t>
+  </si>
+  <si>
+    <t>359 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>shipper ứng tiền cho nhà xe</t>
+  </si>
+  <si>
+    <t>Tuyết</t>
+  </si>
+  <si>
+    <t>HD018429</t>
+  </si>
+  <si>
+    <t>30/18 đường số 6 KP18 Phường Vĩnh Hội</t>
+  </si>
+  <si>
+    <t>Hồng Miên</t>
+  </si>
+  <si>
+    <t>HD018250</t>
+  </si>
+  <si>
+    <t>123 đường số 11 tân kiểng tân quy</t>
+  </si>
+  <si>
+    <t>HD018376</t>
+  </si>
+  <si>
+    <t>Loan Thỏ</t>
+  </si>
+  <si>
+    <t>HD018544</t>
+  </si>
+  <si>
+    <t>81/6 Hồ thị kỷ, phường 1</t>
+  </si>
+  <si>
+    <t>FANG FANG</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>DARAVIN</t>
+  </si>
+  <si>
+    <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
+  </si>
+  <si>
+    <t>at 05-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -963,457 +1418,289 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Nhung SaLin</t>
-  </si>
-  <si>
-    <t>HD018538</t>
-  </si>
-  <si>
-    <t>19a Trần Quang diệu p13</t>
-  </si>
-  <si>
-    <t>05-05-2026</t>
-  </si>
-  <si>
-    <t>gộp</t>
-  </si>
-  <si>
-    <t>Lan Anh Nguyễn</t>
-  </si>
-  <si>
-    <t>HD018539</t>
-  </si>
-  <si>
-    <t>70 đường số 1 KDC nam long</t>
-  </si>
-  <si>
-    <t>AT 05-05</t>
-  </si>
-  <si>
-    <t>Trâm Trang</t>
-  </si>
-  <si>
-    <t>HD018328</t>
-  </si>
-  <si>
-    <t>346 bến vân đồn p1</t>
-  </si>
-  <si>
-    <t>Giáng Hương</t>
-  </si>
-  <si>
-    <t>HD018400</t>
-  </si>
-  <si>
-    <t>111 đường số 10 phường 13</t>
-  </si>
-  <si>
-    <t>Nhi</t>
-  </si>
-  <si>
-    <t>HD018213</t>
-  </si>
-  <si>
-    <t>Hiểu My</t>
-  </si>
-  <si>
-    <t>HD018563</t>
-  </si>
-  <si>
-    <t>Toà 2, chung cư river panorama, 20 lê thị chợ, phường phú thuận</t>
-  </si>
-  <si>
-    <t>Trần Thục Oanh</t>
-  </si>
-  <si>
-    <t>HD018532</t>
-  </si>
-  <si>
-    <t>118 đường 3/2, p12</t>
-  </si>
-  <si>
-    <t>Nhung Bùi</t>
-  </si>
-  <si>
-    <t>H0018373</t>
-  </si>
-  <si>
-    <t>409/108/32/14c huynh thị hai, tân chánh hiệp</t>
-  </si>
-  <si>
-    <t>Trần Ngọc Thúy</t>
-  </si>
-  <si>
-    <t>HD018516</t>
-  </si>
-  <si>
-    <t>saigon mia block b cổng sau</t>
-  </si>
-  <si>
-    <t>Ngọc Vinh</t>
-  </si>
-  <si>
-    <t>HD018285</t>
-  </si>
-  <si>
-    <t>17-19 Trường Sơn P4</t>
-  </si>
-  <si>
-    <t>C. Phương fb Nuory Le</t>
-  </si>
-  <si>
-    <t>HD018435</t>
-  </si>
-  <si>
-    <t>A28/1Dw3 quốc lộ 50 ấp 1 xã bình hưng</t>
-  </si>
-  <si>
-    <t>ny nhỏ</t>
-  </si>
-  <si>
-    <t>HD018341</t>
-  </si>
-  <si>
-    <t>49 le quang kim p8</t>
-  </si>
-  <si>
-    <t>Miu miu quỳnh</t>
-  </si>
-  <si>
-    <t>HD018466</t>
-  </si>
-  <si>
-    <t>109 Bến Vân Đồn P9</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Bảo Loan</t>
-  </si>
-  <si>
-    <t>HD018401</t>
-  </si>
-  <si>
-    <t>tòa b2 chung cư lavida plus số 1181 nguyễn văn linh tân phong</t>
-  </si>
-  <si>
-    <t>Hoàng Bảo Trân</t>
-  </si>
-  <si>
-    <t>HD018387</t>
-  </si>
-  <si>
-    <t>2/11 đường thiên phước, p9</t>
-  </si>
-  <si>
-    <t>Vy Vy</t>
-  </si>
-  <si>
-    <t>HD018348</t>
-  </si>
-  <si>
-    <t>Block B chung cư Sunrise RiverSide, Nguyễn Hữu Thọ, Phước Kiển</t>
-  </si>
-  <si>
-    <t>Lê Thị Minh Phượng</t>
-  </si>
-  <si>
-    <t>HD018553</t>
-  </si>
-  <si>
-    <t>155/14 đs 11 bình hưng hoà</t>
-  </si>
-  <si>
-    <t>My Luu</t>
-  </si>
-  <si>
-    <t>HD018552</t>
-  </si>
-  <si>
-    <t>Toà T1, chung cư Vista Verde, số 8 Nguyễn Thanh Sơn, phường Cát Lái</t>
-  </si>
-  <si>
-    <t>gộp, đổi hàng</t>
-  </si>
-  <si>
-    <t>Tuyết Nhi</t>
-  </si>
-  <si>
-    <t>HD018231</t>
-  </si>
-  <si>
-    <t>100/17 liên khu 1-6 bình trị đông</t>
-  </si>
-  <si>
-    <t>Thảo</t>
-  </si>
-  <si>
-    <t>HD018440</t>
-  </si>
-  <si>
-    <t>280a12 Lương Đình Của. An Phú</t>
-  </si>
-  <si>
-    <t>Nguyen Diem My</t>
-  </si>
-  <si>
-    <t>HD018321</t>
-  </si>
-  <si>
-    <t>212 lê quang định phường 14</t>
-  </si>
-  <si>
-    <t>Ngà Ngọc</t>
-  </si>
-  <si>
-    <t>HD018269</t>
-  </si>
-  <si>
-    <t>85 phan xích long p2</t>
-  </si>
-  <si>
-    <t>phu nhuan</t>
-  </si>
-  <si>
-    <t>Elena Nguyễn</t>
-  </si>
-  <si>
-    <t>HD018325</t>
-  </si>
-  <si>
-    <t>56/41 dương ba trạc, Phường 02</t>
-  </si>
-  <si>
-    <t>HD018386</t>
-  </si>
-  <si>
-    <t>hàng của Đào Ngọc Bích</t>
-  </si>
-  <si>
-    <t>HD018540</t>
-  </si>
-  <si>
-    <t>007 Lộ B chung cư Tây Thạnh, phường Tân Thạnh</t>
-  </si>
-  <si>
-    <t>Việt Anh - fb Hồ Thị Uyên</t>
-  </si>
-  <si>
-    <t>HD018388</t>
-  </si>
-  <si>
-    <t>350/27 Lê Văn Quới, Bình Hưng Hòa A</t>
-  </si>
-  <si>
-    <t>HD018494</t>
-  </si>
-  <si>
-    <t>chung cư the park residence, 12 nguyễn hữu thọ phước kien nha be</t>
-  </si>
-  <si>
-    <t>cô dung fb Nini Thach</t>
-  </si>
-  <si>
-    <t>HD018521</t>
-  </si>
-  <si>
-    <t>137/74a âu dương lân - p2</t>
-  </si>
-  <si>
-    <t>Love May</t>
-  </si>
-  <si>
-    <t>HD018311</t>
-  </si>
-  <si>
-    <t>T4 Masteri Đường Số 10, Thảo Điền</t>
-  </si>
-  <si>
-    <t>Mi Ni</t>
-  </si>
-  <si>
-    <t>HD018437</t>
-  </si>
-  <si>
-    <t>536/32/23 âu cơ</t>
-  </si>
-  <si>
-    <t>HD018486</t>
-  </si>
-  <si>
-    <t>HD018546</t>
-  </si>
-  <si>
-    <t>Hoàng Thuý Liên</t>
-  </si>
-  <si>
-    <t>HD017772</t>
-  </si>
-  <si>
-    <t>290 an dương vương phường chợ quán</t>
-  </si>
-  <si>
-    <t>yenchau</t>
-  </si>
-  <si>
-    <t>HD018526</t>
-  </si>
-  <si>
-    <t>Chung cu Horita, lo C, Đường D4, P. Tân Hưng</t>
-  </si>
-  <si>
-    <t>Thư Ánh Võ</t>
-  </si>
-  <si>
-    <t>HD018343</t>
-  </si>
-  <si>
-    <t>5 lê thánh tôn bến nghé</t>
-  </si>
-  <si>
-    <t>Châu Châu</t>
-  </si>
-  <si>
-    <t>HD018490</t>
-  </si>
-  <si>
-    <t>E3/8 ấp 56 xã vĩnh lộc</t>
-  </si>
-  <si>
-    <t>Ly Sokny- 012776599</t>
-  </si>
-  <si>
-    <t>HD018248</t>
-  </si>
-  <si>
-    <t>359 phạm ngũ lão</t>
-  </si>
-  <si>
-    <t>Tuyết</t>
-  </si>
-  <si>
-    <t>HD018429</t>
-  </si>
-  <si>
-    <t>30/18 đường số 6 KP18 Phường Vĩnh Hội</t>
-  </si>
-  <si>
-    <t>Hồng Miên</t>
-  </si>
-  <si>
-    <t>HD018250</t>
-  </si>
-  <si>
-    <t>123 đường số 11 tân kiểng tân quy</t>
-  </si>
-  <si>
-    <t>Đinh Thị Kim Lan</t>
-  </si>
-  <si>
-    <t>HD018306</t>
-  </si>
-  <si>
-    <t>Ngân hàng Tpbank 303 (39/6) Trường Chinh P Tân Thới Nhất</t>
-  </si>
-  <si>
-    <t>Thu Ba DS</t>
-  </si>
-  <si>
-    <t>HD018302</t>
-  </si>
-  <si>
-    <t>395 Bùi Đình Tuý, p14</t>
-  </si>
-  <si>
-    <t>Thanh Xuân</t>
-  </si>
-  <si>
-    <t>HD018565</t>
-  </si>
-  <si>
-    <t>17/4B Liên khu 5-6 bình hưng hòa b</t>
-  </si>
-  <si>
-    <t>Ivy Dao</t>
-  </si>
-  <si>
-    <t>HD018318</t>
-  </si>
-  <si>
-    <t>238/3 trường chinh, đông hưng thuận</t>
-  </si>
-  <si>
-    <t>HD018376</t>
-  </si>
-  <si>
-    <t>Loan Thỏ</t>
-  </si>
-  <si>
-    <t>HD018544</t>
-  </si>
-  <si>
-    <t>81/6 Hồ thị kỷ, phường 1</t>
-  </si>
-  <si>
-    <t>Hồng My</t>
-  </si>
-  <si>
-    <t>HD018549</t>
-  </si>
-  <si>
-    <t>192 Phạm Đức Sơn, Phường 16 (Chung Cư Heaven Riverview - Mỹ Phúc) Block B</t>
-  </si>
-  <si>
-    <t>Mỹ Ngọc</t>
-  </si>
-  <si>
-    <t>HD018275</t>
-  </si>
-  <si>
-    <t>242 nguyễn oanh, phường gò vấp</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hải</t>
-  </si>
-  <si>
-    <t>17 Đường Số 13 Bình Hưng Hoà</t>
-  </si>
-  <si>
-    <t>FANG FANG</t>
-  </si>
-  <si>
-    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
-  </si>
-  <si>
-    <t>Ly Clara Selena</t>
-  </si>
-  <si>
-    <t>403 tân sơn p12</t>
-  </si>
-  <si>
-    <t>LISA</t>
-  </si>
-  <si>
-    <t>685 tân sơn phường 12</t>
-  </si>
-  <si>
-    <t>THU TRƯƠNG</t>
-  </si>
-  <si>
-    <t>159/43/5 Đường Bạch Đằng, phường Tân Sơn Hòa</t>
-  </si>
-  <si>
-    <t>DARAVIN</t>
-  </si>
-  <si>
-    <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
-  </si>
-  <si>
-    <t>at 05-05</t>
-  </si>
-  <si>
-    <t>shipper ứng tiền cho nhà xe</t>
-  </si>
-  <si>
-    <t>27 nguyễn hữu thọ (sunrise city toà X1) phường Tân Hưng</t>
+    <t>KIM LIÊN</t>
+  </si>
+  <si>
+    <t>25/17/11 CỬU LONG PHƯỜNG 2</t>
+  </si>
+  <si>
+    <t>06-05-2026</t>
+  </si>
+  <si>
+    <t>Su Anh</t>
+  </si>
+  <si>
+    <t>22/40 Yên Thế, P2</t>
+  </si>
+  <si>
+    <t>TEQUILA THAO VY</t>
+  </si>
+  <si>
+    <t>426 nơ trang long</t>
+  </si>
+  <si>
+    <t>TOM AG</t>
+  </si>
+  <si>
+    <t>12 HỒ VĂN HUÊ PHƯỜNG 9</t>
+  </si>
+  <si>
+    <t>Tường Vi</t>
+  </si>
+  <si>
+    <t>HD018651</t>
+  </si>
+  <si>
+    <t>325 phan xích long</t>
+  </si>
+  <si>
+    <t>C Phước - fb Yến Nguyễn</t>
+  </si>
+  <si>
+    <t>HD018741</t>
+  </si>
+  <si>
+    <t>Block C 685 Âu Cơ, Chung Cư Oriental Plaza</t>
+  </si>
+  <si>
+    <t>AT 06-05</t>
+  </si>
+  <si>
+    <t>Phạm Vui</t>
+  </si>
+  <si>
+    <t>HD018823</t>
+  </si>
+  <si>
+    <t>508/16 trường chinh p13</t>
+  </si>
+  <si>
+    <t>Chi Kim</t>
+  </si>
+  <si>
+    <t>HD018829</t>
+  </si>
+  <si>
+    <t>68A trung mỹ tây 3, phường trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Tâm Như</t>
+  </si>
+  <si>
+    <t>HD018669</t>
+  </si>
+  <si>
+    <t>33 Võ Văn Ngân, P.Linh Chiểu</t>
+  </si>
+  <si>
+    <t>Tăng Ánh Hồng</t>
+  </si>
+  <si>
+    <t>HD018739</t>
+  </si>
+  <si>
+    <t>41a phú định p16</t>
+  </si>
+  <si>
+    <t>Trúc Ly</t>
+  </si>
+  <si>
+    <t>HD018824</t>
+  </si>
+  <si>
+    <t>280 Bình Trị Đông, Phường Bình Trị Đông</t>
+  </si>
+  <si>
+    <t>Fb: Vân Nhung</t>
+  </si>
+  <si>
+    <t>HD018780</t>
+  </si>
+  <si>
+    <t>Cty Thế Long Express 27/5 quách văn tuấn, F12</t>
+  </si>
+  <si>
+    <t>thaoquyen tran</t>
+  </si>
+  <si>
+    <t>HD018784</t>
+  </si>
+  <si>
+    <t>21/41 bình lợi p13</t>
+  </si>
+  <si>
+    <t>Jasploy9989 (inst slideincloset)</t>
+  </si>
+  <si>
+    <t>HD018695</t>
+  </si>
+  <si>
+    <t>275/14B1 Đặng Nguyên Cẩn, Phường Phú Lâm (phường 14 cũ)</t>
+  </si>
+  <si>
+    <t>Lê Thảo</t>
+  </si>
+  <si>
+    <t>HD017759</t>
+  </si>
+  <si>
+    <t>3 Đặng Dung, P Tân Định</t>
+  </si>
+  <si>
+    <t>Hoàng Nhung</t>
+  </si>
+  <si>
+    <t>HD018652</t>
+  </si>
+  <si>
+    <t>Chung cư Sai Gon Avenue - Đường số 11, khu phố 4, phường Tam Bình</t>
+  </si>
+  <si>
+    <t>Ánh Tuyết</t>
+  </si>
+  <si>
+    <t>HD018620</t>
+  </si>
+  <si>
+    <t>23 lộc hưng p6</t>
+  </si>
+  <si>
+    <t>Hoàng Thúy Triều</t>
+  </si>
+  <si>
+    <t>HD018807</t>
+  </si>
+  <si>
+    <t>477 19 nguyễn văn công p3</t>
+  </si>
+  <si>
+    <t>Michelle Nguyen (Tu Anh)</t>
+  </si>
+  <si>
+    <t>HD018799</t>
+  </si>
+  <si>
+    <t>19 Yên Thế p.2</t>
+  </si>
+  <si>
+    <t>Charii ( inst chari_importshop )-BN2441</t>
+  </si>
+  <si>
+    <t>HD018456</t>
+  </si>
+  <si>
+    <t>163 Trương Thị Hoa, phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Tên dinh - fb NG Eric 0đ</t>
+  </si>
+  <si>
+    <t>HD018721</t>
+  </si>
+  <si>
+    <t>215 tên lửa, bình trị đông b</t>
+  </si>
+  <si>
+    <t>Phương Như Tiết</t>
+  </si>
+  <si>
+    <t>HD018610</t>
+  </si>
+  <si>
+    <t>8 đường 19 phường Bình Trị Đông B</t>
+  </si>
+  <si>
+    <t>Gia Linh</t>
+  </si>
+  <si>
+    <t>HD018601</t>
+  </si>
+  <si>
+    <t>100 đinh văn ước ấp5 xã hưng long</t>
+  </si>
+  <si>
+    <t>Thiên Trang</t>
+  </si>
+  <si>
+    <t>HD018668</t>
+  </si>
+  <si>
+    <t>221 trần bình trọng p2</t>
+  </si>
+  <si>
+    <t>Nam Diep Hung Tue</t>
+  </si>
+  <si>
+    <t>HD018802</t>
+  </si>
+  <si>
+    <t>Chung cư Sơn Kỳ 2 số 37 đường DC 13 p Tây Thạnh</t>
+  </si>
+  <si>
+    <t>BN182 miki chouchou Fb</t>
+  </si>
+  <si>
+    <t>HD018603</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Phượng Nhi</t>
+  </si>
+  <si>
+    <t>HD018622</t>
+  </si>
+  <si>
+    <t>35 đặng thị nhu phường Nguyễn thái bình</t>
+  </si>
+  <si>
+    <t>Lý Ngọc Khuyên ( 1805) fb Jessy Dang</t>
+  </si>
+  <si>
+    <t>HD018774</t>
+  </si>
+  <si>
+    <t>Toà nhà Bảy Hiền : 9 Phạm Phu Thử, nay phường Bảy Hiền (phuong 11 cũ)</t>
+  </si>
+  <si>
+    <t>Quỳnh Hương</t>
+  </si>
+  <si>
+    <t>HD018593</t>
+  </si>
+  <si>
+    <t>Saigon Royal Residence, Nguyễn Trường Tộ, phường 13</t>
+  </si>
+  <si>
+    <t>Huỳnh Thị Thúy Kiều</t>
+  </si>
+  <si>
+    <t>HD018671</t>
+  </si>
+  <si>
+    <t>Chung cư zentower 34/1 ql1 phường thới an</t>
+  </si>
+  <si>
+    <t>Macie Nguyen</t>
+  </si>
+  <si>
+    <t>HD018621</t>
+  </si>
+  <si>
+    <t>91 Phạm Văn Hai, f3</t>
+  </si>
+  <si>
+    <t>Trân Hoàng Kỳ Châu</t>
+  </si>
+  <si>
+    <t>HD018517</t>
+  </si>
+  <si>
+    <t>Công ty TNHH GỐM sứ Kim Trúc, khu công nghiệp Tân Bình, đường số 3 lô 4, phường Tây Thạnh</t>
+  </si>
+  <si>
+    <t>at 06-05</t>
   </si>
 </sst>
 </file>
@@ -6603,13 +6890,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="F3" s="18">
         <v>7</v>
@@ -6621,17 +6908,17 @@
         <v>30</v>
       </c>
       <c r="I3" s="18">
-        <f t="shared" ref="I3:I55" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>0</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>126</v>
@@ -6649,13 +6936,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="F4" s="16">
         <v>6</v>
@@ -6671,13 +6958,13 @@
         <v>890</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
@@ -6693,13 +6980,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="F5" s="16">
         <v>7</v>
@@ -6715,13 +7002,13 @@
         <v>820</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
@@ -6737,13 +7024,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="F6" s="16">
         <v>12</v>
@@ -6759,13 +7046,13 @@
         <v>640</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -6781,13 +7068,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>139</v>
@@ -6803,13 +7090,13 @@
         <v>1480</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -6825,13 +7112,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="F8" s="16">
         <v>8</v>
@@ -6847,13 +7134,13 @@
         <v>660</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -6869,13 +7156,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>95</v>
@@ -6891,13 +7178,13 @@
         <v>1320</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -6913,13 +7200,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>349</v>
+        <v>312</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>350</v>
+        <v>313</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>26</v>
@@ -6935,13 +7222,13 @@
         <v>820</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
@@ -6957,13 +7244,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>26</v>
@@ -6979,13 +7266,13 @@
         <v>800</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
@@ -7001,13 +7288,13 @@
         <v>17</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>373</v>
+        <v>318</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>374</v>
+        <v>319</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>375</v>
+        <v>320</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>46</v>
@@ -7023,13 +7310,13 @@
         <v>-25</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -7045,13 +7332,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>376</v>
+        <v>321</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>377</v>
+        <v>322</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>378</v>
+        <v>323</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>26</v>
@@ -7067,13 +7354,13 @@
         <v>750</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
@@ -7089,13 +7376,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>382</v>
+        <v>325</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="F14" s="16">
         <v>8</v>
@@ -7111,13 +7398,13 @@
         <v>710</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K14" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
@@ -7133,13 +7420,13 @@
         <v>17</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>388</v>
+        <v>328</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>389</v>
+        <v>329</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>95</v>
@@ -7155,13 +7442,13 @@
         <v>730</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K15" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
@@ -7180,7 +7467,7 @@
         <v>65</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>67</v>
@@ -7199,13 +7486,13 @@
         <v>740</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
@@ -7221,13 +7508,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>401</v>
+        <v>331</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>139</v>
@@ -7243,13 +7530,13 @@
         <v>700</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
@@ -7265,13 +7552,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>419</v>
+        <v>334</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>420</v>
+        <v>335</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>421</v>
+        <v>336</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>26</v>
@@ -7287,13 +7574,13 @@
         <v>-30</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
@@ -7309,13 +7596,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>429</v>
+        <v>337</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>430</v>
+        <v>338</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>431</v>
+        <v>339</v>
       </c>
       <c r="F19" s="16">
         <v>8</v>
@@ -7331,13 +7618,13 @@
         <v>660</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
@@ -7355,11 +7642,11 @@
         <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
-        <v>436</v>
+        <v>341</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>26</v>
@@ -7375,13 +7662,13 @@
         <v>-35</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>21</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -7397,13 +7684,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>391</v>
+        <v>343</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F21" s="18">
         <v>2</v>
@@ -7425,10 +7712,10 @@
         <v>21</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
@@ -7443,13 +7730,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F22" s="18">
         <v>2</v>
@@ -7471,10 +7758,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
@@ -7489,13 +7776,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="F23" s="16">
         <v>2</v>
@@ -7517,7 +7804,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -7533,13 +7820,13 @@
         <v>17</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>85</v>
@@ -7561,7 +7848,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
@@ -7577,13 +7864,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="F25" s="16">
         <v>2</v>
@@ -7605,7 +7892,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M25" s="20" t="s">
         <v>167</v>
@@ -7623,13 +7910,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>413</v>
+        <v>356</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>414</v>
+        <v>357</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>415</v>
+        <v>358</v>
       </c>
       <c r="F26" s="16">
         <v>12</v>
@@ -7651,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
@@ -7667,13 +7954,13 @@
         <v>17</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>416</v>
+        <v>359</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>417</v>
+        <v>360</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>418</v>
+        <v>361</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>85</v>
@@ -7695,7 +7982,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M27" s="17" t="s">
         <v>126</v>
@@ -7713,13 +8000,13 @@
         <v>17</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="F28" s="16">
         <v>12</v>
@@ -7741,7 +8028,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
@@ -7757,13 +8044,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>432</v>
+        <v>365</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>433</v>
+        <v>366</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>434</v>
+        <v>367</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>77</v>
@@ -7785,7 +8072,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
@@ -7803,11 +8090,11 @@
         <v>17</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>439</v>
+        <v>368</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="15" t="s">
-        <v>440</v>
+        <v>369</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>77</v>
@@ -7829,7 +8116,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -7847,11 +8134,11 @@
         <v>17</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>441</v>
+        <v>370</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15" t="s">
-        <v>442</v>
+        <v>371</v>
       </c>
       <c r="F31" s="15" t="s">
         <v>77</v>
@@ -7873,7 +8160,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
@@ -7891,11 +8178,11 @@
         <v>17</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>443</v>
+        <v>372</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="15" t="s">
-        <v>444</v>
+        <v>373</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>95</v>
@@ -7917,7 +8204,7 @@
         <v>21</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
@@ -7933,13 +8220,13 @@
         <v>17</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="F33" s="16">
         <v>3</v>
@@ -7961,10 +8248,10 @@
         <v>21</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
@@ -7979,13 +8266,13 @@
         <v>17</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>300</v>
+        <v>378</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="F34" s="16">
         <v>3</v>
@@ -8007,10 +8294,10 @@
         <v>21</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M34" s="20" t="s">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="N34" s="15"/>
       <c r="O34" s="15"/>
@@ -8025,13 +8312,13 @@
         <v>17</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>308</v>
+        <v>379</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>309</v>
+        <v>380</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>310</v>
+        <v>381</v>
       </c>
       <c r="F35" s="16">
         <v>4</v>
@@ -8043,7 +8330,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
         <v>510</v>
       </c>
       <c r="J35" s="15" t="s">
@@ -8053,7 +8340,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
@@ -8069,13 +8356,13 @@
         <v>17</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>315</v>
+        <v>383</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>449</v>
+        <v>384</v>
       </c>
       <c r="F36" s="16">
         <v>7</v>
@@ -8087,7 +8374,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J36" s="15" t="s">
@@ -8097,7 +8384,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -8113,13 +8400,13 @@
         <v>17</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>319</v>
+        <v>385</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>320</v>
+        <v>386</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>321</v>
+        <v>387</v>
       </c>
       <c r="F37" s="16">
         <v>10</v>
@@ -8131,7 +8418,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2590</v>
       </c>
       <c r="J37" s="15" t="s">
@@ -8141,7 +8428,7 @@
         <v>21</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M37" s="20" t="s">
         <v>167</v>
@@ -8159,13 +8446,13 @@
         <v>17</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>139</v>
@@ -8177,7 +8464,7 @@
         <v>35</v>
       </c>
       <c r="I38" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>670</v>
       </c>
       <c r="J38" s="15" t="s">
@@ -8187,7 +8474,7 @@
         <v>21</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
@@ -8203,13 +8490,13 @@
         <v>17</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>328</v>
+        <v>391</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>95</v>
@@ -8221,7 +8508,7 @@
         <v>30</v>
       </c>
       <c r="I39" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2830</v>
       </c>
       <c r="J39" s="15" t="s">
@@ -8231,7 +8518,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M39" s="20" t="s">
         <v>167</v>
@@ -8249,13 +8536,13 @@
         <v>17</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="F40" s="16">
         <v>4</v>
@@ -8267,7 +8554,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1140</v>
       </c>
       <c r="J40" s="15" t="s">
@@ -8277,7 +8564,7 @@
         <v>21</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
@@ -8293,13 +8580,13 @@
         <v>17</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="F41" s="16">
         <v>7</v>
@@ -8311,7 +8598,7 @@
         <v>30</v>
       </c>
       <c r="I41" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1320</v>
       </c>
       <c r="J41" s="15" t="s">
@@ -8321,7 +8608,7 @@
         <v>21</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
@@ -8337,13 +8624,13 @@
         <v>17</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>134</v>
@@ -8355,7 +8642,7 @@
         <v>35</v>
       </c>
       <c r="I42" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="J42" s="15" t="s">
@@ -8365,7 +8652,7 @@
         <v>21</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
@@ -8381,16 +8668,16 @@
         <v>17</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="G43" s="16">
         <v>660</v>
@@ -8399,7 +8686,7 @@
         <v>20</v>
       </c>
       <c r="I43" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="J43" s="15" t="s">
@@ -8409,7 +8696,7 @@
         <v>21</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
@@ -8425,13 +8712,13 @@
         <v>17</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="F44" s="16">
         <v>8</v>
@@ -8443,7 +8730,7 @@
         <v>30</v>
       </c>
       <c r="I44" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
       <c r="J44" s="15" t="s">
@@ -8453,7 +8740,7 @@
         <v>21</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
@@ -8472,10 +8759,10 @@
         <v>131</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>134</v>
@@ -8487,7 +8774,7 @@
         <v>35</v>
       </c>
       <c r="I45" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J45" s="15" t="s">
@@ -8497,7 +8784,7 @@
         <v>21</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M45" s="15"/>
       <c r="N45" s="15"/>
@@ -8513,13 +8800,13 @@
         <v>17</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="F46" s="16">
         <v>5</v>
@@ -8531,7 +8818,7 @@
         <v>30</v>
       </c>
       <c r="I46" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2090</v>
       </c>
       <c r="J46" s="15" t="s">
@@ -8541,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M46" s="20" t="s">
         <v>167</v>
@@ -8559,13 +8846,13 @@
         <v>17</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="F47" s="16">
         <v>7</v>
@@ -8577,7 +8864,7 @@
         <v>30</v>
       </c>
       <c r="I47" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J47" s="15" t="s">
@@ -8587,7 +8874,7 @@
         <v>21</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
@@ -8603,13 +8890,13 @@
         <v>17</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="F48" s="16">
         <v>1</v>
@@ -8621,7 +8908,7 @@
         <v>25</v>
       </c>
       <c r="I48" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>510</v>
       </c>
       <c r="J48" s="15" t="s">
@@ -8631,7 +8918,7 @@
         <v>21</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
@@ -8647,13 +8934,13 @@
         <v>17</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="F49" s="16">
         <v>1</v>
@@ -8665,7 +8952,7 @@
         <v>25</v>
       </c>
       <c r="I49" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-205</v>
       </c>
       <c r="J49" s="15" t="s">
@@ -8675,10 +8962,10 @@
         <v>21</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M49" s="20" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="N49" s="15"/>
       <c r="O49" s="15"/>
@@ -8693,13 +8980,13 @@
         <v>17</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="F50" s="16">
         <v>4</v>
@@ -8711,7 +8998,7 @@
         <v>25</v>
       </c>
       <c r="I50" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1330</v>
       </c>
       <c r="J50" s="15" t="s">
@@ -8721,7 +9008,7 @@
         <v>21</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
@@ -8737,13 +9024,13 @@
         <v>17</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="F51" s="16">
         <v>7</v>
@@ -8755,7 +9042,7 @@
         <v>30</v>
       </c>
       <c r="I51" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1860</v>
       </c>
       <c r="J51" s="15" t="s">
@@ -8765,7 +9052,7 @@
         <v>21</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
@@ -8784,7 +9071,7 @@
         <v>171</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>173</v>
@@ -8799,7 +9086,7 @@
         <v>30</v>
       </c>
       <c r="I52" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J52" s="17" t="s">
@@ -8809,7 +9096,7 @@
         <v>21</v>
       </c>
       <c r="L52" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M52" s="17" t="s">
         <v>126</v>
@@ -8827,13 +9114,13 @@
         <v>17</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F53" s="16">
         <v>10</v>
@@ -8845,7 +9132,7 @@
         <v>25</v>
       </c>
       <c r="I53" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J53" s="15" t="s">
@@ -8855,7 +9142,7 @@
         <v>21</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
@@ -8873,11 +9160,11 @@
         <v>17</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>95</v>
@@ -8889,7 +9176,7 @@
         <v>30</v>
       </c>
       <c r="I54" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>720</v>
       </c>
       <c r="J54" s="15" t="s">
@@ -8899,7 +9186,7 @@
         <v>21</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
@@ -8917,11 +9204,11 @@
         <v>17</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="15" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="F55" s="16">
         <v>1</v>
@@ -8933,7 +9220,7 @@
         <v>30</v>
       </c>
       <c r="I55" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J55" s="15" t="s">
@@ -8943,7 +9230,7 @@
         <v>21</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
@@ -8959,47 +9246,47 @@
         <v>47</v>
       </c>
       <c r="G57" s="1">
-        <f t="shared" ref="G57:Q57" si="1">SUBTOTAL(9,G3:G55)</f>
+        <f t="shared" ref="G57:Q57" si="2">SUBTOTAL(9,G3:G55)</f>
         <v>39405</v>
       </c>
       <c r="H57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1515</v>
       </c>
       <c r="I57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>37890</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
     </row>
@@ -9039,7 +9326,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>195</v>
@@ -9099,7 +9386,7 @@
         <v>22</v>
       </c>
       <c r="O61" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="P61">
         <f>L73</f>
@@ -9151,7 +9438,7 @@
       </c>
       <c r="P63">
         <f>-C67</f>
-        <v>-37890</v>
+        <v>-37860</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -9168,14 +9455,16 @@
       </c>
       <c r="P64" s="4">
         <f>SUBTOTAL(9,P60:P63)</f>
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B65" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="C65" s="25"/>
+      <c r="C65" s="25">
+        <v>-30</v>
+      </c>
       <c r="D65" s="25"/>
       <c r="L65" s="13">
         <f>SUBTOTAL(9,L60:L64)</f>
@@ -9192,14 +9481,14 @@
       </c>
       <c r="C67" s="26">
         <f>C63+C64+C65</f>
-        <v>37890</v>
+        <v>37860</v>
       </c>
       <c r="D67" s="26"/>
       <c r="E67" s="1" t="s">
         <v>211</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="L67" s="11" t="s">
         <v>193</v>
@@ -9330,7 +9619,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A2:P55" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P55">
       <sortCondition ref="J2:J55"/>
     </sortState>
@@ -9351,6 +9640,1892 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A2:Q60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="87" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="16">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <v>25</v>
+      </c>
+      <c r="I3" s="16">
+        <f>G3-H3</f>
+        <v>-25</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="F4" s="16">
+        <v>12</v>
+      </c>
+      <c r="G4" s="16">
+        <v>400</v>
+      </c>
+      <c r="H4" s="16">
+        <v>30</v>
+      </c>
+      <c r="I4" s="16">
+        <f>G4-H4</f>
+        <v>370</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F5" s="16">
+        <v>8</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1060</v>
+      </c>
+      <c r="H5" s="16">
+        <v>30</v>
+      </c>
+      <c r="I5" s="16">
+        <f>G5-H5</f>
+        <v>1030</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="16">
+        <v>820</v>
+      </c>
+      <c r="H6" s="16">
+        <v>30</v>
+      </c>
+      <c r="I6" s="16">
+        <f>G6-H6</f>
+        <v>790</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F7" s="16">
+        <v>6</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <v>25</v>
+      </c>
+      <c r="I7" s="16">
+        <f>G7-H7</f>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="16">
+        <v>890</v>
+      </c>
+      <c r="H8" s="16">
+        <v>30</v>
+      </c>
+      <c r="I8" s="16">
+        <f>G8-H8</f>
+        <v>860</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="16">
+        <v>850</v>
+      </c>
+      <c r="H9" s="16">
+        <v>30</v>
+      </c>
+      <c r="I9" s="16">
+        <f>G9-H9</f>
+        <v>820</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="16">
+        <v>855</v>
+      </c>
+      <c r="H10" s="16">
+        <v>35</v>
+      </c>
+      <c r="I10" s="16">
+        <f>G10-H10</f>
+        <v>820</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="16">
+        <v>1175</v>
+      </c>
+      <c r="H11" s="16">
+        <v>25</v>
+      </c>
+      <c r="I11" s="16">
+        <f>G11-H11</f>
+        <v>1150</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>530</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="16">
+        <v>715</v>
+      </c>
+      <c r="H12" s="16">
+        <v>25</v>
+      </c>
+      <c r="I12" s="16">
+        <f>G12-H12</f>
+        <v>690</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="F13" s="16">
+        <v>12</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1150</v>
+      </c>
+      <c r="H13" s="16">
+        <v>30</v>
+      </c>
+      <c r="I13" s="16">
+        <f>G13-H13</f>
+        <v>1120</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="16">
+        <v>25</v>
+      </c>
+      <c r="I14" s="16">
+        <f>G14-H14</f>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>25</v>
+      </c>
+      <c r="I15" s="18">
+        <f>G15-H15</f>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="16">
+        <v>985</v>
+      </c>
+      <c r="H16" s="16">
+        <v>25</v>
+      </c>
+      <c r="I16" s="16">
+        <f>G16-H16</f>
+        <v>960</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="16">
+        <v>560</v>
+      </c>
+      <c r="H17" s="16">
+        <v>30</v>
+      </c>
+      <c r="I17" s="16">
+        <f>G17-H17</f>
+        <v>530</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="16">
+        <v>815</v>
+      </c>
+      <c r="H18" s="16">
+        <v>25</v>
+      </c>
+      <c r="I18" s="16">
+        <f>G18-H18</f>
+        <v>790</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="16">
+        <v>1140</v>
+      </c>
+      <c r="H19" s="16">
+        <v>20</v>
+      </c>
+      <c r="I19" s="16">
+        <f>G19-H19</f>
+        <v>1120</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="16">
+        <v>410</v>
+      </c>
+      <c r="H20" s="16">
+        <v>30</v>
+      </c>
+      <c r="I20" s="16">
+        <f>G20-H20</f>
+        <v>380</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>25</v>
+      </c>
+      <c r="I21" s="16">
+        <f>G21-H21</f>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="F22" s="16">
+        <v>12</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <v>30</v>
+      </c>
+      <c r="I22" s="16">
+        <f>G22-H22</f>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="F23" s="16">
+        <v>12</v>
+      </c>
+      <c r="G23" s="16">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16">
+        <v>30</v>
+      </c>
+      <c r="I23" s="16">
+        <f>G23-H23</f>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="16">
+        <v>0</v>
+      </c>
+      <c r="H24" s="16">
+        <v>30</v>
+      </c>
+      <c r="I24" s="16">
+        <f>G24-H24</f>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="16">
+        <v>0</v>
+      </c>
+      <c r="H25" s="16">
+        <v>30</v>
+      </c>
+      <c r="I25" s="16">
+        <f>G25-H25</f>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G26" s="16">
+        <v>25</v>
+      </c>
+      <c r="H26" s="16">
+        <v>25</v>
+      </c>
+      <c r="I26" s="16">
+        <f>G26-H26</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G27" s="16">
+        <v>4860</v>
+      </c>
+      <c r="H27" s="16">
+        <v>30</v>
+      </c>
+      <c r="I27" s="16">
+        <f>G27-H27</f>
+        <v>4830</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="F28" s="16">
+        <v>1</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <v>25</v>
+      </c>
+      <c r="I28" s="16">
+        <f>G28-H28</f>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="16">
+        <v>795</v>
+      </c>
+      <c r="H29" s="16">
+        <v>25</v>
+      </c>
+      <c r="I29" s="16">
+        <f>G29-H29</f>
+        <v>770</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0</v>
+      </c>
+      <c r="H30" s="16">
+        <v>25</v>
+      </c>
+      <c r="I30" s="16">
+        <f>G30-H30</f>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="F31" s="18">
+        <v>5</v>
+      </c>
+      <c r="G31" s="18">
+        <v>25</v>
+      </c>
+      <c r="H31" s="18">
+        <v>25</v>
+      </c>
+      <c r="I31" s="18">
+        <f>G31-H31</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="F32" s="16">
+        <v>1</v>
+      </c>
+      <c r="G32" s="16">
+        <v>1475</v>
+      </c>
+      <c r="H32" s="16">
+        <v>25</v>
+      </c>
+      <c r="I32" s="16">
+        <f>G32-H32</f>
+        <v>1450</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="F33" s="16">
+        <v>4</v>
+      </c>
+      <c r="G33" s="16">
+        <v>825</v>
+      </c>
+      <c r="H33" s="16">
+        <v>25</v>
+      </c>
+      <c r="I33" s="16">
+        <f>G33-H33</f>
+        <v>800</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="16">
+        <v>3370</v>
+      </c>
+      <c r="H34" s="16">
+        <v>30</v>
+      </c>
+      <c r="I34" s="16">
+        <f>G34-H34</f>
+        <v>3340</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D36" s="1">
+        <f>COUNTA(D3:D34)</f>
+        <v>28</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" ref="G36:Q36" si="0">SUBTOTAL(9,G3:G34)</f>
+        <v>23200</v>
+      </c>
+      <c r="H36" s="1">
+        <f t="shared" si="0"/>
+        <v>875</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="0"/>
+        <v>22325</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <f>-6*17</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38">
+        <f>-5*25</f>
+        <v>-125</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>452</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="28">
+        <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+        <v>22325</v>
+      </c>
+      <c r="D39" s="28"/>
+      <c r="E39" s="3">
+        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K39" t="s">
+        <v>197</v>
+      </c>
+      <c r="L39">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$38)</f>
+        <v>11375</v>
+      </c>
+      <c r="M39">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+      <c r="O39" t="s">
+        <v>135</v>
+      </c>
+      <c r="P39">
+        <f>L44</f>
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="29">
+        <v>0</v>
+      </c>
+      <c r="D40" s="29"/>
+      <c r="K40" t="s">
+        <v>200</v>
+      </c>
+      <c r="L40">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$38)+M40*5</f>
+        <v>-240</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+      <c r="O40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40">
+        <f>L52</f>
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="29">
+        <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="29"/>
+      <c r="E41" s="2">
+        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>202</v>
+      </c>
+      <c r="O41" t="s">
+        <v>544</v>
+      </c>
+      <c r="P41">
+        <f>L60</f>
+        <v>7658</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="27">
+        <f>SUBTOTAL(9,C39:C41)</f>
+        <v>22325</v>
+      </c>
+      <c r="D42" s="27"/>
+      <c r="E42">
+        <f>E39</f>
+        <v>32</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="O42" t="s">
+        <v>207</v>
+      </c>
+      <c r="P42">
+        <f>-C46</f>
+        <v>-22325</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="K43" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P43" s="4">
+        <f>SUBTOTAL(9,P39:P42)</f>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="L44" s="13">
+        <f>SUBTOTAL(9,L39:L43)</f>
+        <v>11135</v>
+      </c>
+      <c r="M44" s="13">
+        <f>M39</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="26">
+        <f>C42+C43+C44</f>
+        <v>22325</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>197</v>
+      </c>
+      <c r="L47">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$46)</f>
+        <v>3910</v>
+      </c>
+      <c r="M47">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>200</v>
+      </c>
+      <c r="L48">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$46)+M48*5</f>
+        <v>-195</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>202</v>
+      </c>
+      <c r="L49">
+        <f>-M49*2</f>
+        <v>-64</v>
+      </c>
+      <c r="M49">
+        <f>E42-(COUNTIFS(M$3:M$34,"*gộp*")/2)-COUNTIFS(M$3:M$34,"*đơn trả*")-COUNTIFS(M$3:M$34,"*hàng tỉnh*")</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L52" s="13">
+        <f>SUBTOTAL(9,L47:L51)</f>
+        <v>3651</v>
+      </c>
+      <c r="M52" s="13">
+        <f>M47</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" t="s">
+        <v>197</v>
+      </c>
+      <c r="L55">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$54)</f>
+        <v>7915</v>
+      </c>
+      <c r="M55">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>200</v>
+      </c>
+      <c r="L56">
+        <f>SUM(H37:H39)</f>
+        <v>-257</v>
+      </c>
+      <c r="M56">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L60" s="13">
+        <f>SUBTOTAL(9,L55:L59)</f>
+        <v>7658</v>
+      </c>
+      <c r="M60" s="13">
+        <f>M55</f>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P34">
+      <sortCondition ref="J2:J34"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -9369,7 +11544,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>289</v>
+        <v>440</v>
       </c>
       <c r="B1" s="5">
         <v>2026</v>
@@ -9377,19 +11552,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>290</v>
+        <v>441</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>291</v>
+        <v>442</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>292</v>
+        <v>443</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>293</v>
+        <v>444</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -9418,11 +11593,11 @@
         <v>46144</v>
       </c>
       <c r="B4" s="8">
-        <f t="shared" ref="B4:B28" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
+        <f t="shared" ref="B4:B27" ca="1" si="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"dd-mm")&amp;"'!L3:L200"),TEXT(A4,"dd-mm")&amp;"-"&amp;B$1),0)</f>
         <v>0</v>
       </c>
       <c r="C4" s="8">
-        <f t="shared" ref="C4:C28" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
+        <f t="shared" ref="C4:C27" ca="1" si="2">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A4,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
         <v>0</v>
       </c>
       <c r="D4" s="8" cm="1">
@@ -9482,7 +11657,7 @@
       </c>
       <c r="B7" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C7" s="8">
         <f t="shared" ca="1" si="2"/>
@@ -9494,7 +11669,7 @@
       </c>
       <c r="E7" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -9922,11 +12097,11 @@
         <v>46172</v>
       </c>
       <c r="B28" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A28,"dd-mm")&amp;"'!L3:L200"),TEXT(A28,"dd-mm")&amp;"-"&amp;B$1),0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IFERROR(COUNTIF(INDIRECT("'"&amp;TEXT(A28,"DD-MM")&amp;"'!M3:M200"),"*gộp*")/2,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="8" cm="1">
@@ -9940,16 +12115,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="9" t="s">
-        <v>295</v>
+        <v>446</v>
       </c>
       <c r="E29" s="9">
         <f ca="1">SUBTOTAL(9,E4:E28)</f>
-        <v>67</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="9" t="s">
-        <v>296</v>
+        <v>447</v>
       </c>
       <c r="E30" s="9" cm="1">
         <f t="array" ref="E30" ca="1">SUMPRODUCT(
@@ -9961,29 +12136,29 @@
         ),
     0)
 )</f>
-        <v>229</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="9" t="s">
-        <v>297</v>
+        <v>448</v>
       </c>
       <c r="E31" s="9">
         <f ca="1">-E29*2</f>
-        <v>-134</v>
+        <v>-198</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D32" s="9" t="s">
-        <v>298</v>
+        <v>449</v>
       </c>
       <c r="E32" s="9">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>95</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D28">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/data/May/InternalDailyReport.xlsx
+++ b/data/May/InternalDailyReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021BA7CB-0393-4424-BC9D-7C866772DBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE06C03-E240-49EA-BD72-E2B30B518A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="7" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="05-05" sheetId="9" r:id="rId3"/>
     <sheet name="06-05" sheetId="10" r:id="rId4"/>
     <sheet name="07-05" sheetId="11" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId6"/>
+    <sheet name="08-05" sheetId="12" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="19" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01-05'!$A$2:$P$56</definedName>
@@ -26,7 +27,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'05-05'!$A$2:$P$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'06-05'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'07-05'!$A$2:$P$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet1!$A$2:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'08-05'!$A$2:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="735">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -1675,6 +1677,294 @@
     <t>at 06-05</t>
   </si>
   <si>
+    <t>Thuỳ Duyên - fb Elyna Tran</t>
+  </si>
+  <si>
+    <t>HD019033</t>
+  </si>
+  <si>
+    <t>Vinhome Grandpark Be3, Nguyễn Xiển, Long Bình</t>
+  </si>
+  <si>
+    <t>07-05-2026</t>
+  </si>
+  <si>
+    <t>Phương Phạm</t>
+  </si>
+  <si>
+    <t>HD018958</t>
+  </si>
+  <si>
+    <t>Bs16A vinhome grand park long bình</t>
+  </si>
+  <si>
+    <t>Tuyến fb Có Đuôi Gà</t>
+  </si>
+  <si>
+    <t>HD019062</t>
+  </si>
+  <si>
+    <t>7/88, Ik 5-6, bình Hưng hoà B</t>
+  </si>
+  <si>
+    <t>AT 07-05</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng.</t>
+  </si>
+  <si>
+    <t>HD019071</t>
+  </si>
+  <si>
+    <t>155/14 ds 11 bình hưng hoà</t>
+  </si>
+  <si>
+    <t>My Nhung Ly</t>
+  </si>
+  <si>
+    <t>HD019061</t>
+  </si>
+  <si>
+    <t>số 13 đường số 9, P13</t>
+  </si>
+  <si>
+    <t>Chị Phương</t>
+  </si>
+  <si>
+    <t>HD019053</t>
+  </si>
+  <si>
+    <t>984/62 hà huy giáp</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Dung</t>
+  </si>
+  <si>
+    <t>HD019069</t>
+  </si>
+  <si>
+    <t>40/20 trần văn quang p10</t>
+  </si>
+  <si>
+    <t>Thu Phương</t>
+  </si>
+  <si>
+    <t>HD018907</t>
+  </si>
+  <si>
+    <t>96a đg 79 phường tân quy</t>
+  </si>
+  <si>
+    <t>Uyên Phương ( Trân)</t>
+  </si>
+  <si>
+    <t>HD018834</t>
+  </si>
+  <si>
+    <t>31 Nguyễn Văn Linh, phường Tân Thuận Tây</t>
+  </si>
+  <si>
+    <t>Trần Phương Quỳnh</t>
+  </si>
+  <si>
+    <t>HD018973</t>
+  </si>
+  <si>
+    <t>53 nguyễn thị minh khai, p sài gòn tòa nhà avalon</t>
+  </si>
+  <si>
+    <t>VN ( Allie Biiny)</t>
+  </si>
+  <si>
+    <t>HD018858</t>
+  </si>
+  <si>
+    <t>Phương 1 Street/Buildding Name: \450/28Gdương bá trạc(061771181)</t>
+  </si>
+  <si>
+    <t>Kim Hằng</t>
+  </si>
+  <si>
+    <t>HD018939</t>
+  </si>
+  <si>
+    <t>PARK VIEW APARTMENT R4-10-11, Hưng Gia 1,Đ. Số 2, Tân Phong</t>
+  </si>
+  <si>
+    <t>HD018855</t>
+  </si>
+  <si>
+    <t>chung cư the park residence. 12 nguyễn hữu thọ phước kien</t>
+  </si>
+  <si>
+    <t>Ngọc Hân Nghiêm</t>
+  </si>
+  <si>
+    <t>HD018899</t>
+  </si>
+  <si>
+    <t>124 đường số 9 KDC Bình Hưng, Bình Hưng</t>
+  </si>
+  <si>
+    <t>HD018512</t>
+  </si>
+  <si>
+    <t>Thỏ Selina</t>
+  </si>
+  <si>
+    <t>HD019055</t>
+  </si>
+  <si>
+    <t>Tháp S2 - The sun avenue 28 Mai Chí Thọ, P bình trưng</t>
+  </si>
+  <si>
+    <t>ái quyên mai malaysia</t>
+  </si>
+  <si>
+    <t>HD018836</t>
+  </si>
+  <si>
+    <t>22 Tân Thới Nhất 1B, p. Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Trang Lê</t>
+  </si>
+  <si>
+    <t>HD019057</t>
+  </si>
+  <si>
+    <t>8A Sông Thương P2</t>
+  </si>
+  <si>
+    <t>Phạm Thị Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD018909</t>
+  </si>
+  <si>
+    <t>Block B Chung Cư Urban Green, Đường Số 6, Hiệp Bình</t>
+  </si>
+  <si>
+    <t>Thụy Uyên Vũ</t>
+  </si>
+  <si>
+    <t>HD018911</t>
+  </si>
+  <si>
+    <t>Chung cư the manor 2</t>
+  </si>
+  <si>
+    <t>Phương Thúy</t>
+  </si>
+  <si>
+    <t>HD018990</t>
+  </si>
+  <si>
+    <t>33 đường số 5 cát lái</t>
+  </si>
+  <si>
+    <t>HD019025</t>
+  </si>
+  <si>
+    <t>Nguyễn Trang</t>
+  </si>
+  <si>
+    <t>HD018885</t>
+  </si>
+  <si>
+    <t>Chung cư freshca lock b Phường Bình Chiểu</t>
+  </si>
+  <si>
+    <t>Diễm Quỳnh</t>
+  </si>
+  <si>
+    <t>HD019054</t>
+  </si>
+  <si>
+    <t>Masteri thảo điền tháp t3 Thao dien</t>
+  </si>
+  <si>
+    <t>ELLY NGUYỄN - THẮM NGUYÊN</t>
+  </si>
+  <si>
+    <t>HD019058</t>
+  </si>
+  <si>
+    <t>120/3/11 Đăng Thùy Trâm, P13 ( CTY GIA HUY EXPRESS )</t>
+  </si>
+  <si>
+    <t>Lê Thị Quỳnh Yến</t>
+  </si>
+  <si>
+    <t>HD019032</t>
+  </si>
+  <si>
+    <t>82 bạch vân</t>
+  </si>
+  <si>
+    <t>Phương Thảo</t>
+  </si>
+  <si>
+    <t>HD018831</t>
+  </si>
+  <si>
+    <t>504 Nguyễn Tất Thành, phường 18 chung cư Riva Park</t>
+  </si>
+  <si>
+    <t>Huyền</t>
+  </si>
+  <si>
+    <t>HD018987</t>
+  </si>
+  <si>
+    <t>218/10 nam kì khởi nghĩa</t>
+  </si>
+  <si>
+    <t>huyền nguyễn</t>
+  </si>
+  <si>
+    <t>HD016429</t>
+  </si>
+  <si>
+    <t>Trần HUỆ</t>
+  </si>
+  <si>
+    <t>HD018874</t>
+  </si>
+  <si>
+    <t>391 ngô gia tự p2</t>
+  </si>
+  <si>
+    <t>CUS TWO EIGHT EIGHT TWO NINE</t>
+  </si>
+  <si>
+    <t>HD018877</t>
+  </si>
+  <si>
+    <t>270B LÝ THƯỜNG KIỆT KP1 P6</t>
+  </si>
+  <si>
+    <t>hải my fb Bé Hân</t>
+  </si>
+  <si>
+    <t>HD018959</t>
+  </si>
+  <si>
+    <t>31 an bình P6</t>
+  </si>
+  <si>
+    <t>Thanh Thanh Trương</t>
+  </si>
+  <si>
+    <t>HD019041</t>
+  </si>
+  <si>
+    <t>518/24 võ văn kiệt</t>
+  </si>
+  <si>
+    <t>at 07-05</t>
+  </si>
+  <si>
     <t>THÁNG 5</t>
   </si>
   <si>
@@ -1705,292 +1995,286 @@
     <t>Lợi nhuận</t>
   </si>
   <si>
-    <t>Tuyến fb Có Đuôi Gà</t>
-  </si>
-  <si>
-    <t>HD019062</t>
-  </si>
-  <si>
-    <t>7/88, Ik 5-6, bình Hưng hoà B</t>
-  </si>
-  <si>
-    <t>AT 07-05</t>
-  </si>
-  <si>
-    <t>07-05-2026</t>
-  </si>
-  <si>
-    <t>Lê Thị Quỳnh Yến</t>
-  </si>
-  <si>
-    <t>HD019032</t>
-  </si>
-  <si>
-    <t>82 bạch vân</t>
-  </si>
-  <si>
-    <t>Thuỳ Duyên - fb Elyna Tran</t>
-  </si>
-  <si>
-    <t>HD019033</t>
-  </si>
-  <si>
-    <t>Vinhome Grandpark Be3, Nguyễn Xiển, Long Bình</t>
-  </si>
-  <si>
-    <t>Thỏ Selina</t>
-  </si>
-  <si>
-    <t>HD019055</t>
-  </si>
-  <si>
-    <t>Tháp S2 - The sun avenue 28 Mai Chí Thọ, P bình trưng</t>
-  </si>
-  <si>
-    <t>ái quyên mai malaysia</t>
-  </si>
-  <si>
-    <t>HD018836</t>
-  </si>
-  <si>
-    <t>22 Tân Thới Nhất 1B, p. Tân Thới Nhất</t>
-  </si>
-  <si>
-    <t>Phương Thảo</t>
-  </si>
-  <si>
-    <t>HD018831</t>
-  </si>
-  <si>
-    <t>504 Nguyễn Tất Thành, phường 18 chung cư Riva Park</t>
-  </si>
-  <si>
-    <t>Huyền</t>
-  </si>
-  <si>
-    <t>HD018987</t>
-  </si>
-  <si>
-    <t>218/10 nam kì khởi nghĩa</t>
-  </si>
-  <si>
-    <t>Phương Phạm</t>
-  </si>
-  <si>
-    <t>HD018958</t>
-  </si>
-  <si>
-    <t>Bs16A vinhome grand park long bình</t>
-  </si>
-  <si>
-    <t>Trang Lê</t>
-  </si>
-  <si>
-    <t>HD019057</t>
-  </si>
-  <si>
-    <t>8A Sông Thương P2</t>
-  </si>
-  <si>
-    <t>Lê Thị Minh Phượng.</t>
-  </si>
-  <si>
-    <t>HD019071</t>
-  </si>
-  <si>
-    <t>155/14 ds 11 bình hưng hoà</t>
-  </si>
-  <si>
-    <t>Phạm Thị Bảo Trân</t>
-  </si>
-  <si>
-    <t>HD018909</t>
-  </si>
-  <si>
-    <t>Block B Chung Cư Urban Green, Đường Số 6, Hiệp Bình</t>
-  </si>
-  <si>
-    <t>My Nhung Ly</t>
-  </si>
-  <si>
-    <t>HD019061</t>
-  </si>
-  <si>
-    <t>số 13 đường số 9, P13</t>
-  </si>
-  <si>
-    <t>Chị Phương</t>
-  </si>
-  <si>
-    <t>HD019053</t>
-  </si>
-  <si>
-    <t>984/62 hà huy giáp</t>
-  </si>
-  <si>
-    <t>Nguyễn Kim Dung</t>
-  </si>
-  <si>
-    <t>HD019069</t>
-  </si>
-  <si>
-    <t>40/20 trần văn quang p10</t>
-  </si>
-  <si>
-    <t>Thụy Uyên Vũ</t>
-  </si>
-  <si>
-    <t>HD018911</t>
-  </si>
-  <si>
-    <t>Chung cư the manor 2</t>
-  </si>
-  <si>
-    <t>huyền nguyễn</t>
-  </si>
-  <si>
-    <t>HD016429</t>
-  </si>
-  <si>
-    <t>Thu Phương</t>
-  </si>
-  <si>
-    <t>HD018907</t>
-  </si>
-  <si>
-    <t>96a đg 79 phường tân quy</t>
-  </si>
-  <si>
-    <t>Uyên Phương ( Trân)</t>
-  </si>
-  <si>
-    <t>HD018834</t>
-  </si>
-  <si>
-    <t>31 Nguyễn Văn Linh, phường Tân Thuận Tây</t>
-  </si>
-  <si>
-    <t>Trần Phương Quỳnh</t>
-  </si>
-  <si>
-    <t>HD018973</t>
-  </si>
-  <si>
-    <t>53 nguyễn thị minh khai, p sài gòn tòa nhà avalon</t>
-  </si>
-  <si>
-    <t>VN ( Allie Biiny)</t>
-  </si>
-  <si>
-    <t>HD018858</t>
-  </si>
-  <si>
-    <t>Phương 1 Street/Buildding Name: \450/28Gdương bá trạc(061771181)</t>
-  </si>
-  <si>
-    <t>Kim Hằng</t>
-  </si>
-  <si>
-    <t>HD018939</t>
-  </si>
-  <si>
-    <t>PARK VIEW APARTMENT R4-10-11, Hưng Gia 1,Đ. Số 2, Tân Phong</t>
-  </si>
-  <si>
-    <t>HD018855</t>
-  </si>
-  <si>
-    <t>chung cư the park residence. 12 nguyễn hữu thọ phước kien</t>
-  </si>
-  <si>
-    <t>Phương Thúy</t>
-  </si>
-  <si>
-    <t>HD018990</t>
-  </si>
-  <si>
-    <t>33 đường số 5 cát lái</t>
-  </si>
-  <si>
-    <t>Trần HUỆ</t>
-  </si>
-  <si>
-    <t>HD018874</t>
-  </si>
-  <si>
-    <t>391 ngô gia tự p2</t>
-  </si>
-  <si>
-    <t>HD019025</t>
-  </si>
-  <si>
-    <t>Nguyễn Trang</t>
-  </si>
-  <si>
-    <t>HD018885</t>
-  </si>
-  <si>
-    <t>Chung cư freshca lock b Phường Bình Chiểu</t>
-  </si>
-  <si>
-    <t>Diễm Quỳnh</t>
-  </si>
-  <si>
-    <t>HD019054</t>
-  </si>
-  <si>
-    <t>Masteri thảo điền tháp t3 Thao dien</t>
-  </si>
-  <si>
-    <t>ELLY NGUYỄN - THẮM NGUYÊN</t>
-  </si>
-  <si>
-    <t>HD019058</t>
-  </si>
-  <si>
-    <t>120/3/11 Đăng Thùy Trâm, P13 ( CTY GIA HUY EXPRESS )</t>
-  </si>
-  <si>
-    <t>Ngọc Hân Nghiêm</t>
-  </si>
-  <si>
-    <t>HD018899</t>
-  </si>
-  <si>
-    <t>124 đường số 9 KDC Bình Hưng, Bình Hưng</t>
-  </si>
-  <si>
-    <t>HD018512</t>
-  </si>
-  <si>
-    <t>CUS TWO EIGHT EIGHT TWO NINE</t>
-  </si>
-  <si>
-    <t>HD018877</t>
-  </si>
-  <si>
-    <t>270B LÝ THƯỜNG KIỆT KP1 P6</t>
-  </si>
-  <si>
-    <t>hải my fb Bé Hân</t>
-  </si>
-  <si>
-    <t>HD018959</t>
-  </si>
-  <si>
-    <t>31 an bình P6</t>
-  </si>
-  <si>
-    <t>Thanh Thanh Trương</t>
-  </si>
-  <si>
-    <t>HD019041</t>
-  </si>
-  <si>
-    <t>518/24 võ văn kiệt</t>
-  </si>
-  <si>
-    <t>at 07-05</t>
+    <t>08-05-2026</t>
+  </si>
+  <si>
+    <t>VNTH Dịch vụ vận chuyển - NoyNa Thailand Service</t>
+  </si>
+  <si>
+    <t>275/14B1 Đặng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>AT 08-05</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải (Bow)</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Trương Kim Hồng</t>
+  </si>
+  <si>
+    <t>HD019237</t>
+  </si>
+  <si>
+    <t>114/15/14 Phạm Văn Chiêu, P.Thông Tây Hội</t>
+  </si>
+  <si>
+    <t>Thịnh Nguyễn fb Loan Nguyen</t>
+  </si>
+  <si>
+    <t>HD019175</t>
+  </si>
+  <si>
+    <t>20/15 đường số 8 hẻm 20 phường Long Phước</t>
+  </si>
+  <si>
+    <t>Tần Châu Yến Vy</t>
+  </si>
+  <si>
+    <t>HD019113</t>
+  </si>
+  <si>
+    <t>2B Mai Chí Thọ, Enpi, Toà "lạ thường Thủ Thiêm</t>
+  </si>
+  <si>
+    <t>HD019096</t>
+  </si>
+  <si>
+    <t>Nhật Nguyên</t>
+  </si>
+  <si>
+    <t>HD019225</t>
+  </si>
+  <si>
+    <t>Nhà Trọ Mai Anh, Ấp 3, Phước kiển (cuối đường b7)</t>
+  </si>
+  <si>
+    <t>Trân Helen</t>
+  </si>
+  <si>
+    <t>HD019219</t>
+  </si>
+  <si>
+    <t>36/15 Yên Thế, Phường Tân Sơn Hoà, Phường Tân Bình</t>
+  </si>
+  <si>
+    <t>HD019156</t>
+  </si>
+  <si>
+    <t>W3337</t>
+  </si>
+  <si>
+    <t>HD019276</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD019275</t>
+  </si>
+  <si>
+    <t>Hẻm 218, An dương vương, phường 16</t>
+  </si>
+  <si>
+    <t>Thảo Nguyên Thị Nguyễn</t>
+  </si>
+  <si>
+    <t>HD019222</t>
+  </si>
+  <si>
+    <t>40/18 ấp bắc</t>
+  </si>
+  <si>
+    <t>Mi Mi</t>
+  </si>
+  <si>
+    <t>HD018473</t>
+  </si>
+  <si>
+    <t>2 đường 3643 phạm thế hiển p7</t>
+  </si>
+  <si>
+    <t>Tuyến fb Cỏ Đuôi Già</t>
+  </si>
+  <si>
+    <t>HD019271</t>
+  </si>
+  <si>
+    <t>Minh Nguyệt + Lin Xiao</t>
+  </si>
+  <si>
+    <t>HD019184</t>
+  </si>
+  <si>
+    <t>C16 - Lô C1, đg DD5, Phường Đông Hưng Thuận (Sau chợ An Sương)</t>
+  </si>
+  <si>
+    <t>Trần Hạ Mây</t>
+  </si>
+  <si>
+    <t>HD019227</t>
+  </si>
+  <si>
+    <t>Hòm thư A1.11-14, toà Aqua 1, Vinhomes golden river, số 2 Tôn Đức Thắng, phường Bến Nghé</t>
+  </si>
+  <si>
+    <t>Mai Nguyen</t>
+  </si>
+  <si>
+    <t>HD019299</t>
+  </si>
+  <si>
+    <t>272/21D lê văn quới, phường bình trị đông</t>
+  </si>
+  <si>
+    <t>Hà Chi</t>
+  </si>
+  <si>
+    <t>HD014556</t>
+  </si>
+  <si>
+    <t>1400 Đồng Văn Cống, phường Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>Cô Kiều</t>
+  </si>
+  <si>
+    <t>HD019279</t>
+  </si>
+  <si>
+    <t>59/7 điện biên phủ p10</t>
+  </si>
+  <si>
+    <t>Nguyễn Ái My</t>
+  </si>
+  <si>
+    <t>HD019244</t>
+  </si>
+  <si>
+    <t>702/45/31 điện biên phủ phường 13</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Trà My</t>
+  </si>
+  <si>
+    <t>HD019248</t>
+  </si>
+  <si>
+    <t>325/9 bùi minh trực phường 6</t>
+  </si>
+  <si>
+    <t>Mỷ Ý</t>
+  </si>
+  <si>
+    <t>HD019154</t>
+  </si>
+  <si>
+    <t>137 Hoàng Hoa Thám</t>
+  </si>
+  <si>
+    <t>Kim - fb July Phan</t>
+  </si>
+  <si>
+    <t>HD019137</t>
+  </si>
+  <si>
+    <t>86 Lê Thị Riêng p. Bến Thành</t>
+  </si>
+  <si>
+    <t>Thuy An Dao</t>
+  </si>
+  <si>
+    <t>HD019092</t>
+  </si>
+  <si>
+    <t>Sảnh B2 chung cư Emerald phường Sơn Kỳ</t>
+  </si>
+  <si>
+    <t>Trần Thảo Ngân</t>
+  </si>
+  <si>
+    <t>HD019270</t>
+  </si>
+  <si>
+    <t>Ngân 27-19 block G chung cư eco green, đường nguyễn văn linh, phường tân thuận tây</t>
+  </si>
+  <si>
+    <t>Hoàng Lê Dung</t>
+  </si>
+  <si>
+    <t>HD019266</t>
+  </si>
+  <si>
+    <t>27/24/30 điện biên phủ, F. gia định</t>
+  </si>
+  <si>
+    <t>borameyyy 015738168</t>
+  </si>
+  <si>
+    <t>HD019089</t>
+  </si>
+  <si>
+    <t>363-365-367 363 Đi Hung Vương, Phường 9</t>
+  </si>
+  <si>
+    <t>Trần Chi</t>
+  </si>
+  <si>
+    <t>HD019216</t>
+  </si>
+  <si>
+    <t>260 Nguyễn Tiểu La P8</t>
+  </si>
+  <si>
+    <t>HD019293</t>
+  </si>
+  <si>
+    <t>Trúc Anh</t>
+  </si>
+  <si>
+    <t>HD018871</t>
+  </si>
+  <si>
+    <t>99 trần não phường an khánh</t>
+  </si>
+  <si>
+    <t>Thuý Đào</t>
+  </si>
+  <si>
+    <t>HD019309</t>
+  </si>
+  <si>
+    <t>53/34/49 bình lợi, p13</t>
+  </si>
+  <si>
+    <t>HD019277</t>
+  </si>
+  <si>
+    <t>Ngọc Diệp</t>
+  </si>
+  <si>
+    <t>HD019226</t>
+  </si>
+  <si>
+    <t>Ngọc diệp ak neo chung cư akari 77 đại lộ võ văn kiệt p an lạc</t>
+  </si>
+  <si>
+    <t>Phương liên (jun đặng)</t>
+  </si>
+  <si>
+    <t>HD019311</t>
+  </si>
+  <si>
+    <t>241 đông Hưng Thuận 2 phường Tân Hưng</t>
+  </si>
+  <si>
+    <t>at 08-05</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +2409,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2158,6 +2442,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11895,13 +12180,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F3" s="21">
         <v>9</v>
@@ -11913,7 +12198,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I16" si="0">G3-H3</f>
         <v>820</v>
       </c>
       <c r="J3" s="20" t="s">
@@ -11923,7 +12208,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
@@ -11939,13 +12224,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>568</v>
+        <v>539</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>569</v>
+        <v>540</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>570</v>
+        <v>541</v>
       </c>
       <c r="F4" s="21">
         <v>9</v>
@@ -11957,7 +12242,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
       <c r="J4" s="20" t="s">
@@ -11967,7 +12252,7 @@
         <v>21</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -11983,13 +12268,13 @@
         <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>26</v>
@@ -12001,17 +12286,17 @@
         <v>30</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
@@ -12031,13 +12316,13 @@
         <v>17</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>574</v>
+        <v>546</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="F6" s="20" t="s">
         <v>26</v>
@@ -12049,17 +12334,17 @@
         <v>30</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
@@ -12075,13 +12360,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>580</v>
+        <v>549</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="F7" s="21">
         <v>6</v>
@@ -12093,17 +12378,17 @@
         <v>25</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>750</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -12119,13 +12404,13 @@
         <v>17</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="F8" s="21">
         <v>12</v>
@@ -12137,17 +12422,17 @@
         <v>30</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>370</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
@@ -12163,13 +12448,13 @@
         <v>17</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>95</v>
@@ -12181,17 +12466,17 @@
         <v>25</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
@@ -12211,13 +12496,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>594</v>
+        <v>558</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>595</v>
+        <v>559</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>596</v>
+        <v>560</v>
       </c>
       <c r="F10" s="21">
         <v>7</v>
@@ -12229,17 +12514,17 @@
         <v>30</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
@@ -12255,13 +12540,13 @@
         <v>17</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>597</v>
+        <v>561</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>599</v>
+        <v>563</v>
       </c>
       <c r="F11" s="21">
         <v>7</v>
@@ -12273,17 +12558,17 @@
         <v>30</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>450</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
@@ -12299,13 +12584,13 @@
         <v>17</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>600</v>
+        <v>564</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>601</v>
+        <v>565</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>602</v>
+        <v>566</v>
       </c>
       <c r="F12" s="21">
         <v>1</v>
@@ -12317,17 +12602,17 @@
         <v>25</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>1110</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K12" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -12343,13 +12628,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>603</v>
+        <v>567</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>604</v>
+        <v>568</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="F13" s="21">
         <v>8</v>
@@ -12361,17 +12646,17 @@
         <v>30</v>
       </c>
       <c r="I13" s="21">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -12391,13 +12676,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>606</v>
+        <v>570</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>607</v>
+        <v>571</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>608</v>
+        <v>572</v>
       </c>
       <c r="F14" s="21">
         <v>7</v>
@@ -12409,17 +12694,17 @@
         <v>30</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>640</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -12438,10 +12723,10 @@
         <v>131</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>609</v>
+        <v>573</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>610</v>
+        <v>574</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>134</v>
@@ -12453,17 +12738,17 @@
         <v>35</v>
       </c>
       <c r="I15" s="23">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M15" s="22" t="s">
         <v>126</v>
@@ -12481,13 +12766,13 @@
         <v>17</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>627</v>
+        <v>575</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>628</v>
+        <v>576</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>629</v>
+        <v>577</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>139</v>
@@ -12499,17 +12784,17 @@
         <v>35</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M16" s="25" t="s">
         <v>377</v>
@@ -12521,7 +12806,7 @@
         <v>1</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" ref="R16:R17" si="0">H16</f>
+        <f>H16</f>
         <v>35</v>
       </c>
     </row>
@@ -12531,13 +12816,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>627</v>
+        <v>575</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>630</v>
+        <v>578</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>629</v>
+        <v>577</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>139</v>
@@ -12553,13 +12838,13 @@
         <v>0</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M17" s="25" t="s">
         <v>377</v>
@@ -12571,7 +12856,7 @@
         <v>1</v>
       </c>
       <c r="R17" s="15">
-        <f t="shared" si="0"/>
+        <f>H17</f>
         <v>0</v>
       </c>
     </row>
@@ -12581,13 +12866,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="F18" s="21">
         <v>2</v>
@@ -12599,7 +12884,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="21">
-        <f>G18-H18</f>
+        <f t="shared" ref="I18:I36" si="1">G18-H18</f>
         <v>820</v>
       </c>
       <c r="J18" s="20" t="s">
@@ -12609,7 +12894,7 @@
         <v>21</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -12625,13 +12910,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="F19" s="21">
         <v>12</v>
@@ -12643,7 +12928,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -12653,7 +12938,7 @@
         <v>21</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -12673,13 +12958,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>95</v>
@@ -12691,7 +12976,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="1"/>
         <v>2170</v>
       </c>
       <c r="J20" s="20" t="s">
@@ -12701,7 +12986,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M20" s="25" t="s">
         <v>167</v>
@@ -12723,13 +13008,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>81</v>
@@ -12741,7 +13026,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -12751,7 +13036,7 @@
         <v>21</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
@@ -12767,13 +13052,13 @@
         <v>17</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>85</v>
@@ -12785,7 +13070,7 @@
         <v>20</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="1"/>
         <v>-20</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -12795,7 +13080,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M22" s="20"/>
       <c r="N22" s="20"/>
@@ -12815,13 +13100,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="F23" s="21">
         <v>2</v>
@@ -12833,7 +13118,7 @@
         <v>30</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -12843,7 +13128,7 @@
         <v>21</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
@@ -12862,7 +13147,7 @@
         <v>78</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>80</v>
@@ -12877,7 +13162,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="23">
-        <f>G24-H24</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J24" s="22" t="s">
@@ -12887,7 +13172,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M24" s="22" t="s">
         <v>126</v>
@@ -12905,13 +13190,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>81</v>
@@ -12923,7 +13208,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="1"/>
         <v>750</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -12933,7 +13218,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
@@ -12949,13 +13234,13 @@
         <v>17</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="F26" s="21">
         <v>2</v>
@@ -12967,7 +13252,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -12977,7 +13262,7 @@
         <v>21</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
@@ -12993,13 +13278,13 @@
         <v>17</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>85</v>
@@ -13011,7 +13296,7 @@
         <v>20</v>
       </c>
       <c r="I27" s="21">
-        <f>G27-H27</f>
+        <f t="shared" si="1"/>
         <v>-20</v>
       </c>
       <c r="J27" s="20" t="s">
@@ -13021,7 +13306,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
@@ -13059,7 +13344,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -13069,7 +13354,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -13085,13 +13370,13 @@
         <v>17</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>550</v>
+        <v>607</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>551</v>
+        <v>608</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>552</v>
+        <v>609</v>
       </c>
       <c r="F29" s="21">
         <v>5</v>
@@ -13103,7 +13388,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="1"/>
         <v>1150</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -13113,7 +13398,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -13129,13 +13414,13 @@
         <v>17</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>562</v>
+        <v>610</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>563</v>
+        <v>611</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>564</v>
+        <v>612</v>
       </c>
       <c r="F30" s="21">
         <v>4</v>
@@ -13147,7 +13432,7 @@
         <v>25</v>
       </c>
       <c r="I30" s="21">
-        <f>G30-H30</f>
+        <f t="shared" si="1"/>
         <v>740</v>
       </c>
       <c r="J30" s="20" t="s">
@@ -13157,7 +13442,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
@@ -13173,13 +13458,13 @@
         <v>17</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>565</v>
+        <v>613</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>566</v>
+        <v>614</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>567</v>
+        <v>615</v>
       </c>
       <c r="F31" s="21">
         <v>3</v>
@@ -13191,7 +13476,7 @@
         <v>25</v>
       </c>
       <c r="I31" s="21">
-        <f>G31-H31</f>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -13201,7 +13486,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
@@ -13221,10 +13506,10 @@
         <v>17</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>270</v>
@@ -13239,7 +13524,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="21">
-        <f>G32-H32</f>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J32" s="20" t="s">
@@ -13249,7 +13534,7 @@
         <v>21</v>
       </c>
       <c r="L32" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M32" s="20"/>
       <c r="N32" s="20"/>
@@ -13265,13 +13550,13 @@
         <v>17</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="F33" s="21">
         <v>10</v>
@@ -13283,7 +13568,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="21">
-        <f>G33-H33</f>
+        <f t="shared" si="1"/>
         <v>840</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -13293,7 +13578,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M33" s="20"/>
       <c r="N33" s="20"/>
@@ -13309,13 +13594,13 @@
         <v>17</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>95</v>
@@ -13327,7 +13612,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="21">
-        <f>G34-H34</f>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J34" s="20" t="s">
@@ -13337,7 +13622,7 @@
         <v>21</v>
       </c>
       <c r="L34" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M34" s="20"/>
       <c r="N34" s="20"/>
@@ -13347,7 +13632,7 @@
         <v>1</v>
       </c>
       <c r="R34" s="15">
-        <f t="shared" ref="R34:R35" si="1">H34</f>
+        <f>H34</f>
         <v>25</v>
       </c>
     </row>
@@ -13357,13 +13642,13 @@
         <v>17</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="F35" s="21">
         <v>5</v>
@@ -13375,7 +13660,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="21">
-        <f>G35-H35</f>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J35" s="20" t="s">
@@ -13385,7 +13670,7 @@
         <v>21</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M35" s="20"/>
       <c r="N35" s="20"/>
@@ -13395,7 +13680,7 @@
         <v>1</v>
       </c>
       <c r="R35" s="15">
-        <f t="shared" si="1"/>
+        <f>H35</f>
         <v>25</v>
       </c>
     </row>
@@ -13405,13 +13690,13 @@
         <v>17</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="F36" s="21">
         <v>1</v>
@@ -13423,7 +13708,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="21">
-        <f>G36-H36</f>
+        <f t="shared" si="1"/>
         <v>2020</v>
       </c>
       <c r="J36" s="20" t="s">
@@ -13433,7 +13718,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="M36" s="25" t="s">
         <v>167</v>
@@ -13521,7 +13806,7 @@
         <v>-75</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>193</v>
@@ -13535,7 +13820,7 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>195</v>
@@ -13568,7 +13853,7 @@
         <v>12</v>
       </c>
       <c r="O41" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="P41">
         <f>L46</f>
@@ -13895,7 +14180,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P36" xr:uid="{00000000-0009-0000-0000-000005000000}">
+  <autoFilter ref="A2:P36" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P36">
       <sortCondition ref="J2:J36"/>
     </sortState>
@@ -13915,6 +14200,2118 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A2:R64"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="85.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="F3" s="21">
+        <v>6</v>
+      </c>
+      <c r="G3" s="21">
+        <v>0</v>
+      </c>
+      <c r="H3" s="21">
+        <v>30</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>-30</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+      <c r="R3" s="15">
+        <f>H3</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="21">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21">
+        <v>35</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>-35</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+      <c r="R4" s="15">
+        <f>H4</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="F5" s="21">
+        <v>9</v>
+      </c>
+      <c r="G5" s="21">
+        <v>2630</v>
+      </c>
+      <c r="H5" s="21">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>2600</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="15">
+        <f>H5</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>657</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="21">
+        <v>905</v>
+      </c>
+      <c r="H6" s="21">
+        <v>35</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>870</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="F7" s="21">
+        <v>8</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+      <c r="R7" s="15">
+        <f>H7</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="F8" s="21">
+        <v>8</v>
+      </c>
+      <c r="G8" s="21">
+        <v>470</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>440</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+      <c r="R9" s="15">
+        <f>H9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="21">
+        <v>980</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>950</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>696</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="F11" s="21">
+        <v>8</v>
+      </c>
+      <c r="G11" s="21">
+        <v>950</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>920</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>705</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>706</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>707</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="21">
+        <v>895</v>
+      </c>
+      <c r="H12" s="21">
+        <v>25</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>870</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>720</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="23">
+        <v>8</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23">
+        <f>G13-H13</f>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>644</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>641</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="30">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>728</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>729</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>730</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="21">
+        <v>670</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>640</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="21">
+        <v>30</v>
+      </c>
+      <c r="H15" s="21">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="21">
+        <v>565</v>
+      </c>
+      <c r="H16" s="21">
+        <v>25</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>540</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="F17" s="21">
+        <v>2</v>
+      </c>
+      <c r="G17" s="21">
+        <v>1670</v>
+      </c>
+      <c r="H17" s="21">
+        <v>30</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>1640</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="F18" s="21">
+        <v>12</v>
+      </c>
+      <c r="G18" s="21">
+        <v>741</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>711</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="F19" s="21">
+        <v>12</v>
+      </c>
+      <c r="G19" s="21">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>30</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+      <c r="R19" s="15">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="21">
+        <v>805</v>
+      </c>
+      <c r="H20" s="21">
+        <v>25</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>780</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="F21" s="21">
+        <v>12</v>
+      </c>
+      <c r="G21" s="21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+      <c r="R21" s="15">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="F22" s="21">
+        <v>2</v>
+      </c>
+      <c r="G22" s="21">
+        <v>30</v>
+      </c>
+      <c r="H22" s="21">
+        <v>30</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>700</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="21">
+        <v>50</v>
+      </c>
+      <c r="H23" s="21">
+        <v>50</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>711</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>712</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>713</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="21">
+        <v>710</v>
+      </c>
+      <c r="H24" s="21">
+        <v>20</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>690</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>722</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>723</v>
+      </c>
+      <c r="F25" s="21">
+        <v>2</v>
+      </c>
+      <c r="G25" s="21">
+        <v>820</v>
+      </c>
+      <c r="H25" s="21">
+        <v>30</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>790</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>724</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="21">
+        <v>880</v>
+      </c>
+      <c r="H26" s="21">
+        <v>20</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>860</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="21">
+        <v>845</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f>G27-H27</f>
+        <v>820</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>731</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>732</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>733</v>
+      </c>
+      <c r="F28" s="21">
+        <v>12</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21">
+        <v>30</v>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
+        <v>-30</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+      <c r="R28" s="15">
+        <f t="shared" ref="R28:R30" si="0">H28</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="F29" s="21">
+        <v>1</v>
+      </c>
+      <c r="G29" s="21">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21">
+        <v>30</v>
+      </c>
+      <c r="I29" s="21">
+        <f>G29-H29</f>
+        <v>-30</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+      <c r="R29" s="15">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>660</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="21">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>25</v>
+      </c>
+      <c r="I30" s="21">
+        <f>G30-H30</f>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20">
+        <v>1</v>
+      </c>
+      <c r="R30" s="15">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F31" s="21">
+        <v>4</v>
+      </c>
+      <c r="G31" s="21">
+        <v>885</v>
+      </c>
+      <c r="H31" s="21">
+        <v>25</v>
+      </c>
+      <c r="I31" s="21">
+        <f>G31-H31</f>
+        <v>860</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>682</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="F32" s="21">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21">
+        <v>825</v>
+      </c>
+      <c r="H32" s="21">
+        <v>25</v>
+      </c>
+      <c r="I32" s="21">
+        <f>G32-H32</f>
+        <v>800</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="F33" s="21">
+        <v>10</v>
+      </c>
+      <c r="G33" s="21">
+        <v>0</v>
+      </c>
+      <c r="H33" s="21">
+        <v>25</v>
+      </c>
+      <c r="I33" s="21">
+        <f>G33-H33</f>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20">
+        <v>1</v>
+      </c>
+      <c r="R33" s="15">
+        <f>H33</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>693</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>694</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="F34" s="21">
+        <v>10</v>
+      </c>
+      <c r="G34" s="21">
+        <v>815</v>
+      </c>
+      <c r="H34" s="21">
+        <v>25</v>
+      </c>
+      <c r="I34" s="21">
+        <f>G34-H34</f>
+        <v>790</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>702</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>703</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>704</v>
+      </c>
+      <c r="F35" s="23">
+        <v>1</v>
+      </c>
+      <c r="G35" s="23">
+        <v>25</v>
+      </c>
+      <c r="H35" s="23">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <f>G35-H35</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>641</v>
+      </c>
+      <c r="M35" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>708</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>709</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>710</v>
+      </c>
+      <c r="F36" s="21">
+        <v>7</v>
+      </c>
+      <c r="G36" s="21">
+        <v>850</v>
+      </c>
+      <c r="H36" s="21">
+        <v>30</v>
+      </c>
+      <c r="I36" s="21">
+        <f>G36-H36</f>
+        <v>820</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>714</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>715</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>716</v>
+      </c>
+      <c r="F37" s="21">
+        <v>5</v>
+      </c>
+      <c r="G37" s="21">
+        <v>0</v>
+      </c>
+      <c r="H37" s="21">
+        <v>25</v>
+      </c>
+      <c r="I37" s="21">
+        <f>G37-H37</f>
+        <v>-25</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20">
+        <v>1</v>
+      </c>
+      <c r="R37" s="15">
+        <f>H37</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>717</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>718</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="F38" s="21">
+        <v>10</v>
+      </c>
+      <c r="G38" s="21">
+        <v>455</v>
+      </c>
+      <c r="H38" s="21">
+        <v>25</v>
+      </c>
+      <c r="I38" s="21">
+        <f>G38-H38</f>
+        <v>430</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D40" s="6">
+        <f>COUNTA(D3:D38)</f>
+        <v>32</v>
+      </c>
+      <c r="G40" s="6">
+        <f t="shared" ref="G40:Q40" si="1">SUBTOTAL(9,G3:G38)</f>
+        <v>18501</v>
+      </c>
+      <c r="H40" s="6">
+        <f t="shared" si="1"/>
+        <v>1030</v>
+      </c>
+      <c r="I40" s="6">
+        <f t="shared" si="1"/>
+        <v>17471</v>
+      </c>
+      <c r="J40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="6">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H41">
+        <f>-6*17</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H42">
+        <f>-5*25</f>
+        <v>-125</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>641</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" s="4">
+        <f>SUMIFS(I$3:I$38,B$3:B$38,A$42,L$3:L$38,A$43)</f>
+        <v>17471</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="8">
+        <f>SUMIFS(Q$3:Q$38,B$3:B$38,A$42,L$3:L$38,A$43)</f>
+        <v>36</v>
+      </c>
+      <c r="F43" t="s">
+        <v>196</v>
+      </c>
+      <c r="H43">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K43" t="s">
+        <v>197</v>
+      </c>
+      <c r="L43">
+        <f>SUMIFS(G$3:G$38,J$3:J$38,K$42)</f>
+        <v>3855</v>
+      </c>
+      <c r="M43">
+        <f>SUMIFS(Q$3:Q$38,J$3:J$38,K$42)-INT(COUNTIFS(J$3:J$38,K$42,M$3:M$38,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+      <c r="O43" t="s">
+        <v>135</v>
+      </c>
+      <c r="P43">
+        <f>L48</f>
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="K44" t="s">
+        <v>200</v>
+      </c>
+      <c r="L44">
+        <f>-SUMIFS(H$3:H$38,J$3:J$38,K$42)+M44*5</f>
+        <v>-210</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$38,J$3:J$38,K$42)-INT(COUNTIFS(J$3:J$38,K$42,M$3:M$38,"*gộp*")/2)</f>
+        <v>10</v>
+      </c>
+      <c r="O44" t="s">
+        <v>734</v>
+      </c>
+      <c r="P44">
+        <f>L56</f>
+        <v>7243</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="3">
+        <f>-SUMIFS(I$3:I$38,B$3:B$38,A$42,P$3:P$38,"xx",N$3:N$38,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="7">
+        <f>SUMIFS(Q$3:Q$38,B$3:B$38,A$42,P$3:P$38,"xx",N$3:N$38,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>202</v>
+      </c>
+      <c r="O45" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45">
+        <f>L64</f>
+        <v>6739</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" s="5">
+        <f>SUBTOTAL(9,C43:C45)</f>
+        <v>17471</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46">
+        <f>E43</f>
+        <v>36</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O46" t="s">
+        <v>207</v>
+      </c>
+      <c r="P46">
+        <f>-C50</f>
+        <v>-17471</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="K47" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P47" s="9">
+        <f>SUBTOTAL(9,P43:P46)</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B48" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="L48" s="18">
+        <f>SUBTOTAL(9,L43:L47)</f>
+        <v>3645</v>
+      </c>
+      <c r="M48" s="18">
+        <f>M43</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B50" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C50" s="1">
+        <f>C46+C47+C48</f>
+        <v>17471</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>197</v>
+      </c>
+      <c r="L51">
+        <f>SUMIFS(G$3:G$38,J$3:J$38,K$50)</f>
+        <v>7500</v>
+      </c>
+      <c r="M51">
+        <f>SUMIFS(Q$3:Q$38,J$3:J$38,K$50)-INT(COUNTIFS(J$3:J$38,K$50,M$3:M$38,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>200</v>
+      </c>
+      <c r="L52">
+        <f>SUM(H41:H43)+SUMIFS(H$3:H$38,J$3:J$38,K$50,M$3:M$38,"*gộp*")/2</f>
+        <v>-257</v>
+      </c>
+      <c r="M52">
+        <f>SUMIFS(Q$3:Q$38,J$3:J$38,K$50)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L56" s="18">
+        <f>SUBTOTAL(9,L51:L55)</f>
+        <v>7243</v>
+      </c>
+      <c r="M56" s="18">
+        <f>M51</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
+        <v>197</v>
+      </c>
+      <c r="L59">
+        <f>SUMIFS(G$3:G$38,J$3:J$38,K$58)</f>
+        <v>7146</v>
+      </c>
+      <c r="M59">
+        <f>SUMIFS(Q$3:Q$38,J$3:J$38,K$58)-INT(COUNTIFS(J$3:J$38,K$58,M$3:M$38,"*gộp*")/2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K60" t="s">
+        <v>200</v>
+      </c>
+      <c r="L60">
+        <f>-SUMIFS(H$3:H$38,J$3:J$38,K$58)+M60*5</f>
+        <v>-335</v>
+      </c>
+      <c r="M60">
+        <f>SUMIFS(Q$3:Q$38,J$3:J$38,K$58)-INT(COUNTIFS(J$3:J$38,K$58,M$3:M$38,"*gộp*")/2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K61" t="s">
+        <v>202</v>
+      </c>
+      <c r="L61">
+        <f>-M61*2</f>
+        <v>-72</v>
+      </c>
+      <c r="M61">
+        <f>E46-(COUNTIFS(M$3:M$38,"*gộp*")/2)-COUNTIFS(M$3:M$38,"*đơn trả*")-COUNTIFS(M$3:M$38,"*hàng tỉnh*")</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K62" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K63" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L64" s="18">
+        <f>SUBTOTAL(9,L59:L63)</f>
+        <v>6739</v>
+      </c>
+      <c r="M64" s="18">
+        <f>M59</f>
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P38" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P38">
+      <sortCondition ref="J2:J38"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9B982-EAEB-4F31-86BF-4D059AFDEA27}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -13933,7 +16330,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>535</v>
+        <v>631</v>
       </c>
       <c r="B1" s="10">
         <v>2026</v>
@@ -13941,19 +16338,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>536</v>
+        <v>632</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>537</v>
+        <v>633</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>538</v>
+        <v>634</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>539</v>
+        <v>635</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>540</v>
+        <v>636</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -14088,7 +16485,7 @@
       </c>
       <c r="B9" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C9" s="13">
         <f t="shared" ca="1" si="2"/>
@@ -14100,7 +16497,7 @@
       </c>
       <c r="E9" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -14504,16 +16901,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="14" t="s">
-        <v>541</v>
+        <v>637</v>
       </c>
       <c r="E29" s="14">
         <f ca="1">SUBTOTAL(9,E4:E28)</f>
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D30" s="14" t="s">
-        <v>542</v>
+        <v>638</v>
       </c>
       <c r="E30" s="14" cm="1">
         <f t="array" ref="E30" ca="1">SUMPRODUCT(
@@ -14525,29 +16922,29 @@
         ),
     0)
 )</f>
-        <v>488</v>
+        <v>644</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D31" s="14" t="s">
-        <v>543</v>
+        <v>639</v>
       </c>
       <c r="E31" s="14">
         <f ca="1">-E29*2</f>
-        <v>-264</v>
+        <v>-336</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D32" s="14" t="s">
-        <v>544</v>
+        <v>640</v>
       </c>
       <c r="E32" s="14">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>224</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A2:E28" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C3:D28">
     <cfRule type="expression" dxfId="0" priority="1">
